--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/26,06,26 ПОКОМ ЗПФ/Копия дв 250626 млрсч пок зпф от Боярко.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/26,06,26 ПОКОМ ЗПФ/Копия дв 250626 млрсч пок зпф от Боярко.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\06,26\26,06,26 ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22781CA3-78B6-4CF4-8C0A-824A7E7810B2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B90CFE-DF3C-471F-8A89-2344570B2778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,15 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AJ$67</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -528,7 +520,7 @@
     <t>итого</t>
   </si>
   <si>
-    <t>30,06,</t>
+    <t>ОТМЕНА</t>
   </si>
 </sst>
 </file>

--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/26,06,26 ПОКОМ ЗПФ/Копия дв 250626 млрсч пок зпф от Боярко.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/26,06,26 ПОКОМ ЗПФ/Копия дв 250626 млрсч пок зпф от Боярко.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\06,26\26,06,26 ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B90CFE-DF3C-471F-8A89-2344570B2778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55DBDEA0-47C5-438D-AAD0-7EE6C457A1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -532,7 +532,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.00_ ;[Red]\-0.00\ "/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -578,6 +578,22 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
@@ -660,7 +676,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -686,6 +702,11 @@
     <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1004,7 +1025,9 @@
     <col min="12" max="12" width="5.42578125" customWidth="1"/>
     <col min="13" max="14" width="0.5703125" customWidth="1"/>
     <col min="15" max="16" width="6" customWidth="1"/>
-    <col min="17" max="20" width="7" customWidth="1"/>
+    <col min="17" max="18" width="7" customWidth="1"/>
+    <col min="19" max="19" width="7" style="29" customWidth="1"/>
+    <col min="20" max="20" width="7" customWidth="1"/>
     <col min="21" max="21" width="15" customWidth="1"/>
     <col min="22" max="23" width="5" customWidth="1"/>
     <col min="24" max="28" width="6" customWidth="1"/>
@@ -1039,7 +1062,7 @@
       <c r="R1" s="24">
         <v>1.6</v>
       </c>
-      <c r="S1" s="1"/>
+      <c r="S1" s="25"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
@@ -1093,7 +1116,7 @@
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
+      <c r="S2" s="25"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
@@ -1277,7 +1300,7 @@
       </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
+      <c r="S4" s="25"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -1372,7 +1395,7 @@
         <f t="shared" si="0"/>
         <v>10815.000000000002</v>
       </c>
-      <c r="S5" s="4">
+      <c r="S5" s="26">
         <f t="shared" si="0"/>
         <v>11456</v>
       </c>
@@ -1424,7 +1447,10 @@
         <v>16.200793650793653</v>
       </c>
       <c r="AK5" s="1"/>
-      <c r="AL5" s="1"/>
+      <c r="AL5" s="4">
+        <f>SUM(AL6:AL500)</f>
+        <v>1236.1780000000001</v>
+      </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="1"/>
       <c r="AO5" s="1"/>
@@ -1483,7 +1509,7 @@
       </c>
       <c r="Q6" s="18"/>
       <c r="R6" s="18"/>
-      <c r="S6" s="18"/>
+      <c r="S6" s="27"/>
       <c r="T6" s="18"/>
       <c r="U6" s="15"/>
       <c r="V6" s="15">
@@ -1577,7 +1603,7 @@
       </c>
       <c r="Q7" s="18"/>
       <c r="R7" s="18"/>
-      <c r="S7" s="18"/>
+      <c r="S7" s="27"/>
       <c r="T7" s="18"/>
       <c r="U7" s="15"/>
       <c r="V7" s="15">
@@ -1671,7 +1697,7 @@
       </c>
       <c r="Q8" s="18"/>
       <c r="R8" s="18"/>
-      <c r="S8" s="18"/>
+      <c r="S8" s="27"/>
       <c r="T8" s="18"/>
       <c r="U8" s="15"/>
       <c r="V8" s="15">
@@ -1768,7 +1794,7 @@
         <f>T9</f>
         <v>200</v>
       </c>
-      <c r="S9" s="5">
+      <c r="S9" s="28">
         <f t="shared" ref="S9:S20" si="5">AE9*AF9</f>
         <v>168</v>
       </c>
@@ -1826,7 +1852,10 @@
         <v>0.2</v>
       </c>
       <c r="AK9" s="1"/>
-      <c r="AL9" s="1"/>
+      <c r="AL9" s="1">
+        <f>P9*G9</f>
+        <v>1.716</v>
+      </c>
       <c r="AM9" s="1"/>
       <c r="AN9" s="1"/>
       <c r="AO9" s="1"/>
@@ -1892,7 +1921,7 @@
         <f t="shared" ref="R10:R13" si="10">T10</f>
         <v>400</v>
       </c>
-      <c r="S10" s="5">
+      <c r="S10" s="28">
         <f t="shared" si="5"/>
         <v>336</v>
       </c>
@@ -1950,7 +1979,10 @@
         <v>0.4</v>
       </c>
       <c r="AK10" s="1"/>
-      <c r="AL10" s="1"/>
+      <c r="AL10" s="1">
+        <f t="shared" ref="AL10:AL66" si="11">P10*G10</f>
+        <v>11.639999999999999</v>
+      </c>
       <c r="AM10" s="1"/>
       <c r="AN10" s="1"/>
       <c r="AO10" s="1"/>
@@ -2016,7 +2048,7 @@
         <f t="shared" si="10"/>
         <v>300</v>
       </c>
-      <c r="S11" s="5">
+      <c r="S11" s="28">
         <f t="shared" si="5"/>
         <v>336</v>
       </c>
@@ -2074,7 +2106,10 @@
         <v>0.4</v>
       </c>
       <c r="AK11" s="1"/>
-      <c r="AL11" s="1"/>
+      <c r="AL11" s="1">
+        <f t="shared" si="11"/>
+        <v>12.376000000000001</v>
+      </c>
       <c r="AM11" s="1"/>
       <c r="AN11" s="1"/>
       <c r="AO11" s="1"/>
@@ -2140,7 +2175,7 @@
         <f t="shared" si="10"/>
         <v>200</v>
       </c>
-      <c r="S12" s="5">
+      <c r="S12" s="28">
         <f t="shared" si="5"/>
         <v>168</v>
       </c>
@@ -2198,7 +2233,10 @@
         <v>0.2</v>
       </c>
       <c r="AK12" s="1"/>
-      <c r="AL12" s="1"/>
+      <c r="AL12" s="1">
+        <f t="shared" si="11"/>
+        <v>12.24</v>
+      </c>
       <c r="AM12" s="1"/>
       <c r="AN12" s="1"/>
       <c r="AO12" s="1"/>
@@ -2264,7 +2302,7 @@
         <f t="shared" si="10"/>
         <v>200</v>
       </c>
-      <c r="S13" s="5">
+      <c r="S13" s="28">
         <f t="shared" si="5"/>
         <v>168</v>
       </c>
@@ -2322,7 +2360,10 @@
         <v>0.2</v>
       </c>
       <c r="AK13" s="1"/>
-      <c r="AL13" s="1"/>
+      <c r="AL13" s="1">
+        <f t="shared" si="11"/>
+        <v>15.743999999999998</v>
+      </c>
       <c r="AM13" s="1"/>
       <c r="AN13" s="1"/>
       <c r="AO13" s="1"/>
@@ -2387,10 +2428,10 @@
         <v>132.59999999999997</v>
       </c>
       <c r="R14" s="5">
-        <f t="shared" ref="R14:R21" si="11">14*P14-O14-F14</f>
+        <f t="shared" ref="R14:R21" si="12">14*P14-O14-F14</f>
         <v>132.59999999999997</v>
       </c>
-      <c r="S14" s="5">
+      <c r="S14" s="28">
         <f t="shared" si="5"/>
         <v>168</v>
       </c>
@@ -2446,7 +2487,10 @@
         <v>0.2</v>
       </c>
       <c r="AK14" s="1"/>
-      <c r="AL14" s="1"/>
+      <c r="AL14" s="1">
+        <f t="shared" si="11"/>
+        <v>8.2560000000000002</v>
+      </c>
       <c r="AM14" s="1"/>
       <c r="AN14" s="1"/>
       <c r="AO14" s="1"/>
@@ -2516,7 +2560,7 @@
         <f>Q15*$R$1</f>
         <v>645.12000000000012</v>
       </c>
-      <c r="S15" s="5">
+      <c r="S15" s="28">
         <f t="shared" si="5"/>
         <v>672</v>
       </c>
@@ -2572,7 +2616,10 @@
         <v>0.8</v>
       </c>
       <c r="AK15" s="1"/>
-      <c r="AL15" s="1"/>
+      <c r="AL15" s="1">
+        <f t="shared" si="11"/>
+        <v>26.591999999999999</v>
+      </c>
       <c r="AM15" s="1"/>
       <c r="AN15" s="1"/>
       <c r="AO15" s="1"/>
@@ -2638,7 +2685,7 @@
         <f>T16</f>
         <v>300</v>
       </c>
-      <c r="S16" s="5">
+      <c r="S16" s="28">
         <f t="shared" si="5"/>
         <v>336</v>
       </c>
@@ -2696,7 +2743,10 @@
         <v>0.6</v>
       </c>
       <c r="AK16" s="1"/>
-      <c r="AL16" s="1"/>
+      <c r="AL16" s="1">
+        <f t="shared" si="11"/>
+        <v>8.64</v>
+      </c>
       <c r="AM16" s="1"/>
       <c r="AN16" s="1"/>
       <c r="AO16" s="1"/>
@@ -2761,10 +2811,10 @@
         <v>220.60000000000002</v>
       </c>
       <c r="R17" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>220.60000000000002</v>
       </c>
-      <c r="S17" s="5">
+      <c r="S17" s="28">
         <f t="shared" si="5"/>
         <v>280</v>
       </c>
@@ -2820,7 +2870,10 @@
         <v>0.4</v>
       </c>
       <c r="AK17" s="1"/>
-      <c r="AL17" s="1"/>
+      <c r="AL17" s="1">
+        <f t="shared" si="11"/>
+        <v>14.903999999999998</v>
+      </c>
       <c r="AM17" s="1"/>
       <c r="AN17" s="1"/>
       <c r="AO17" s="1"/>
@@ -2881,7 +2934,7 @@
       </c>
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
-      <c r="S18" s="5">
+      <c r="S18" s="28">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2937,7 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AK18" s="1"/>
-      <c r="AL18" s="1"/>
+      <c r="AL18" s="1">
+        <f t="shared" si="11"/>
+        <v>1.1199999999999999</v>
+      </c>
       <c r="AM18" s="1"/>
       <c r="AN18" s="1"/>
       <c r="AO18" s="1"/>
@@ -3000,7 +3056,7 @@
       </c>
       <c r="Q19" s="5"/>
       <c r="R19" s="5"/>
-      <c r="S19" s="5">
+      <c r="S19" s="28">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3056,7 +3112,10 @@
         <v>0</v>
       </c>
       <c r="AK19" s="1"/>
-      <c r="AL19" s="1"/>
+      <c r="AL19" s="1">
+        <f t="shared" si="11"/>
+        <v>7.28</v>
+      </c>
       <c r="AM19" s="1"/>
       <c r="AN19" s="1"/>
       <c r="AO19" s="1"/>
@@ -3118,7 +3177,7 @@
         <f>T20</f>
         <v>100</v>
       </c>
-      <c r="S20" s="5">
+      <c r="S20" s="28">
         <f t="shared" si="5"/>
         <v>168</v>
       </c>
@@ -3176,7 +3235,10 @@
         <v>0.2</v>
       </c>
       <c r="AK20" s="1"/>
-      <c r="AL20" s="1"/>
+      <c r="AL20" s="1">
+        <f t="shared" si="11"/>
+        <v>20.8</v>
+      </c>
       <c r="AM20" s="1"/>
       <c r="AN20" s="1"/>
       <c r="AO20" s="1"/>
@@ -3243,10 +3305,10 @@
         <v>91</v>
       </c>
       <c r="R21" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>91</v>
       </c>
-      <c r="S21" s="5">
+      <c r="S21" s="28">
         <f>AE21*AF21</f>
         <v>112</v>
       </c>
@@ -3302,7 +3364,10 @@
         <v>0.23333333333333334</v>
       </c>
       <c r="AK21" s="1"/>
-      <c r="AL21" s="1"/>
+      <c r="AL21" s="1">
+        <f t="shared" si="11"/>
+        <v>30</v>
+      </c>
       <c r="AM21" s="1"/>
       <c r="AN21" s="1"/>
       <c r="AO21" s="1"/>
@@ -3361,7 +3426,7 @@
       </c>
       <c r="Q22" s="18"/>
       <c r="R22" s="18"/>
-      <c r="S22" s="18"/>
+      <c r="S22" s="27"/>
       <c r="T22" s="18"/>
       <c r="U22" s="15"/>
       <c r="V22" s="15">
@@ -3396,7 +3461,10 @@
       <c r="AI22" s="15"/>
       <c r="AJ22" s="19"/>
       <c r="AK22" s="1"/>
-      <c r="AL22" s="1"/>
+      <c r="AL22" s="1">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM22" s="1"/>
       <c r="AN22" s="1"/>
       <c r="AO22" s="1"/>
@@ -3459,11 +3527,11 @@
       </c>
       <c r="Q23" s="5"/>
       <c r="R23" s="5">
-        <f t="shared" ref="R23:R26" si="12">T23</f>
+        <f t="shared" ref="R23:R26" si="13">T23</f>
         <v>100</v>
       </c>
-      <c r="S23" s="5">
-        <f t="shared" ref="S23:S66" si="13">AE23*AF23</f>
+      <c r="S23" s="28">
+        <f t="shared" ref="S23:S66" si="14">AE23*AF23</f>
         <v>132</v>
       </c>
       <c r="T23" s="23">
@@ -3497,18 +3565,18 @@
         <v>162</v>
       </c>
       <c r="AD23" s="1">
-        <f t="shared" ref="AD23:AD66" si="14">G23*R23</f>
+        <f t="shared" ref="AD23:AD66" si="15">G23*R23</f>
         <v>100</v>
       </c>
       <c r="AE23" s="10">
         <v>5.5</v>
       </c>
       <c r="AF23" s="1">
-        <f t="shared" ref="AF23:AF66" si="15">MROUND(R23, AE23*AH23)/AE23</f>
+        <f t="shared" ref="AF23:AF66" si="16">MROUND(R23, AE23*AH23)/AE23</f>
         <v>24</v>
       </c>
       <c r="AG23" s="1">
-        <f t="shared" ref="AG23:AG66" si="16">AF23*AE23*G23</f>
+        <f t="shared" ref="AG23:AG66" si="17">AF23*AE23*G23</f>
         <v>132</v>
       </c>
       <c r="AH23" s="1">
@@ -3518,11 +3586,14 @@
         <v>84</v>
       </c>
       <c r="AJ23" s="10">
-        <f t="shared" ref="AJ23:AJ66" si="17">AF23/AI23</f>
+        <f t="shared" ref="AJ23:AJ66" si="18">AF23/AI23</f>
         <v>0.2857142857142857</v>
       </c>
       <c r="AK23" s="1"/>
-      <c r="AL23" s="1"/>
+      <c r="AL23" s="1">
+        <f t="shared" si="11"/>
+        <v>9.9</v>
+      </c>
       <c r="AM23" s="1"/>
       <c r="AN23" s="1"/>
       <c r="AO23" s="1"/>
@@ -3585,11 +3656,11 @@
       </c>
       <c r="Q24" s="5"/>
       <c r="R24" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
-      <c r="S24" s="5">
-        <f t="shared" si="13"/>
+      <c r="S24" s="28">
+        <f t="shared" si="14"/>
         <v>84</v>
       </c>
       <c r="T24" s="23">
@@ -3621,18 +3692,18 @@
       </c>
       <c r="AC24" s="1"/>
       <c r="AD24" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>100</v>
       </c>
       <c r="AE24" s="10">
         <v>3</v>
       </c>
       <c r="AF24" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>28</v>
       </c>
       <c r="AG24" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>84</v>
       </c>
       <c r="AH24" s="1">
@@ -3642,11 +3713,14 @@
         <v>126</v>
       </c>
       <c r="AJ24" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.22222222222222221</v>
       </c>
       <c r="AK24" s="1"/>
-      <c r="AL24" s="1"/>
+      <c r="AL24" s="1">
+        <f t="shared" si="11"/>
+        <v>10.8</v>
+      </c>
       <c r="AM24" s="1"/>
       <c r="AN24" s="1"/>
       <c r="AO24" s="1"/>
@@ -3709,11 +3783,11 @@
       </c>
       <c r="Q25" s="5"/>
       <c r="R25" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>200</v>
       </c>
-      <c r="S25" s="5">
-        <f t="shared" si="13"/>
+      <c r="S25" s="28">
+        <f t="shared" si="14"/>
         <v>168</v>
       </c>
       <c r="T25" s="23">
@@ -3747,18 +3821,18 @@
         <v>81</v>
       </c>
       <c r="AD25" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>50</v>
       </c>
       <c r="AE25" s="10">
         <v>6</v>
       </c>
       <c r="AF25" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>28</v>
       </c>
       <c r="AG25" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>42</v>
       </c>
       <c r="AH25" s="1">
@@ -3768,11 +3842,14 @@
         <v>140</v>
       </c>
       <c r="AJ25" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.2</v>
       </c>
       <c r="AK25" s="1"/>
-      <c r="AL25" s="1"/>
+      <c r="AL25" s="1">
+        <f t="shared" si="11"/>
+        <v>11.05</v>
+      </c>
       <c r="AM25" s="1"/>
       <c r="AN25" s="1"/>
       <c r="AO25" s="1"/>
@@ -3835,11 +3912,11 @@
       </c>
       <c r="Q26" s="5"/>
       <c r="R26" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
-      <c r="S26" s="5">
-        <f t="shared" si="13"/>
+      <c r="S26" s="28">
+        <f t="shared" si="14"/>
         <v>84</v>
       </c>
       <c r="T26" s="23">
@@ -3873,18 +3950,18 @@
         <v>162</v>
       </c>
       <c r="AD26" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>25</v>
       </c>
       <c r="AE26" s="10">
         <v>6</v>
       </c>
       <c r="AF26" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>14</v>
       </c>
       <c r="AG26" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>21</v>
       </c>
       <c r="AH26" s="1">
@@ -3894,11 +3971,14 @@
         <v>140</v>
       </c>
       <c r="AJ26" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.1</v>
       </c>
       <c r="AK26" s="1"/>
-      <c r="AL26" s="1"/>
+      <c r="AL26" s="1">
+        <f t="shared" si="11"/>
+        <v>6.1</v>
+      </c>
       <c r="AM26" s="1"/>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1"/>
@@ -3966,8 +4046,8 @@
         <f>Q27*$R$1</f>
         <v>785.2800000000002</v>
       </c>
-      <c r="S27" s="5">
-        <f t="shared" si="13"/>
+      <c r="S27" s="28">
+        <f t="shared" si="14"/>
         <v>792</v>
       </c>
       <c r="T27" s="5"/>
@@ -3997,18 +4077,18 @@
       </c>
       <c r="AC27" s="1"/>
       <c r="AD27" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>785.2800000000002</v>
       </c>
       <c r="AE27" s="10">
         <v>6</v>
       </c>
       <c r="AF27" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>132</v>
       </c>
       <c r="AG27" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>792</v>
       </c>
       <c r="AH27" s="1">
@@ -4018,11 +4098,14 @@
         <v>84</v>
       </c>
       <c r="AJ27" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="AK27" s="1"/>
-      <c r="AL27" s="1"/>
+      <c r="AL27" s="1">
+        <f t="shared" si="11"/>
+        <v>61.2</v>
+      </c>
       <c r="AM27" s="1"/>
       <c r="AN27" s="1"/>
       <c r="AO27" s="1"/>
@@ -4083,11 +4166,11 @@
       </c>
       <c r="Q28" s="5"/>
       <c r="R28" s="5">
-        <f t="shared" ref="R28:R30" si="18">T28</f>
+        <f t="shared" ref="R28:R30" si="19">T28</f>
         <v>300</v>
       </c>
-      <c r="S28" s="5">
-        <f t="shared" si="13"/>
+      <c r="S28" s="28">
+        <f t="shared" si="14"/>
         <v>336</v>
       </c>
       <c r="T28" s="23">
@@ -4119,18 +4202,18 @@
       </c>
       <c r="AC28" s="1"/>
       <c r="AD28" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>69</v>
       </c>
       <c r="AE28" s="10">
         <v>12</v>
       </c>
       <c r="AF28" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>28</v>
       </c>
       <c r="AG28" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>77.28</v>
       </c>
       <c r="AH28" s="1">
@@ -4140,11 +4223,14 @@
         <v>70</v>
       </c>
       <c r="AJ28" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.4</v>
       </c>
       <c r="AK28" s="1"/>
-      <c r="AL28" s="1"/>
+      <c r="AL28" s="1">
+        <f t="shared" si="11"/>
+        <v>3.266</v>
+      </c>
       <c r="AM28" s="1"/>
       <c r="AN28" s="1"/>
       <c r="AO28" s="1"/>
@@ -4207,11 +4293,11 @@
       </c>
       <c r="Q29" s="5"/>
       <c r="R29" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>300</v>
       </c>
-      <c r="S29" s="5">
-        <f t="shared" si="13"/>
+      <c r="S29" s="28">
+        <f t="shared" si="14"/>
         <v>336</v>
       </c>
       <c r="T29" s="23">
@@ -4243,18 +4329,18 @@
       </c>
       <c r="AC29" s="1"/>
       <c r="AD29" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>75</v>
       </c>
       <c r="AE29" s="10">
         <v>12</v>
       </c>
       <c r="AF29" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>28</v>
       </c>
       <c r="AG29" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>84</v>
       </c>
       <c r="AH29" s="1">
@@ -4264,11 +4350,14 @@
         <v>70</v>
       </c>
       <c r="AJ29" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.4</v>
       </c>
       <c r="AK29" s="1"/>
-      <c r="AL29" s="1"/>
+      <c r="AL29" s="1">
+        <f t="shared" si="11"/>
+        <v>19.05</v>
+      </c>
       <c r="AM29" s="1"/>
       <c r="AN29" s="1"/>
       <c r="AO29" s="1"/>
@@ -4331,11 +4420,11 @@
       </c>
       <c r="Q30" s="5"/>
       <c r="R30" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>200</v>
       </c>
-      <c r="S30" s="5">
-        <f t="shared" si="13"/>
+      <c r="S30" s="28">
+        <f t="shared" si="14"/>
         <v>168</v>
       </c>
       <c r="T30" s="23">
@@ -4367,18 +4456,18 @@
       </c>
       <c r="AC30" s="1"/>
       <c r="AD30" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>50</v>
       </c>
       <c r="AE30" s="10">
         <v>12</v>
       </c>
       <c r="AF30" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>14</v>
       </c>
       <c r="AG30" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>42</v>
       </c>
       <c r="AH30" s="1">
@@ -4388,11 +4477,14 @@
         <v>70</v>
       </c>
       <c r="AJ30" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.2</v>
       </c>
       <c r="AK30" s="1"/>
-      <c r="AL30" s="1"/>
+      <c r="AL30" s="1">
+        <f t="shared" si="11"/>
+        <v>21.6</v>
+      </c>
       <c r="AM30" s="1"/>
       <c r="AN30" s="1"/>
       <c r="AO30" s="1"/>
@@ -4455,8 +4547,8 @@
       </c>
       <c r="Q31" s="5"/>
       <c r="R31" s="5"/>
-      <c r="S31" s="5">
-        <f t="shared" si="13"/>
+      <c r="S31" s="28">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T31" s="5"/>
@@ -4488,20 +4580,20 @@
         <v>76</v>
       </c>
       <c r="AD31" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE31" s="10">
         <v>12</v>
       </c>
       <c r="AF31" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AG31" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
+      <c r="AG31" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="AH31" s="1">
         <v>14</v>
       </c>
@@ -4509,11 +4601,14 @@
         <v>70</v>
       </c>
       <c r="AJ31" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AK31" s="1"/>
-      <c r="AL31" s="1"/>
+      <c r="AL31" s="1">
+        <f t="shared" si="11"/>
+        <v>22.25</v>
+      </c>
       <c r="AM31" s="1"/>
       <c r="AN31" s="1"/>
       <c r="AO31" s="1"/>
@@ -4574,7 +4669,7 @@
       </c>
       <c r="Q32" s="18"/>
       <c r="R32" s="18"/>
-      <c r="S32" s="18"/>
+      <c r="S32" s="27"/>
       <c r="T32" s="18"/>
       <c r="U32" s="15"/>
       <c r="V32" s="15">
@@ -4609,7 +4704,10 @@
       <c r="AI32" s="15"/>
       <c r="AJ32" s="19"/>
       <c r="AK32" s="1"/>
-      <c r="AL32" s="1"/>
+      <c r="AL32" s="1">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM32" s="1"/>
       <c r="AN32" s="1"/>
       <c r="AO32" s="1"/>
@@ -4670,11 +4768,11 @@
         <v>92.799999999999983</v>
       </c>
       <c r="R33" s="5">
-        <f t="shared" ref="R33:R37" si="19">T33</f>
+        <f t="shared" ref="R33:R37" si="20">T33</f>
         <v>350</v>
       </c>
-      <c r="S33" s="5">
-        <f t="shared" si="13"/>
+      <c r="S33" s="28">
+        <f t="shared" si="14"/>
         <v>336</v>
       </c>
       <c r="T33" s="23">
@@ -4706,18 +4804,18 @@
       </c>
       <c r="AC33" s="1"/>
       <c r="AD33" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>87.5</v>
       </c>
       <c r="AE33" s="10">
         <v>12</v>
       </c>
       <c r="AF33" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>28</v>
       </c>
       <c r="AG33" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>84</v>
       </c>
       <c r="AH33" s="1">
@@ -4727,11 +4825,14 @@
         <v>70</v>
       </c>
       <c r="AJ33" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.4</v>
       </c>
       <c r="AK33" s="1"/>
-      <c r="AL33" s="1"/>
+      <c r="AL33" s="1">
+        <f t="shared" si="11"/>
+        <v>2.65</v>
+      </c>
       <c r="AM33" s="1"/>
       <c r="AN33" s="1"/>
       <c r="AO33" s="1"/>
@@ -4794,11 +4895,11 @@
       </c>
       <c r="Q34" s="5"/>
       <c r="R34" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>100</v>
       </c>
-      <c r="S34" s="5">
-        <f t="shared" si="13"/>
+      <c r="S34" s="28">
+        <f t="shared" si="14"/>
         <v>96</v>
       </c>
       <c r="T34" s="23">
@@ -4830,18 +4931,18 @@
       </c>
       <c r="AC34" s="1"/>
       <c r="AD34" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>70</v>
       </c>
       <c r="AE34" s="10">
         <v>4</v>
       </c>
       <c r="AF34" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>24</v>
       </c>
       <c r="AG34" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>67.199999999999989</v>
       </c>
       <c r="AH34" s="1">
@@ -4851,11 +4952,14 @@
         <v>84</v>
       </c>
       <c r="AJ34" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="AK34" s="1"/>
-      <c r="AL34" s="1"/>
+      <c r="AL34" s="1">
+        <f t="shared" si="11"/>
+        <v>12.179999999999998</v>
+      </c>
       <c r="AM34" s="1"/>
       <c r="AN34" s="1"/>
       <c r="AO34" s="1"/>
@@ -4918,11 +5022,11 @@
       </c>
       <c r="Q35" s="5"/>
       <c r="R35" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>150</v>
       </c>
-      <c r="S35" s="5">
-        <f t="shared" si="13"/>
+      <c r="S35" s="28">
+        <f t="shared" si="14"/>
         <v>192</v>
       </c>
       <c r="T35" s="23">
@@ -4954,18 +5058,18 @@
       </c>
       <c r="AC35" s="1"/>
       <c r="AD35" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>105</v>
       </c>
       <c r="AE35" s="10">
         <v>8</v>
       </c>
       <c r="AF35" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>24</v>
       </c>
       <c r="AG35" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>134.39999999999998</v>
       </c>
       <c r="AH35" s="1">
@@ -4975,11 +5079,14 @@
         <v>84</v>
       </c>
       <c r="AJ35" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="AK35" s="1"/>
-      <c r="AL35" s="1"/>
+      <c r="AL35" s="1">
+        <f t="shared" si="11"/>
+        <v>17.779999999999998</v>
+      </c>
       <c r="AM35" s="1"/>
       <c r="AN35" s="1"/>
       <c r="AO35" s="1"/>
@@ -5042,11 +5149,11 @@
       </c>
       <c r="Q36" s="5"/>
       <c r="R36" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>50</v>
       </c>
-      <c r="S36" s="5">
-        <f t="shared" si="13"/>
+      <c r="S36" s="28">
+        <f t="shared" si="14"/>
         <v>96</v>
       </c>
       <c r="T36" s="23">
@@ -5078,18 +5185,18 @@
       </c>
       <c r="AC36" s="1"/>
       <c r="AD36" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>35</v>
       </c>
       <c r="AE36" s="10">
         <v>8</v>
       </c>
       <c r="AF36" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
       <c r="AG36" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>67.199999999999989</v>
       </c>
       <c r="AH36" s="1">
@@ -5099,11 +5206,14 @@
         <v>84</v>
       </c>
       <c r="AJ36" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="AK36" s="1"/>
-      <c r="AL36" s="1"/>
+      <c r="AL36" s="1">
+        <f t="shared" si="11"/>
+        <v>13.86</v>
+      </c>
       <c r="AM36" s="1"/>
       <c r="AN36" s="1"/>
       <c r="AO36" s="1"/>
@@ -5168,11 +5278,11 @@
         <v>219.39999999999986</v>
       </c>
       <c r="R37" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>550</v>
       </c>
-      <c r="S37" s="5">
-        <f t="shared" si="13"/>
+      <c r="S37" s="28">
+        <f t="shared" si="14"/>
         <v>600</v>
       </c>
       <c r="T37" s="23">
@@ -5204,18 +5314,18 @@
       </c>
       <c r="AC37" s="1"/>
       <c r="AD37" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>385</v>
       </c>
       <c r="AE37" s="10">
         <v>10</v>
       </c>
       <c r="AF37" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>60</v>
       </c>
       <c r="AG37" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>420</v>
       </c>
       <c r="AH37" s="1">
@@ -5225,11 +5335,14 @@
         <v>84</v>
       </c>
       <c r="AJ37" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="AK37" s="1"/>
-      <c r="AL37" s="1"/>
+      <c r="AL37" s="1">
+        <f t="shared" si="11"/>
+        <v>48.719999999999992</v>
+      </c>
       <c r="AM37" s="1"/>
       <c r="AN37" s="1"/>
       <c r="AO37" s="1"/>
@@ -5278,7 +5391,7 @@
         <v>85</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L67" si="20">E38-K38</f>
+        <f t="shared" ref="L38:L67" si="21">E38-K38</f>
         <v>-3</v>
       </c>
       <c r="M38" s="1"/>
@@ -5292,8 +5405,8 @@
       </c>
       <c r="Q38" s="5"/>
       <c r="R38" s="5"/>
-      <c r="S38" s="5">
-        <f t="shared" si="13"/>
+      <c r="S38" s="28">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T38" s="5"/>
@@ -5325,20 +5438,20 @@
         <v>163</v>
       </c>
       <c r="AD38" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE38" s="10">
         <v>10</v>
       </c>
       <c r="AF38" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AG38" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
+      <c r="AG38" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="AH38" s="1">
         <v>12</v>
       </c>
@@ -5346,11 +5459,14 @@
         <v>84</v>
       </c>
       <c r="AJ38" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AK38" s="1"/>
-      <c r="AL38" s="1"/>
+      <c r="AL38" s="1">
+        <f t="shared" si="11"/>
+        <v>11.479999999999999</v>
+      </c>
       <c r="AM38" s="1"/>
       <c r="AN38" s="1"/>
       <c r="AO38" s="1"/>
@@ -5399,7 +5515,7 @@
         <v>326</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-23</v>
       </c>
       <c r="M39" s="1"/>
@@ -5415,11 +5531,11 @@
         <v>177.39999999999998</v>
       </c>
       <c r="R39" s="5">
-        <f t="shared" ref="R39:R43" si="21">T39</f>
+        <f t="shared" ref="R39:R43" si="22">T39</f>
         <v>300</v>
       </c>
-      <c r="S39" s="5">
-        <f t="shared" si="13"/>
+      <c r="S39" s="28">
+        <f t="shared" si="14"/>
         <v>360</v>
       </c>
       <c r="T39" s="23">
@@ -5451,18 +5567,18 @@
       </c>
       <c r="AC39" s="1"/>
       <c r="AD39" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>210</v>
       </c>
       <c r="AE39" s="10">
         <v>10</v>
       </c>
       <c r="AF39" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>36</v>
       </c>
       <c r="AG39" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>251.99999999999997</v>
       </c>
       <c r="AH39" s="1">
@@ -5472,11 +5588,14 @@
         <v>84</v>
       </c>
       <c r="AJ39" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="AK39" s="1"/>
-      <c r="AL39" s="1"/>
+      <c r="AL39" s="1">
+        <f t="shared" si="11"/>
+        <v>42.42</v>
+      </c>
       <c r="AM39" s="1"/>
       <c r="AN39" s="1"/>
       <c r="AO39" s="1"/>
@@ -5525,7 +5644,7 @@
         <v>231</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-70</v>
       </c>
       <c r="M40" s="1"/>
@@ -5539,11 +5658,11 @@
       </c>
       <c r="Q40" s="5"/>
       <c r="R40" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>200</v>
       </c>
-      <c r="S40" s="5">
-        <f t="shared" si="13"/>
+      <c r="S40" s="28">
+        <f t="shared" si="14"/>
         <v>240</v>
       </c>
       <c r="T40" s="23">
@@ -5575,18 +5694,18 @@
       </c>
       <c r="AC40" s="1"/>
       <c r="AD40" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>140</v>
       </c>
       <c r="AE40" s="10">
         <v>10</v>
       </c>
       <c r="AF40" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>24</v>
       </c>
       <c r="AG40" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>168</v>
       </c>
       <c r="AH40" s="1">
@@ -5596,11 +5715,14 @@
         <v>84</v>
       </c>
       <c r="AJ40" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="AK40" s="1"/>
-      <c r="AL40" s="1"/>
+      <c r="AL40" s="1">
+        <f t="shared" si="11"/>
+        <v>22.54</v>
+      </c>
       <c r="AM40" s="1"/>
       <c r="AN40" s="1"/>
       <c r="AO40" s="1"/>
@@ -5649,7 +5771,7 @@
         <v>405</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-15</v>
       </c>
       <c r="M41" s="1"/>
@@ -5663,11 +5785,11 @@
       </c>
       <c r="Q41" s="5"/>
       <c r="R41" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>300</v>
       </c>
-      <c r="S41" s="5">
-        <f t="shared" si="13"/>
+      <c r="S41" s="28">
+        <f t="shared" si="14"/>
         <v>300</v>
       </c>
       <c r="T41" s="23">
@@ -5701,18 +5823,18 @@
         <v>76</v>
       </c>
       <c r="AD41" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>300</v>
       </c>
       <c r="AE41" s="10">
         <v>5</v>
       </c>
       <c r="AF41" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>60</v>
       </c>
       <c r="AG41" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>300</v>
       </c>
       <c r="AH41" s="1">
@@ -5722,11 +5844,14 @@
         <v>144</v>
       </c>
       <c r="AJ41" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.41666666666666669</v>
       </c>
       <c r="AK41" s="1"/>
-      <c r="AL41" s="1"/>
+      <c r="AL41" s="1">
+        <f t="shared" si="11"/>
+        <v>78</v>
+      </c>
       <c r="AM41" s="1"/>
       <c r="AN41" s="1"/>
       <c r="AO41" s="1"/>
@@ -5775,7 +5900,7 @@
         <v>165</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-26</v>
       </c>
       <c r="M42" s="1"/>
@@ -5789,11 +5914,11 @@
       </c>
       <c r="Q42" s="5"/>
       <c r="R42" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>100</v>
       </c>
-      <c r="S42" s="5">
-        <f t="shared" si="13"/>
+      <c r="S42" s="28">
+        <f t="shared" si="14"/>
         <v>192</v>
       </c>
       <c r="T42" s="23">
@@ -5825,18 +5950,18 @@
       </c>
       <c r="AC42" s="1"/>
       <c r="AD42" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>40</v>
       </c>
       <c r="AE42" s="10">
         <v>16</v>
       </c>
       <c r="AF42" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
       <c r="AG42" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>76.800000000000011</v>
       </c>
       <c r="AH42" s="1">
@@ -5846,11 +5971,14 @@
         <v>84</v>
       </c>
       <c r="AJ42" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="AK42" s="1"/>
-      <c r="AL42" s="1"/>
+      <c r="AL42" s="1">
+        <f t="shared" si="11"/>
+        <v>11.120000000000001</v>
+      </c>
       <c r="AM42" s="1"/>
       <c r="AN42" s="1"/>
       <c r="AO42" s="1"/>
@@ -5899,7 +6027,7 @@
         <v>595</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-11</v>
       </c>
       <c r="M43" s="1"/>
@@ -5913,11 +6041,11 @@
       </c>
       <c r="Q43" s="5"/>
       <c r="R43" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>200</v>
       </c>
-      <c r="S43" s="5">
-        <f t="shared" si="13"/>
+      <c r="S43" s="28">
+        <f t="shared" si="14"/>
         <v>240</v>
       </c>
       <c r="T43" s="23">
@@ -5951,18 +6079,18 @@
         <v>81</v>
       </c>
       <c r="AD43" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>140</v>
       </c>
       <c r="AE43" s="10">
         <v>10</v>
       </c>
       <c r="AF43" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>24</v>
       </c>
       <c r="AG43" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>168</v>
       </c>
       <c r="AH43" s="1">
@@ -5972,11 +6100,14 @@
         <v>84</v>
       </c>
       <c r="AJ43" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="AK43" s="1"/>
-      <c r="AL43" s="1"/>
+      <c r="AL43" s="1">
+        <f t="shared" si="11"/>
+        <v>81.759999999999991</v>
+      </c>
       <c r="AM43" s="1"/>
       <c r="AN43" s="1"/>
       <c r="AO43" s="1"/>
@@ -6025,7 +6156,7 @@
         <v>336</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-16</v>
       </c>
       <c r="M44" s="1"/>
@@ -6041,11 +6172,11 @@
         <v>231</v>
       </c>
       <c r="R44" s="5">
-        <f t="shared" ref="R44:R62" si="22">14*P44-O44-F44</f>
+        <f t="shared" ref="R44:R62" si="23">14*P44-O44-F44</f>
         <v>231</v>
       </c>
-      <c r="S44" s="5">
-        <f t="shared" si="13"/>
+      <c r="S44" s="28">
+        <f t="shared" si="14"/>
         <v>192</v>
       </c>
       <c r="T44" s="5"/>
@@ -6075,18 +6206,18 @@
       </c>
       <c r="AC44" s="1"/>
       <c r="AD44" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>92.4</v>
       </c>
       <c r="AE44" s="10">
         <v>16</v>
       </c>
       <c r="AF44" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
       <c r="AG44" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>76.800000000000011</v>
       </c>
       <c r="AH44" s="1">
@@ -6096,11 +6227,14 @@
         <v>84</v>
       </c>
       <c r="AJ44" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="AK44" s="1"/>
-      <c r="AL44" s="1"/>
+      <c r="AL44" s="1">
+        <f t="shared" si="11"/>
+        <v>25.6</v>
+      </c>
       <c r="AM44" s="1"/>
       <c r="AN44" s="1"/>
       <c r="AO44" s="1"/>
@@ -6151,7 +6285,7 @@
         <v>792</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-54</v>
       </c>
       <c r="M45" s="1"/>
@@ -6167,11 +6301,11 @@
         <v>341.40000000000009</v>
       </c>
       <c r="R45" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>341.40000000000009</v>
       </c>
-      <c r="S45" s="5">
-        <f t="shared" si="13"/>
+      <c r="S45" s="28">
+        <f t="shared" si="14"/>
         <v>360</v>
       </c>
       <c r="T45" s="5"/>
@@ -6203,18 +6337,18 @@
         <v>81</v>
       </c>
       <c r="AD45" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>238.98000000000005</v>
       </c>
       <c r="AE45" s="10">
         <v>10</v>
       </c>
       <c r="AF45" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>36</v>
       </c>
       <c r="AG45" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>251.99999999999997</v>
       </c>
       <c r="AH45" s="1">
@@ -6224,11 +6358,14 @@
         <v>84</v>
       </c>
       <c r="AJ45" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="AK45" s="1"/>
-      <c r="AL45" s="1"/>
+      <c r="AL45" s="1">
+        <f t="shared" si="11"/>
+        <v>103.32</v>
+      </c>
       <c r="AM45" s="1"/>
       <c r="AN45" s="1"/>
       <c r="AO45" s="1"/>
@@ -6277,7 +6414,7 @@
         <v>251</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>8</v>
       </c>
       <c r="M46" s="1"/>
@@ -6291,8 +6428,8 @@
       </c>
       <c r="Q46" s="5"/>
       <c r="R46" s="5"/>
-      <c r="S46" s="5">
-        <f t="shared" si="13"/>
+      <c r="S46" s="28">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T46" s="5"/>
@@ -6322,20 +6459,20 @@
       </c>
       <c r="AC46" s="1"/>
       <c r="AD46" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE46" s="10">
         <v>10</v>
       </c>
       <c r="AF46" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AG46" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
+      <c r="AG46" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="AH46" s="1">
         <v>12</v>
       </c>
@@ -6343,11 +6480,14 @@
         <v>84</v>
       </c>
       <c r="AJ46" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AK46" s="1"/>
-      <c r="AL46" s="1"/>
+      <c r="AL46" s="1">
+        <f t="shared" si="11"/>
+        <v>36.26</v>
+      </c>
       <c r="AM46" s="1"/>
       <c r="AN46" s="1"/>
       <c r="AO46" s="1"/>
@@ -6396,7 +6536,7 @@
         <v>213</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-41</v>
       </c>
       <c r="M47" s="1"/>
@@ -6410,11 +6550,11 @@
       </c>
       <c r="Q47" s="5"/>
       <c r="R47" s="5">
-        <f t="shared" ref="R47:R49" si="23">T47</f>
+        <f t="shared" ref="R47:R49" si="24">T47</f>
         <v>400</v>
       </c>
-      <c r="S47" s="5">
-        <f t="shared" si="13"/>
+      <c r="S47" s="28">
+        <f t="shared" si="14"/>
         <v>420</v>
       </c>
       <c r="T47" s="23">
@@ -6446,18 +6586,18 @@
       </c>
       <c r="AC47" s="1"/>
       <c r="AD47" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>400</v>
       </c>
       <c r="AE47" s="10">
         <v>5</v>
       </c>
       <c r="AF47" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>84</v>
       </c>
       <c r="AG47" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>420</v>
       </c>
       <c r="AH47" s="1">
@@ -6467,11 +6607,14 @@
         <v>84</v>
       </c>
       <c r="AJ47" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="AK47" s="1"/>
-      <c r="AL47" s="1"/>
+      <c r="AL47" s="1">
+        <f t="shared" si="11"/>
+        <v>34.4</v>
+      </c>
       <c r="AM47" s="1"/>
       <c r="AN47" s="1"/>
       <c r="AO47" s="1"/>
@@ -6520,7 +6663,7 @@
         <v>234</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-42</v>
       </c>
       <c r="M48" s="1"/>
@@ -6536,11 +6679,11 @@
         <v>275.60000000000002</v>
       </c>
       <c r="R48" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>400</v>
       </c>
-      <c r="S48" s="5">
-        <f t="shared" si="13"/>
+      <c r="S48" s="28">
+        <f t="shared" si="14"/>
         <v>384</v>
       </c>
       <c r="T48" s="23">
@@ -6574,18 +6717,18 @@
         <v>76</v>
       </c>
       <c r="AD48" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>360</v>
       </c>
       <c r="AE48" s="10">
         <v>8</v>
       </c>
       <c r="AF48" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>48</v>
       </c>
       <c r="AG48" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>345.6</v>
       </c>
       <c r="AH48" s="1">
@@ -6595,11 +6738,14 @@
         <v>84</v>
       </c>
       <c r="AJ48" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="AK48" s="1"/>
-      <c r="AL48" s="1"/>
+      <c r="AL48" s="1">
+        <f t="shared" si="11"/>
+        <v>34.56</v>
+      </c>
       <c r="AM48" s="1"/>
       <c r="AN48" s="1"/>
       <c r="AO48" s="1"/>
@@ -6648,7 +6794,7 @@
         <v>171</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-46</v>
       </c>
       <c r="M49" s="1"/>
@@ -6662,11 +6808,11 @@
       </c>
       <c r="Q49" s="5"/>
       <c r="R49" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>300</v>
       </c>
-      <c r="S49" s="5">
-        <f t="shared" si="13"/>
+      <c r="S49" s="28">
+        <f t="shared" si="14"/>
         <v>288</v>
       </c>
       <c r="T49" s="23">
@@ -6700,18 +6846,18 @@
         <v>76</v>
       </c>
       <c r="AD49" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>270</v>
       </c>
       <c r="AE49" s="10">
         <v>8</v>
       </c>
       <c r="AF49" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>36</v>
       </c>
       <c r="AG49" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>259.2</v>
       </c>
       <c r="AH49" s="1">
@@ -6721,11 +6867,14 @@
         <v>84</v>
       </c>
       <c r="AJ49" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="AK49" s="1"/>
-      <c r="AL49" s="1"/>
+      <c r="AL49" s="1">
+        <f t="shared" si="11"/>
+        <v>22.5</v>
+      </c>
       <c r="AM49" s="1"/>
       <c r="AN49" s="1"/>
       <c r="AO49" s="1"/>
@@ -6774,7 +6923,7 @@
         <v>342</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-62</v>
       </c>
       <c r="M50" s="1"/>
@@ -6793,8 +6942,8 @@
         <f>Q50*$R$1</f>
         <v>707.2</v>
       </c>
-      <c r="S50" s="5">
-        <f t="shared" si="13"/>
+      <c r="S50" s="28">
+        <f t="shared" si="14"/>
         <v>720</v>
       </c>
       <c r="T50" s="5"/>
@@ -6826,18 +6975,18 @@
         <v>76</v>
       </c>
       <c r="AD50" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>707.2</v>
       </c>
       <c r="AE50" s="10">
         <v>6</v>
       </c>
       <c r="AF50" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>120</v>
       </c>
       <c r="AG50" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>720</v>
       </c>
       <c r="AH50" s="1">
@@ -6847,11 +6996,14 @@
         <v>84</v>
       </c>
       <c r="AJ50" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1.4285714285714286</v>
       </c>
       <c r="AK50" s="1"/>
-      <c r="AL50" s="1"/>
+      <c r="AL50" s="1">
+        <f t="shared" si="11"/>
+        <v>56</v>
+      </c>
       <c r="AM50" s="1"/>
       <c r="AN50" s="1"/>
       <c r="AO50" s="1"/>
@@ -6898,7 +7050,7 @@
         <v>7.4</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M51" s="1"/>
@@ -6912,8 +7064,8 @@
       </c>
       <c r="Q51" s="5"/>
       <c r="R51" s="5"/>
-      <c r="S51" s="5">
-        <f t="shared" si="13"/>
+      <c r="S51" s="28">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T51" s="5"/>
@@ -6945,20 +7097,20 @@
         <v>163</v>
       </c>
       <c r="AD51" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE51" s="10">
         <v>3.7</v>
       </c>
       <c r="AF51" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AG51" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
+      <c r="AG51" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="AH51" s="1">
         <v>14</v>
       </c>
@@ -6966,11 +7118,14 @@
         <v>126</v>
       </c>
       <c r="AJ51" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AK51" s="1"/>
-      <c r="AL51" s="1"/>
+      <c r="AL51" s="1">
+        <f t="shared" si="11"/>
+        <v>1.48</v>
+      </c>
       <c r="AM51" s="1"/>
       <c r="AN51" s="1"/>
       <c r="AO51" s="1"/>
@@ -7019,7 +7174,7 @@
         <v>113</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-44</v>
       </c>
       <c r="M52" s="1"/>
@@ -7033,11 +7188,11 @@
       </c>
       <c r="Q52" s="5"/>
       <c r="R52" s="5">
-        <f t="shared" ref="R52:R53" si="24">T52</f>
+        <f t="shared" ref="R52:R53" si="25">T52</f>
         <v>350</v>
       </c>
-      <c r="S52" s="5">
-        <f t="shared" si="13"/>
+      <c r="S52" s="28">
+        <f t="shared" si="14"/>
         <v>392</v>
       </c>
       <c r="T52" s="23">
@@ -7069,18 +7224,18 @@
       </c>
       <c r="AC52" s="1"/>
       <c r="AD52" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>80.5</v>
       </c>
       <c r="AE52" s="10">
         <v>7</v>
       </c>
       <c r="AF52" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>56</v>
       </c>
       <c r="AG52" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>90.160000000000011</v>
       </c>
       <c r="AH52" s="1">
@@ -7090,11 +7245,14 @@
         <v>140</v>
       </c>
       <c r="AJ52" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.4</v>
       </c>
       <c r="AK52" s="1"/>
-      <c r="AL52" s="1"/>
+      <c r="AL52" s="1">
+        <f t="shared" si="11"/>
+        <v>3.1740000000000004</v>
+      </c>
       <c r="AM52" s="1"/>
       <c r="AN52" s="1"/>
       <c r="AO52" s="1"/>
@@ -7143,7 +7301,7 @@
         <v>306</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="M53" s="1"/>
@@ -7159,11 +7317,11 @@
         <v>529.79999999999995</v>
       </c>
       <c r="R53" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>600</v>
       </c>
-      <c r="S53" s="5">
-        <f t="shared" si="13"/>
+      <c r="S53" s="28">
+        <f t="shared" si="14"/>
         <v>672</v>
       </c>
       <c r="T53" s="23">
@@ -7197,18 +7355,18 @@
         <v>81</v>
       </c>
       <c r="AD53" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>150</v>
       </c>
       <c r="AE53" s="10">
         <v>12</v>
       </c>
       <c r="AF53" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>56</v>
       </c>
       <c r="AG53" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>168</v>
       </c>
       <c r="AH53" s="1">
@@ -7218,11 +7376,14 @@
         <v>70</v>
       </c>
       <c r="AJ53" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.8</v>
       </c>
       <c r="AK53" s="1"/>
-      <c r="AL53" s="1"/>
+      <c r="AL53" s="1">
+        <f t="shared" si="11"/>
+        <v>15.35</v>
+      </c>
       <c r="AM53" s="1"/>
       <c r="AN53" s="1"/>
       <c r="AO53" s="1"/>
@@ -7271,7 +7432,7 @@
         <v>156</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-1</v>
       </c>
       <c r="M54" s="1"/>
@@ -7285,8 +7446,8 @@
       </c>
       <c r="Q54" s="5"/>
       <c r="R54" s="5"/>
-      <c r="S54" s="5">
-        <f t="shared" si="13"/>
+      <c r="S54" s="28">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T54" s="5"/>
@@ -7316,20 +7477,20 @@
       </c>
       <c r="AC54" s="1"/>
       <c r="AD54" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE54" s="10">
         <v>12</v>
       </c>
       <c r="AF54" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AG54" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
+      <c r="AG54" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="AH54" s="1">
         <v>14</v>
       </c>
@@ -7337,11 +7498,14 @@
         <v>70</v>
       </c>
       <c r="AJ54" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AK54" s="1"/>
-      <c r="AL54" s="1"/>
+      <c r="AL54" s="1">
+        <f t="shared" si="11"/>
+        <v>7.75</v>
+      </c>
       <c r="AM54" s="1"/>
       <c r="AN54" s="1"/>
       <c r="AO54" s="1"/>
@@ -7388,7 +7552,7 @@
         <v>5</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M55" s="1"/>
@@ -7402,8 +7566,8 @@
       </c>
       <c r="Q55" s="5"/>
       <c r="R55" s="5"/>
-      <c r="S55" s="5">
-        <f t="shared" si="13"/>
+      <c r="S55" s="28">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T55" s="5"/>
@@ -7435,20 +7599,20 @@
         <v>163</v>
       </c>
       <c r="AD55" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE55" s="10">
         <v>6</v>
       </c>
       <c r="AF55" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AG55" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
+      <c r="AG55" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="AH55" s="1">
         <v>14</v>
       </c>
@@ -7456,11 +7620,14 @@
         <v>140</v>
       </c>
       <c r="AJ55" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AK55" s="1"/>
-      <c r="AL55" s="1"/>
+      <c r="AL55" s="1">
+        <f t="shared" si="11"/>
+        <v>0.18</v>
+      </c>
       <c r="AM55" s="1"/>
       <c r="AN55" s="1"/>
       <c r="AO55" s="1"/>
@@ -7507,7 +7674,7 @@
         <v>5</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M56" s="1"/>
@@ -7521,8 +7688,8 @@
       </c>
       <c r="Q56" s="5"/>
       <c r="R56" s="5"/>
-      <c r="S56" s="5">
-        <f t="shared" si="13"/>
+      <c r="S56" s="28">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T56" s="5"/>
@@ -7554,20 +7721,20 @@
         <v>163</v>
       </c>
       <c r="AD56" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE56" s="10">
         <v>6</v>
       </c>
       <c r="AF56" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AG56" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
+      <c r="AG56" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="AH56" s="1">
         <v>14</v>
       </c>
@@ -7575,11 +7742,14 @@
         <v>140</v>
       </c>
       <c r="AJ56" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AK56" s="1"/>
-      <c r="AL56" s="1"/>
+      <c r="AL56" s="1">
+        <f t="shared" si="11"/>
+        <v>0.18</v>
+      </c>
       <c r="AM56" s="1"/>
       <c r="AN56" s="1"/>
       <c r="AO56" s="1"/>
@@ -7626,7 +7796,7 @@
         <v>6</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M57" s="1"/>
@@ -7640,8 +7810,8 @@
       </c>
       <c r="Q57" s="5"/>
       <c r="R57" s="5"/>
-      <c r="S57" s="5">
-        <f t="shared" si="13"/>
+      <c r="S57" s="28">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T57" s="5"/>
@@ -7671,20 +7841,20 @@
       </c>
       <c r="AC57" s="1"/>
       <c r="AD57" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE57" s="10">
         <v>6</v>
       </c>
       <c r="AF57" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AG57" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
+      <c r="AG57" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="AH57" s="1">
         <v>14</v>
       </c>
@@ -7692,11 +7862,14 @@
         <v>140</v>
       </c>
       <c r="AJ57" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AK57" s="1"/>
-      <c r="AL57" s="1"/>
+      <c r="AL57" s="1">
+        <f t="shared" si="11"/>
+        <v>0.216</v>
+      </c>
       <c r="AM57" s="1"/>
       <c r="AN57" s="1"/>
       <c r="AO57" s="1"/>
@@ -7745,7 +7918,7 @@
         <v>90</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M58" s="1"/>
@@ -7759,8 +7932,8 @@
       </c>
       <c r="Q58" s="5"/>
       <c r="R58" s="5"/>
-      <c r="S58" s="5">
-        <f t="shared" si="13"/>
+      <c r="S58" s="28">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T58" s="5"/>
@@ -7790,20 +7963,20 @@
       </c>
       <c r="AC58" s="1"/>
       <c r="AD58" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE58" s="10">
         <v>12</v>
       </c>
       <c r="AF58" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AG58" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
+      <c r="AG58" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="AH58" s="1">
         <v>14</v>
       </c>
@@ -7811,11 +7984,14 @@
         <v>70</v>
       </c>
       <c r="AJ58" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AK58" s="1"/>
-      <c r="AL58" s="1"/>
+      <c r="AL58" s="1">
+        <f t="shared" si="11"/>
+        <v>5.3999999999999995</v>
+      </c>
       <c r="AM58" s="1"/>
       <c r="AN58" s="1"/>
       <c r="AO58" s="1"/>
@@ -7864,7 +8040,7 @@
         <v>349</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2</v>
       </c>
       <c r="M59" s="1"/>
@@ -7878,8 +8054,8 @@
       </c>
       <c r="Q59" s="5"/>
       <c r="R59" s="5"/>
-      <c r="S59" s="5">
-        <f t="shared" si="13"/>
+      <c r="S59" s="28">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T59" s="5"/>
@@ -7909,20 +8085,20 @@
       </c>
       <c r="AC59" s="1"/>
       <c r="AD59" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE59" s="10">
         <v>12</v>
       </c>
       <c r="AF59" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AG59" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
+      <c r="AG59" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="AH59" s="1">
         <v>14</v>
       </c>
@@ -7930,11 +8106,14 @@
         <v>70</v>
       </c>
       <c r="AJ59" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AK59" s="1"/>
-      <c r="AL59" s="1"/>
+      <c r="AL59" s="1">
+        <f t="shared" si="11"/>
+        <v>21.06</v>
+      </c>
       <c r="AM59" s="1"/>
       <c r="AN59" s="1"/>
       <c r="AO59" s="1"/>
@@ -7981,7 +8160,7 @@
         <v>33</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="M60" s="1"/>
@@ -8000,8 +8179,8 @@
         <f>22*P60-O60-F60</f>
         <v>99.6</v>
       </c>
-      <c r="S60" s="5">
-        <f t="shared" si="13"/>
+      <c r="S60" s="28">
+        <f t="shared" si="14"/>
         <v>196</v>
       </c>
       <c r="T60" s="5"/>
@@ -8031,18 +8210,18 @@
       </c>
       <c r="AC60" s="1"/>
       <c r="AD60" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>29.879999999999995</v>
       </c>
       <c r="AE60" s="10">
         <v>14</v>
       </c>
       <c r="AF60" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>14</v>
       </c>
       <c r="AG60" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>58.8</v>
       </c>
       <c r="AH60" s="1">
@@ -8052,11 +8231,14 @@
         <v>70</v>
       </c>
       <c r="AJ60" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.2</v>
       </c>
       <c r="AK60" s="1"/>
-      <c r="AL60" s="1"/>
+      <c r="AL60" s="1">
+        <f t="shared" si="11"/>
+        <v>2.04</v>
+      </c>
       <c r="AM60" s="1"/>
       <c r="AN60" s="1"/>
       <c r="AO60" s="1"/>
@@ -8105,7 +8287,7 @@
         <v>545</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-11</v>
       </c>
       <c r="M61" s="1"/>
@@ -8119,8 +8301,8 @@
       </c>
       <c r="Q61" s="5"/>
       <c r="R61" s="5"/>
-      <c r="S61" s="5">
-        <f t="shared" si="13"/>
+      <c r="S61" s="28">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T61" s="5"/>
@@ -8150,20 +8332,20 @@
       </c>
       <c r="AC61" s="1"/>
       <c r="AD61" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE61" s="10">
         <v>12</v>
       </c>
       <c r="AF61" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AG61" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
+      <c r="AG61" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="AH61" s="1">
         <v>14</v>
       </c>
@@ -8171,11 +8353,14 @@
         <v>70</v>
       </c>
       <c r="AJ61" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AK61" s="1"/>
-      <c r="AL61" s="1"/>
+      <c r="AL61" s="1">
+        <f t="shared" si="11"/>
+        <v>26.7</v>
+      </c>
       <c r="AM61" s="1"/>
       <c r="AN61" s="1"/>
       <c r="AO61" s="1"/>
@@ -8226,7 +8411,7 @@
         <v>623</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6</v>
       </c>
       <c r="M62" s="1"/>
@@ -8242,11 +8427,11 @@
         <v>211.20000000000005</v>
       </c>
       <c r="R62" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>211.20000000000005</v>
       </c>
-      <c r="S62" s="5">
-        <f t="shared" si="13"/>
+      <c r="S62" s="28">
+        <f t="shared" si="14"/>
         <v>168</v>
       </c>
       <c r="T62" s="5"/>
@@ -8278,18 +8463,18 @@
         <v>76</v>
       </c>
       <c r="AD62" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>52.800000000000011</v>
       </c>
       <c r="AE62" s="10">
         <v>12</v>
       </c>
       <c r="AF62" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>14</v>
       </c>
       <c r="AG62" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>42</v>
       </c>
       <c r="AH62" s="1">
@@ -8299,11 +8484,14 @@
         <v>70</v>
       </c>
       <c r="AJ62" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.2</v>
       </c>
       <c r="AK62" s="1"/>
-      <c r="AL62" s="1"/>
+      <c r="AL62" s="1">
+        <f t="shared" si="11"/>
+        <v>31.45</v>
+      </c>
       <c r="AM62" s="1"/>
       <c r="AN62" s="1"/>
       <c r="AO62" s="1"/>
@@ -8352,7 +8540,7 @@
         <v>89</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-4</v>
       </c>
       <c r="M63" s="1"/>
@@ -8366,8 +8554,8 @@
       </c>
       <c r="Q63" s="5"/>
       <c r="R63" s="5"/>
-      <c r="S63" s="5">
-        <f t="shared" si="13"/>
+      <c r="S63" s="28">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T63" s="5"/>
@@ -8397,20 +8585,20 @@
       </c>
       <c r="AC63" s="1"/>
       <c r="AD63" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE63" s="10">
         <v>6</v>
       </c>
       <c r="AF63" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AG63" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
+      <c r="AG63" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="AH63" s="1">
         <v>14</v>
       </c>
@@ -8418,11 +8606,14 @@
         <v>140</v>
       </c>
       <c r="AJ63" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AK63" s="1"/>
-      <c r="AL63" s="1"/>
+      <c r="AL63" s="1">
+        <f t="shared" si="11"/>
+        <v>3.4000000000000004</v>
+      </c>
       <c r="AM63" s="1"/>
       <c r="AN63" s="1"/>
       <c r="AO63" s="1"/>
@@ -8471,7 +8662,7 @@
         <v>134</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-10</v>
       </c>
       <c r="M64" s="1"/>
@@ -8485,8 +8676,8 @@
       </c>
       <c r="Q64" s="5"/>
       <c r="R64" s="5"/>
-      <c r="S64" s="5">
-        <f t="shared" si="13"/>
+      <c r="S64" s="28">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T64" s="5"/>
@@ -8516,20 +8707,20 @@
       </c>
       <c r="AC64" s="1"/>
       <c r="AD64" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE64" s="10">
         <v>6</v>
       </c>
       <c r="AF64" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AG64" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
+      <c r="AG64" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="AH64" s="1">
         <v>14</v>
       </c>
@@ -8537,11 +8728,14 @@
         <v>140</v>
       </c>
       <c r="AJ64" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AK64" s="1"/>
-      <c r="AL64" s="1"/>
+      <c r="AL64" s="1">
+        <f t="shared" si="11"/>
+        <v>5.7040000000000006</v>
+      </c>
       <c r="AM64" s="1"/>
       <c r="AN64" s="1"/>
       <c r="AO64" s="1"/>
@@ -8588,7 +8782,7 @@
         <v>61.9</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.20000000000000284</v>
       </c>
       <c r="M65" s="1"/>
@@ -8602,8 +8796,8 @@
       </c>
       <c r="Q65" s="5"/>
       <c r="R65" s="5"/>
-      <c r="S65" s="5">
-        <f t="shared" si="13"/>
+      <c r="S65" s="28">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T65" s="5"/>
@@ -8633,20 +8827,20 @@
       </c>
       <c r="AC65" s="1"/>
       <c r="AD65" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE65" s="10">
         <v>5</v>
       </c>
       <c r="AF65" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AG65" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
+      <c r="AG65" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="AH65" s="1">
         <v>12</v>
       </c>
@@ -8654,11 +8848,14 @@
         <v>84</v>
       </c>
       <c r="AJ65" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AK65" s="1"/>
-      <c r="AL65" s="1"/>
+      <c r="AL65" s="1">
+        <f t="shared" si="11"/>
+        <v>12.42</v>
+      </c>
       <c r="AM65" s="1"/>
       <c r="AN65" s="1"/>
       <c r="AO65" s="1"/>
@@ -8709,7 +8906,7 @@
         <v>350</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>190</v>
       </c>
       <c r="M66" s="1"/>
@@ -8728,8 +8925,8 @@
         <f>T66</f>
         <v>0</v>
       </c>
-      <c r="S66" s="5">
-        <f t="shared" si="13"/>
+      <c r="S66" s="28">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T66" s="23">
@@ -8761,20 +8958,20 @@
       </c>
       <c r="AC66" s="1"/>
       <c r="AD66" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE66" s="10">
         <v>5</v>
       </c>
       <c r="AF66" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AG66" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
+      <c r="AG66" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="AH66" s="1">
         <v>12</v>
       </c>
@@ -8782,11 +8979,14 @@
         <v>84</v>
       </c>
       <c r="AJ66" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AK66" s="1"/>
-      <c r="AL66" s="1"/>
+      <c r="AL66" s="1">
+        <f t="shared" si="11"/>
+        <v>108</v>
+      </c>
       <c r="AM66" s="1"/>
       <c r="AN66" s="1"/>
       <c r="AO66" s="1"/>
@@ -8833,7 +9033,7 @@
         <v>195</v>
       </c>
       <c r="L67" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M67" s="15"/>
@@ -8845,7 +9045,7 @@
       </c>
       <c r="Q67" s="18"/>
       <c r="R67" s="18"/>
-      <c r="S67" s="18"/>
+      <c r="S67" s="27"/>
       <c r="T67" s="18"/>
       <c r="U67" s="15"/>
       <c r="V67" s="15">
@@ -8905,7 +9105,7 @@
       <c r="P68" s="1"/>
       <c r="Q68" s="1"/>
       <c r="R68" s="1"/>
-      <c r="S68" s="1"/>
+      <c r="S68" s="25"/>
       <c r="T68" s="1"/>
       <c r="U68" s="1"/>
       <c r="V68" s="1"/>
@@ -8959,7 +9159,7 @@
       <c r="P69" s="1"/>
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
-      <c r="S69" s="1"/>
+      <c r="S69" s="25"/>
       <c r="T69" s="1"/>
       <c r="U69" s="1"/>
       <c r="V69" s="1"/>
@@ -9013,7 +9213,7 @@
       <c r="P70" s="1"/>
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
-      <c r="S70" s="1"/>
+      <c r="S70" s="25"/>
       <c r="T70" s="1"/>
       <c r="U70" s="1"/>
       <c r="V70" s="1"/>
@@ -9067,7 +9267,7 @@
       <c r="P71" s="1"/>
       <c r="Q71" s="1"/>
       <c r="R71" s="1"/>
-      <c r="S71" s="1"/>
+      <c r="S71" s="25"/>
       <c r="T71" s="1"/>
       <c r="U71" s="1"/>
       <c r="V71" s="1"/>
@@ -9121,7 +9321,7 @@
       <c r="P72" s="1"/>
       <c r="Q72" s="1"/>
       <c r="R72" s="1"/>
-      <c r="S72" s="1"/>
+      <c r="S72" s="25"/>
       <c r="T72" s="1"/>
       <c r="U72" s="1"/>
       <c r="V72" s="1"/>
@@ -9175,7 +9375,7 @@
       <c r="P73" s="1"/>
       <c r="Q73" s="1"/>
       <c r="R73" s="1"/>
-      <c r="S73" s="1"/>
+      <c r="S73" s="25"/>
       <c r="T73" s="1"/>
       <c r="U73" s="1"/>
       <c r="V73" s="1"/>
@@ -9229,7 +9429,7 @@
       <c r="P74" s="1"/>
       <c r="Q74" s="1"/>
       <c r="R74" s="1"/>
-      <c r="S74" s="1"/>
+      <c r="S74" s="25"/>
       <c r="T74" s="1"/>
       <c r="U74" s="1"/>
       <c r="V74" s="1"/>
@@ -9283,7 +9483,7 @@
       <c r="P75" s="1"/>
       <c r="Q75" s="1"/>
       <c r="R75" s="1"/>
-      <c r="S75" s="1"/>
+      <c r="S75" s="25"/>
       <c r="T75" s="1"/>
       <c r="U75" s="1"/>
       <c r="V75" s="1"/>
@@ -9337,7 +9537,7 @@
       <c r="P76" s="1"/>
       <c r="Q76" s="1"/>
       <c r="R76" s="1"/>
-      <c r="S76" s="1"/>
+      <c r="S76" s="25"/>
       <c r="T76" s="1"/>
       <c r="U76" s="1"/>
       <c r="V76" s="1"/>
@@ -9391,7 +9591,7 @@
       <c r="P77" s="1"/>
       <c r="Q77" s="1"/>
       <c r="R77" s="1"/>
-      <c r="S77" s="1"/>
+      <c r="S77" s="25"/>
       <c r="T77" s="1"/>
       <c r="U77" s="1"/>
       <c r="V77" s="1"/>
@@ -9445,7 +9645,7 @@
       <c r="P78" s="1"/>
       <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
-      <c r="S78" s="1"/>
+      <c r="S78" s="25"/>
       <c r="T78" s="1"/>
       <c r="U78" s="1"/>
       <c r="V78" s="1"/>
@@ -9499,7 +9699,7 @@
       <c r="P79" s="1"/>
       <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
-      <c r="S79" s="1"/>
+      <c r="S79" s="25"/>
       <c r="T79" s="1"/>
       <c r="U79" s="1"/>
       <c r="V79" s="1"/>
@@ -9553,7 +9753,7 @@
       <c r="P80" s="1"/>
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
-      <c r="S80" s="1"/>
+      <c r="S80" s="25"/>
       <c r="T80" s="1"/>
       <c r="U80" s="1"/>
       <c r="V80" s="1"/>
@@ -9607,7 +9807,7 @@
       <c r="P81" s="1"/>
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
-      <c r="S81" s="1"/>
+      <c r="S81" s="25"/>
       <c r="T81" s="1"/>
       <c r="U81" s="1"/>
       <c r="V81" s="1"/>
@@ -9661,7 +9861,7 @@
       <c r="P82" s="1"/>
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
-      <c r="S82" s="1"/>
+      <c r="S82" s="25"/>
       <c r="T82" s="1"/>
       <c r="U82" s="1"/>
       <c r="V82" s="1"/>
@@ -9715,7 +9915,7 @@
       <c r="P83" s="1"/>
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
-      <c r="S83" s="1"/>
+      <c r="S83" s="25"/>
       <c r="T83" s="1"/>
       <c r="U83" s="1"/>
       <c r="V83" s="1"/>
@@ -9769,7 +9969,7 @@
       <c r="P84" s="1"/>
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
-      <c r="S84" s="1"/>
+      <c r="S84" s="25"/>
       <c r="T84" s="1"/>
       <c r="U84" s="1"/>
       <c r="V84" s="1"/>
@@ -9823,7 +10023,7 @@
       <c r="P85" s="1"/>
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
-      <c r="S85" s="1"/>
+      <c r="S85" s="25"/>
       <c r="T85" s="1"/>
       <c r="U85" s="1"/>
       <c r="V85" s="1"/>
@@ -9877,7 +10077,7 @@
       <c r="P86" s="1"/>
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
-      <c r="S86" s="1"/>
+      <c r="S86" s="25"/>
       <c r="T86" s="1"/>
       <c r="U86" s="1"/>
       <c r="V86" s="1"/>
@@ -9931,7 +10131,7 @@
       <c r="P87" s="1"/>
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
-      <c r="S87" s="1"/>
+      <c r="S87" s="25"/>
       <c r="T87" s="1"/>
       <c r="U87" s="1"/>
       <c r="V87" s="1"/>
@@ -9985,7 +10185,7 @@
       <c r="P88" s="1"/>
       <c r="Q88" s="1"/>
       <c r="R88" s="1"/>
-      <c r="S88" s="1"/>
+      <c r="S88" s="25"/>
       <c r="T88" s="1"/>
       <c r="U88" s="1"/>
       <c r="V88" s="1"/>
@@ -10039,7 +10239,7 @@
       <c r="P89" s="1"/>
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
-      <c r="S89" s="1"/>
+      <c r="S89" s="25"/>
       <c r="T89" s="1"/>
       <c r="U89" s="1"/>
       <c r="V89" s="1"/>
@@ -10093,7 +10293,7 @@
       <c r="P90" s="1"/>
       <c r="Q90" s="1"/>
       <c r="R90" s="1"/>
-      <c r="S90" s="1"/>
+      <c r="S90" s="25"/>
       <c r="T90" s="1"/>
       <c r="U90" s="1"/>
       <c r="V90" s="1"/>
@@ -10147,7 +10347,7 @@
       <c r="P91" s="1"/>
       <c r="Q91" s="1"/>
       <c r="R91" s="1"/>
-      <c r="S91" s="1"/>
+      <c r="S91" s="25"/>
       <c r="T91" s="1"/>
       <c r="U91" s="1"/>
       <c r="V91" s="1"/>
@@ -10201,7 +10401,7 @@
       <c r="P92" s="1"/>
       <c r="Q92" s="1"/>
       <c r="R92" s="1"/>
-      <c r="S92" s="1"/>
+      <c r="S92" s="25"/>
       <c r="T92" s="1"/>
       <c r="U92" s="1"/>
       <c r="V92" s="1"/>
@@ -10255,7 +10455,7 @@
       <c r="P93" s="1"/>
       <c r="Q93" s="1"/>
       <c r="R93" s="1"/>
-      <c r="S93" s="1"/>
+      <c r="S93" s="25"/>
       <c r="T93" s="1"/>
       <c r="U93" s="1"/>
       <c r="V93" s="1"/>
@@ -10309,7 +10509,7 @@
       <c r="P94" s="1"/>
       <c r="Q94" s="1"/>
       <c r="R94" s="1"/>
-      <c r="S94" s="1"/>
+      <c r="S94" s="25"/>
       <c r="T94" s="1"/>
       <c r="U94" s="1"/>
       <c r="V94" s="1"/>
@@ -10363,7 +10563,7 @@
       <c r="P95" s="1"/>
       <c r="Q95" s="1"/>
       <c r="R95" s="1"/>
-      <c r="S95" s="1"/>
+      <c r="S95" s="25"/>
       <c r="T95" s="1"/>
       <c r="U95" s="1"/>
       <c r="V95" s="1"/>
@@ -10417,7 +10617,7 @@
       <c r="P96" s="1"/>
       <c r="Q96" s="1"/>
       <c r="R96" s="1"/>
-      <c r="S96" s="1"/>
+      <c r="S96" s="25"/>
       <c r="T96" s="1"/>
       <c r="U96" s="1"/>
       <c r="V96" s="1"/>
@@ -10471,7 +10671,7 @@
       <c r="P97" s="1"/>
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
-      <c r="S97" s="1"/>
+      <c r="S97" s="25"/>
       <c r="T97" s="1"/>
       <c r="U97" s="1"/>
       <c r="V97" s="1"/>
@@ -10525,7 +10725,7 @@
       <c r="P98" s="1"/>
       <c r="Q98" s="1"/>
       <c r="R98" s="1"/>
-      <c r="S98" s="1"/>
+      <c r="S98" s="25"/>
       <c r="T98" s="1"/>
       <c r="U98" s="1"/>
       <c r="V98" s="1"/>
@@ -10579,7 +10779,7 @@
       <c r="P99" s="1"/>
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
-      <c r="S99" s="1"/>
+      <c r="S99" s="25"/>
       <c r="T99" s="1"/>
       <c r="U99" s="1"/>
       <c r="V99" s="1"/>
@@ -10633,7 +10833,7 @@
       <c r="P100" s="1"/>
       <c r="Q100" s="1"/>
       <c r="R100" s="1"/>
-      <c r="S100" s="1"/>
+      <c r="S100" s="25"/>
       <c r="T100" s="1"/>
       <c r="U100" s="1"/>
       <c r="V100" s="1"/>
@@ -10687,7 +10887,7 @@
       <c r="P101" s="1"/>
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
-      <c r="S101" s="1"/>
+      <c r="S101" s="25"/>
       <c r="T101" s="1"/>
       <c r="U101" s="1"/>
       <c r="V101" s="1"/>
@@ -10741,7 +10941,7 @@
       <c r="P102" s="1"/>
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
-      <c r="S102" s="1"/>
+      <c r="S102" s="25"/>
       <c r="T102" s="1"/>
       <c r="U102" s="1"/>
       <c r="V102" s="1"/>
@@ -10795,7 +10995,7 @@
       <c r="P103" s="1"/>
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
-      <c r="S103" s="1"/>
+      <c r="S103" s="25"/>
       <c r="T103" s="1"/>
       <c r="U103" s="1"/>
       <c r="V103" s="1"/>
@@ -10849,7 +11049,7 @@
       <c r="P104" s="1"/>
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
-      <c r="S104" s="1"/>
+      <c r="S104" s="25"/>
       <c r="T104" s="1"/>
       <c r="U104" s="1"/>
       <c r="V104" s="1"/>
@@ -10903,7 +11103,7 @@
       <c r="P105" s="1"/>
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
-      <c r="S105" s="1"/>
+      <c r="S105" s="25"/>
       <c r="T105" s="1"/>
       <c r="U105" s="1"/>
       <c r="V105" s="1"/>
@@ -10957,7 +11157,7 @@
       <c r="P106" s="1"/>
       <c r="Q106" s="1"/>
       <c r="R106" s="1"/>
-      <c r="S106" s="1"/>
+      <c r="S106" s="25"/>
       <c r="T106" s="1"/>
       <c r="U106" s="1"/>
       <c r="V106" s="1"/>
@@ -11011,7 +11211,7 @@
       <c r="P107" s="1"/>
       <c r="Q107" s="1"/>
       <c r="R107" s="1"/>
-      <c r="S107" s="1"/>
+      <c r="S107" s="25"/>
       <c r="T107" s="1"/>
       <c r="U107" s="1"/>
       <c r="V107" s="1"/>
@@ -11065,7 +11265,7 @@
       <c r="P108" s="1"/>
       <c r="Q108" s="1"/>
       <c r="R108" s="1"/>
-      <c r="S108" s="1"/>
+      <c r="S108" s="25"/>
       <c r="T108" s="1"/>
       <c r="U108" s="1"/>
       <c r="V108" s="1"/>
@@ -11119,7 +11319,7 @@
       <c r="P109" s="1"/>
       <c r="Q109" s="1"/>
       <c r="R109" s="1"/>
-      <c r="S109" s="1"/>
+      <c r="S109" s="25"/>
       <c r="T109" s="1"/>
       <c r="U109" s="1"/>
       <c r="V109" s="1"/>
@@ -11173,7 +11373,7 @@
       <c r="P110" s="1"/>
       <c r="Q110" s="1"/>
       <c r="R110" s="1"/>
-      <c r="S110" s="1"/>
+      <c r="S110" s="25"/>
       <c r="T110" s="1"/>
       <c r="U110" s="1"/>
       <c r="V110" s="1"/>
@@ -11227,7 +11427,7 @@
       <c r="P111" s="1"/>
       <c r="Q111" s="1"/>
       <c r="R111" s="1"/>
-      <c r="S111" s="1"/>
+      <c r="S111" s="25"/>
       <c r="T111" s="1"/>
       <c r="U111" s="1"/>
       <c r="V111" s="1"/>
@@ -11281,7 +11481,7 @@
       <c r="P112" s="1"/>
       <c r="Q112" s="1"/>
       <c r="R112" s="1"/>
-      <c r="S112" s="1"/>
+      <c r="S112" s="25"/>
       <c r="T112" s="1"/>
       <c r="U112" s="1"/>
       <c r="V112" s="1"/>
@@ -11335,7 +11535,7 @@
       <c r="P113" s="1"/>
       <c r="Q113" s="1"/>
       <c r="R113" s="1"/>
-      <c r="S113" s="1"/>
+      <c r="S113" s="25"/>
       <c r="T113" s="1"/>
       <c r="U113" s="1"/>
       <c r="V113" s="1"/>
@@ -11389,7 +11589,7 @@
       <c r="P114" s="1"/>
       <c r="Q114" s="1"/>
       <c r="R114" s="1"/>
-      <c r="S114" s="1"/>
+      <c r="S114" s="25"/>
       <c r="T114" s="1"/>
       <c r="U114" s="1"/>
       <c r="V114" s="1"/>
@@ -11443,7 +11643,7 @@
       <c r="P115" s="1"/>
       <c r="Q115" s="1"/>
       <c r="R115" s="1"/>
-      <c r="S115" s="1"/>
+      <c r="S115" s="25"/>
       <c r="T115" s="1"/>
       <c r="U115" s="1"/>
       <c r="V115" s="1"/>
@@ -11497,7 +11697,7 @@
       <c r="P116" s="1"/>
       <c r="Q116" s="1"/>
       <c r="R116" s="1"/>
-      <c r="S116" s="1"/>
+      <c r="S116" s="25"/>
       <c r="T116" s="1"/>
       <c r="U116" s="1"/>
       <c r="V116" s="1"/>
@@ -11551,7 +11751,7 @@
       <c r="P117" s="1"/>
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
-      <c r="S117" s="1"/>
+      <c r="S117" s="25"/>
       <c r="T117" s="1"/>
       <c r="U117" s="1"/>
       <c r="V117" s="1"/>
@@ -11605,7 +11805,7 @@
       <c r="P118" s="1"/>
       <c r="Q118" s="1"/>
       <c r="R118" s="1"/>
-      <c r="S118" s="1"/>
+      <c r="S118" s="25"/>
       <c r="T118" s="1"/>
       <c r="U118" s="1"/>
       <c r="V118" s="1"/>
@@ -11659,7 +11859,7 @@
       <c r="P119" s="1"/>
       <c r="Q119" s="1"/>
       <c r="R119" s="1"/>
-      <c r="S119" s="1"/>
+      <c r="S119" s="25"/>
       <c r="T119" s="1"/>
       <c r="U119" s="1"/>
       <c r="V119" s="1"/>
@@ -11713,7 +11913,7 @@
       <c r="P120" s="1"/>
       <c r="Q120" s="1"/>
       <c r="R120" s="1"/>
-      <c r="S120" s="1"/>
+      <c r="S120" s="25"/>
       <c r="T120" s="1"/>
       <c r="U120" s="1"/>
       <c r="V120" s="1"/>
@@ -11767,7 +11967,7 @@
       <c r="P121" s="1"/>
       <c r="Q121" s="1"/>
       <c r="R121" s="1"/>
-      <c r="S121" s="1"/>
+      <c r="S121" s="25"/>
       <c r="T121" s="1"/>
       <c r="U121" s="1"/>
       <c r="V121" s="1"/>
@@ -11821,7 +12021,7 @@
       <c r="P122" s="1"/>
       <c r="Q122" s="1"/>
       <c r="R122" s="1"/>
-      <c r="S122" s="1"/>
+      <c r="S122" s="25"/>
       <c r="T122" s="1"/>
       <c r="U122" s="1"/>
       <c r="V122" s="1"/>
@@ -11875,7 +12075,7 @@
       <c r="P123" s="1"/>
       <c r="Q123" s="1"/>
       <c r="R123" s="1"/>
-      <c r="S123" s="1"/>
+      <c r="S123" s="25"/>
       <c r="T123" s="1"/>
       <c r="U123" s="1"/>
       <c r="V123" s="1"/>
@@ -11929,7 +12129,7 @@
       <c r="P124" s="1"/>
       <c r="Q124" s="1"/>
       <c r="R124" s="1"/>
-      <c r="S124" s="1"/>
+      <c r="S124" s="25"/>
       <c r="T124" s="1"/>
       <c r="U124" s="1"/>
       <c r="V124" s="1"/>
@@ -11983,7 +12183,7 @@
       <c r="P125" s="1"/>
       <c r="Q125" s="1"/>
       <c r="R125" s="1"/>
-      <c r="S125" s="1"/>
+      <c r="S125" s="25"/>
       <c r="T125" s="1"/>
       <c r="U125" s="1"/>
       <c r="V125" s="1"/>
@@ -12037,7 +12237,7 @@
       <c r="P126" s="1"/>
       <c r="Q126" s="1"/>
       <c r="R126" s="1"/>
-      <c r="S126" s="1"/>
+      <c r="S126" s="25"/>
       <c r="T126" s="1"/>
       <c r="U126" s="1"/>
       <c r="V126" s="1"/>
@@ -12091,7 +12291,7 @@
       <c r="P127" s="1"/>
       <c r="Q127" s="1"/>
       <c r="R127" s="1"/>
-      <c r="S127" s="1"/>
+      <c r="S127" s="25"/>
       <c r="T127" s="1"/>
       <c r="U127" s="1"/>
       <c r="V127" s="1"/>
@@ -12145,7 +12345,7 @@
       <c r="P128" s="1"/>
       <c r="Q128" s="1"/>
       <c r="R128" s="1"/>
-      <c r="S128" s="1"/>
+      <c r="S128" s="25"/>
       <c r="T128" s="1"/>
       <c r="U128" s="1"/>
       <c r="V128" s="1"/>
@@ -12199,7 +12399,7 @@
       <c r="P129" s="1"/>
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
-      <c r="S129" s="1"/>
+      <c r="S129" s="25"/>
       <c r="T129" s="1"/>
       <c r="U129" s="1"/>
       <c r="V129" s="1"/>
@@ -12253,7 +12453,7 @@
       <c r="P130" s="1"/>
       <c r="Q130" s="1"/>
       <c r="R130" s="1"/>
-      <c r="S130" s="1"/>
+      <c r="S130" s="25"/>
       <c r="T130" s="1"/>
       <c r="U130" s="1"/>
       <c r="V130" s="1"/>
@@ -12307,7 +12507,7 @@
       <c r="P131" s="1"/>
       <c r="Q131" s="1"/>
       <c r="R131" s="1"/>
-      <c r="S131" s="1"/>
+      <c r="S131" s="25"/>
       <c r="T131" s="1"/>
       <c r="U131" s="1"/>
       <c r="V131" s="1"/>
@@ -12361,7 +12561,7 @@
       <c r="P132" s="1"/>
       <c r="Q132" s="1"/>
       <c r="R132" s="1"/>
-      <c r="S132" s="1"/>
+      <c r="S132" s="25"/>
       <c r="T132" s="1"/>
       <c r="U132" s="1"/>
       <c r="V132" s="1"/>
@@ -12415,7 +12615,7 @@
       <c r="P133" s="1"/>
       <c r="Q133" s="1"/>
       <c r="R133" s="1"/>
-      <c r="S133" s="1"/>
+      <c r="S133" s="25"/>
       <c r="T133" s="1"/>
       <c r="U133" s="1"/>
       <c r="V133" s="1"/>
@@ -12469,7 +12669,7 @@
       <c r="P134" s="1"/>
       <c r="Q134" s="1"/>
       <c r="R134" s="1"/>
-      <c r="S134" s="1"/>
+      <c r="S134" s="25"/>
       <c r="T134" s="1"/>
       <c r="U134" s="1"/>
       <c r="V134" s="1"/>
@@ -12523,7 +12723,7 @@
       <c r="P135" s="1"/>
       <c r="Q135" s="1"/>
       <c r="R135" s="1"/>
-      <c r="S135" s="1"/>
+      <c r="S135" s="25"/>
       <c r="T135" s="1"/>
       <c r="U135" s="1"/>
       <c r="V135" s="1"/>
@@ -12577,7 +12777,7 @@
       <c r="P136" s="1"/>
       <c r="Q136" s="1"/>
       <c r="R136" s="1"/>
-      <c r="S136" s="1"/>
+      <c r="S136" s="25"/>
       <c r="T136" s="1"/>
       <c r="U136" s="1"/>
       <c r="V136" s="1"/>
@@ -12631,7 +12831,7 @@
       <c r="P137" s="1"/>
       <c r="Q137" s="1"/>
       <c r="R137" s="1"/>
-      <c r="S137" s="1"/>
+      <c r="S137" s="25"/>
       <c r="T137" s="1"/>
       <c r="U137" s="1"/>
       <c r="V137" s="1"/>
@@ -12685,7 +12885,7 @@
       <c r="P138" s="1"/>
       <c r="Q138" s="1"/>
       <c r="R138" s="1"/>
-      <c r="S138" s="1"/>
+      <c r="S138" s="25"/>
       <c r="T138" s="1"/>
       <c r="U138" s="1"/>
       <c r="V138" s="1"/>
@@ -12739,7 +12939,7 @@
       <c r="P139" s="1"/>
       <c r="Q139" s="1"/>
       <c r="R139" s="1"/>
-      <c r="S139" s="1"/>
+      <c r="S139" s="25"/>
       <c r="T139" s="1"/>
       <c r="U139" s="1"/>
       <c r="V139" s="1"/>
@@ -12793,7 +12993,7 @@
       <c r="P140" s="1"/>
       <c r="Q140" s="1"/>
       <c r="R140" s="1"/>
-      <c r="S140" s="1"/>
+      <c r="S140" s="25"/>
       <c r="T140" s="1"/>
       <c r="U140" s="1"/>
       <c r="V140" s="1"/>
@@ -12847,7 +13047,7 @@
       <c r="P141" s="1"/>
       <c r="Q141" s="1"/>
       <c r="R141" s="1"/>
-      <c r="S141" s="1"/>
+      <c r="S141" s="25"/>
       <c r="T141" s="1"/>
       <c r="U141" s="1"/>
       <c r="V141" s="1"/>
@@ -12901,7 +13101,7 @@
       <c r="P142" s="1"/>
       <c r="Q142" s="1"/>
       <c r="R142" s="1"/>
-      <c r="S142" s="1"/>
+      <c r="S142" s="25"/>
       <c r="T142" s="1"/>
       <c r="U142" s="1"/>
       <c r="V142" s="1"/>
@@ -12955,7 +13155,7 @@
       <c r="P143" s="1"/>
       <c r="Q143" s="1"/>
       <c r="R143" s="1"/>
-      <c r="S143" s="1"/>
+      <c r="S143" s="25"/>
       <c r="T143" s="1"/>
       <c r="U143" s="1"/>
       <c r="V143" s="1"/>
@@ -13009,7 +13209,7 @@
       <c r="P144" s="1"/>
       <c r="Q144" s="1"/>
       <c r="R144" s="1"/>
-      <c r="S144" s="1"/>
+      <c r="S144" s="25"/>
       <c r="T144" s="1"/>
       <c r="U144" s="1"/>
       <c r="V144" s="1"/>
@@ -13063,7 +13263,7 @@
       <c r="P145" s="1"/>
       <c r="Q145" s="1"/>
       <c r="R145" s="1"/>
-      <c r="S145" s="1"/>
+      <c r="S145" s="25"/>
       <c r="T145" s="1"/>
       <c r="U145" s="1"/>
       <c r="V145" s="1"/>
@@ -13117,7 +13317,7 @@
       <c r="P146" s="1"/>
       <c r="Q146" s="1"/>
       <c r="R146" s="1"/>
-      <c r="S146" s="1"/>
+      <c r="S146" s="25"/>
       <c r="T146" s="1"/>
       <c r="U146" s="1"/>
       <c r="V146" s="1"/>
@@ -13171,7 +13371,7 @@
       <c r="P147" s="1"/>
       <c r="Q147" s="1"/>
       <c r="R147" s="1"/>
-      <c r="S147" s="1"/>
+      <c r="S147" s="25"/>
       <c r="T147" s="1"/>
       <c r="U147" s="1"/>
       <c r="V147" s="1"/>
@@ -13225,7 +13425,7 @@
       <c r="P148" s="1"/>
       <c r="Q148" s="1"/>
       <c r="R148" s="1"/>
-      <c r="S148" s="1"/>
+      <c r="S148" s="25"/>
       <c r="T148" s="1"/>
       <c r="U148" s="1"/>
       <c r="V148" s="1"/>
@@ -13279,7 +13479,7 @@
       <c r="P149" s="1"/>
       <c r="Q149" s="1"/>
       <c r="R149" s="1"/>
-      <c r="S149" s="1"/>
+      <c r="S149" s="25"/>
       <c r="T149" s="1"/>
       <c r="U149" s="1"/>
       <c r="V149" s="1"/>
@@ -13333,7 +13533,7 @@
       <c r="P150" s="1"/>
       <c r="Q150" s="1"/>
       <c r="R150" s="1"/>
-      <c r="S150" s="1"/>
+      <c r="S150" s="25"/>
       <c r="T150" s="1"/>
       <c r="U150" s="1"/>
       <c r="V150" s="1"/>
@@ -13387,7 +13587,7 @@
       <c r="P151" s="1"/>
       <c r="Q151" s="1"/>
       <c r="R151" s="1"/>
-      <c r="S151" s="1"/>
+      <c r="S151" s="25"/>
       <c r="T151" s="1"/>
       <c r="U151" s="1"/>
       <c r="V151" s="1"/>
@@ -13441,7 +13641,7 @@
       <c r="P152" s="1"/>
       <c r="Q152" s="1"/>
       <c r="R152" s="1"/>
-      <c r="S152" s="1"/>
+      <c r="S152" s="25"/>
       <c r="T152" s="1"/>
       <c r="U152" s="1"/>
       <c r="V152" s="1"/>
@@ -13495,7 +13695,7 @@
       <c r="P153" s="1"/>
       <c r="Q153" s="1"/>
       <c r="R153" s="1"/>
-      <c r="S153" s="1"/>
+      <c r="S153" s="25"/>
       <c r="T153" s="1"/>
       <c r="U153" s="1"/>
       <c r="V153" s="1"/>
@@ -13549,7 +13749,7 @@
       <c r="P154" s="1"/>
       <c r="Q154" s="1"/>
       <c r="R154" s="1"/>
-      <c r="S154" s="1"/>
+      <c r="S154" s="25"/>
       <c r="T154" s="1"/>
       <c r="U154" s="1"/>
       <c r="V154" s="1"/>
@@ -13603,7 +13803,7 @@
       <c r="P155" s="1"/>
       <c r="Q155" s="1"/>
       <c r="R155" s="1"/>
-      <c r="S155" s="1"/>
+      <c r="S155" s="25"/>
       <c r="T155" s="1"/>
       <c r="U155" s="1"/>
       <c r="V155" s="1"/>
@@ -13657,7 +13857,7 @@
       <c r="P156" s="1"/>
       <c r="Q156" s="1"/>
       <c r="R156" s="1"/>
-      <c r="S156" s="1"/>
+      <c r="S156" s="25"/>
       <c r="T156" s="1"/>
       <c r="U156" s="1"/>
       <c r="V156" s="1"/>
@@ -13711,7 +13911,7 @@
       <c r="P157" s="1"/>
       <c r="Q157" s="1"/>
       <c r="R157" s="1"/>
-      <c r="S157" s="1"/>
+      <c r="S157" s="25"/>
       <c r="T157" s="1"/>
       <c r="U157" s="1"/>
       <c r="V157" s="1"/>
@@ -13765,7 +13965,7 @@
       <c r="P158" s="1"/>
       <c r="Q158" s="1"/>
       <c r="R158" s="1"/>
-      <c r="S158" s="1"/>
+      <c r="S158" s="25"/>
       <c r="T158" s="1"/>
       <c r="U158" s="1"/>
       <c r="V158" s="1"/>
@@ -13819,7 +14019,7 @@
       <c r="P159" s="1"/>
       <c r="Q159" s="1"/>
       <c r="R159" s="1"/>
-      <c r="S159" s="1"/>
+      <c r="S159" s="25"/>
       <c r="T159" s="1"/>
       <c r="U159" s="1"/>
       <c r="V159" s="1"/>
@@ -13873,7 +14073,7 @@
       <c r="P160" s="1"/>
       <c r="Q160" s="1"/>
       <c r="R160" s="1"/>
-      <c r="S160" s="1"/>
+      <c r="S160" s="25"/>
       <c r="T160" s="1"/>
       <c r="U160" s="1"/>
       <c r="V160" s="1"/>
@@ -13927,7 +14127,7 @@
       <c r="P161" s="1"/>
       <c r="Q161" s="1"/>
       <c r="R161" s="1"/>
-      <c r="S161" s="1"/>
+      <c r="S161" s="25"/>
       <c r="T161" s="1"/>
       <c r="U161" s="1"/>
       <c r="V161" s="1"/>
@@ -13981,7 +14181,7 @@
       <c r="P162" s="1"/>
       <c r="Q162" s="1"/>
       <c r="R162" s="1"/>
-      <c r="S162" s="1"/>
+      <c r="S162" s="25"/>
       <c r="T162" s="1"/>
       <c r="U162" s="1"/>
       <c r="V162" s="1"/>
@@ -14035,7 +14235,7 @@
       <c r="P163" s="1"/>
       <c r="Q163" s="1"/>
       <c r="R163" s="1"/>
-      <c r="S163" s="1"/>
+      <c r="S163" s="25"/>
       <c r="T163" s="1"/>
       <c r="U163" s="1"/>
       <c r="V163" s="1"/>
@@ -14089,7 +14289,7 @@
       <c r="P164" s="1"/>
       <c r="Q164" s="1"/>
       <c r="R164" s="1"/>
-      <c r="S164" s="1"/>
+      <c r="S164" s="25"/>
       <c r="T164" s="1"/>
       <c r="U164" s="1"/>
       <c r="V164" s="1"/>
@@ -14143,7 +14343,7 @@
       <c r="P165" s="1"/>
       <c r="Q165" s="1"/>
       <c r="R165" s="1"/>
-      <c r="S165" s="1"/>
+      <c r="S165" s="25"/>
       <c r="T165" s="1"/>
       <c r="U165" s="1"/>
       <c r="V165" s="1"/>
@@ -14197,7 +14397,7 @@
       <c r="P166" s="1"/>
       <c r="Q166" s="1"/>
       <c r="R166" s="1"/>
-      <c r="S166" s="1"/>
+      <c r="S166" s="25"/>
       <c r="T166" s="1"/>
       <c r="U166" s="1"/>
       <c r="V166" s="1"/>
@@ -14251,7 +14451,7 @@
       <c r="P167" s="1"/>
       <c r="Q167" s="1"/>
       <c r="R167" s="1"/>
-      <c r="S167" s="1"/>
+      <c r="S167" s="25"/>
       <c r="T167" s="1"/>
       <c r="U167" s="1"/>
       <c r="V167" s="1"/>
@@ -14305,7 +14505,7 @@
       <c r="P168" s="1"/>
       <c r="Q168" s="1"/>
       <c r="R168" s="1"/>
-      <c r="S168" s="1"/>
+      <c r="S168" s="25"/>
       <c r="T168" s="1"/>
       <c r="U168" s="1"/>
       <c r="V168" s="1"/>
@@ -14359,7 +14559,7 @@
       <c r="P169" s="1"/>
       <c r="Q169" s="1"/>
       <c r="R169" s="1"/>
-      <c r="S169" s="1"/>
+      <c r="S169" s="25"/>
       <c r="T169" s="1"/>
       <c r="U169" s="1"/>
       <c r="V169" s="1"/>
@@ -14413,7 +14613,7 @@
       <c r="P170" s="1"/>
       <c r="Q170" s="1"/>
       <c r="R170" s="1"/>
-      <c r="S170" s="1"/>
+      <c r="S170" s="25"/>
       <c r="T170" s="1"/>
       <c r="U170" s="1"/>
       <c r="V170" s="1"/>
@@ -14467,7 +14667,7 @@
       <c r="P171" s="1"/>
       <c r="Q171" s="1"/>
       <c r="R171" s="1"/>
-      <c r="S171" s="1"/>
+      <c r="S171" s="25"/>
       <c r="T171" s="1"/>
       <c r="U171" s="1"/>
       <c r="V171" s="1"/>
@@ -14521,7 +14721,7 @@
       <c r="P172" s="1"/>
       <c r="Q172" s="1"/>
       <c r="R172" s="1"/>
-      <c r="S172" s="1"/>
+      <c r="S172" s="25"/>
       <c r="T172" s="1"/>
       <c r="U172" s="1"/>
       <c r="V172" s="1"/>
@@ -14575,7 +14775,7 @@
       <c r="P173" s="1"/>
       <c r="Q173" s="1"/>
       <c r="R173" s="1"/>
-      <c r="S173" s="1"/>
+      <c r="S173" s="25"/>
       <c r="T173" s="1"/>
       <c r="U173" s="1"/>
       <c r="V173" s="1"/>
@@ -14629,7 +14829,7 @@
       <c r="P174" s="1"/>
       <c r="Q174" s="1"/>
       <c r="R174" s="1"/>
-      <c r="S174" s="1"/>
+      <c r="S174" s="25"/>
       <c r="T174" s="1"/>
       <c r="U174" s="1"/>
       <c r="V174" s="1"/>
@@ -14683,7 +14883,7 @@
       <c r="P175" s="1"/>
       <c r="Q175" s="1"/>
       <c r="R175" s="1"/>
-      <c r="S175" s="1"/>
+      <c r="S175" s="25"/>
       <c r="T175" s="1"/>
       <c r="U175" s="1"/>
       <c r="V175" s="1"/>
@@ -14737,7 +14937,7 @@
       <c r="P176" s="1"/>
       <c r="Q176" s="1"/>
       <c r="R176" s="1"/>
-      <c r="S176" s="1"/>
+      <c r="S176" s="25"/>
       <c r="T176" s="1"/>
       <c r="U176" s="1"/>
       <c r="V176" s="1"/>
@@ -14791,7 +14991,7 @@
       <c r="P177" s="1"/>
       <c r="Q177" s="1"/>
       <c r="R177" s="1"/>
-      <c r="S177" s="1"/>
+      <c r="S177" s="25"/>
       <c r="T177" s="1"/>
       <c r="U177" s="1"/>
       <c r="V177" s="1"/>
@@ -14845,7 +15045,7 @@
       <c r="P178" s="1"/>
       <c r="Q178" s="1"/>
       <c r="R178" s="1"/>
-      <c r="S178" s="1"/>
+      <c r="S178" s="25"/>
       <c r="T178" s="1"/>
       <c r="U178" s="1"/>
       <c r="V178" s="1"/>
@@ -14899,7 +15099,7 @@
       <c r="P179" s="1"/>
       <c r="Q179" s="1"/>
       <c r="R179" s="1"/>
-      <c r="S179" s="1"/>
+      <c r="S179" s="25"/>
       <c r="T179" s="1"/>
       <c r="U179" s="1"/>
       <c r="V179" s="1"/>
@@ -14953,7 +15153,7 @@
       <c r="P180" s="1"/>
       <c r="Q180" s="1"/>
       <c r="R180" s="1"/>
-      <c r="S180" s="1"/>
+      <c r="S180" s="25"/>
       <c r="T180" s="1"/>
       <c r="U180" s="1"/>
       <c r="V180" s="1"/>
@@ -15007,7 +15207,7 @@
       <c r="P181" s="1"/>
       <c r="Q181" s="1"/>
       <c r="R181" s="1"/>
-      <c r="S181" s="1"/>
+      <c r="S181" s="25"/>
       <c r="T181" s="1"/>
       <c r="U181" s="1"/>
       <c r="V181" s="1"/>
@@ -15061,7 +15261,7 @@
       <c r="P182" s="1"/>
       <c r="Q182" s="1"/>
       <c r="R182" s="1"/>
-      <c r="S182" s="1"/>
+      <c r="S182" s="25"/>
       <c r="T182" s="1"/>
       <c r="U182" s="1"/>
       <c r="V182" s="1"/>
@@ -15115,7 +15315,7 @@
       <c r="P183" s="1"/>
       <c r="Q183" s="1"/>
       <c r="R183" s="1"/>
-      <c r="S183" s="1"/>
+      <c r="S183" s="25"/>
       <c r="T183" s="1"/>
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
@@ -15169,7 +15369,7 @@
       <c r="P184" s="1"/>
       <c r="Q184" s="1"/>
       <c r="R184" s="1"/>
-      <c r="S184" s="1"/>
+      <c r="S184" s="25"/>
       <c r="T184" s="1"/>
       <c r="U184" s="1"/>
       <c r="V184" s="1"/>
@@ -15223,7 +15423,7 @@
       <c r="P185" s="1"/>
       <c r="Q185" s="1"/>
       <c r="R185" s="1"/>
-      <c r="S185" s="1"/>
+      <c r="S185" s="25"/>
       <c r="T185" s="1"/>
       <c r="U185" s="1"/>
       <c r="V185" s="1"/>
@@ -15277,7 +15477,7 @@
       <c r="P186" s="1"/>
       <c r="Q186" s="1"/>
       <c r="R186" s="1"/>
-      <c r="S186" s="1"/>
+      <c r="S186" s="25"/>
       <c r="T186" s="1"/>
       <c r="U186" s="1"/>
       <c r="V186" s="1"/>
@@ -15331,7 +15531,7 @@
       <c r="P187" s="1"/>
       <c r="Q187" s="1"/>
       <c r="R187" s="1"/>
-      <c r="S187" s="1"/>
+      <c r="S187" s="25"/>
       <c r="T187" s="1"/>
       <c r="U187" s="1"/>
       <c r="V187" s="1"/>
@@ -15385,7 +15585,7 @@
       <c r="P188" s="1"/>
       <c r="Q188" s="1"/>
       <c r="R188" s="1"/>
-      <c r="S188" s="1"/>
+      <c r="S188" s="25"/>
       <c r="T188" s="1"/>
       <c r="U188" s="1"/>
       <c r="V188" s="1"/>
@@ -15439,7 +15639,7 @@
       <c r="P189" s="1"/>
       <c r="Q189" s="1"/>
       <c r="R189" s="1"/>
-      <c r="S189" s="1"/>
+      <c r="S189" s="25"/>
       <c r="T189" s="1"/>
       <c r="U189" s="1"/>
       <c r="V189" s="1"/>
@@ -15493,7 +15693,7 @@
       <c r="P190" s="1"/>
       <c r="Q190" s="1"/>
       <c r="R190" s="1"/>
-      <c r="S190" s="1"/>
+      <c r="S190" s="25"/>
       <c r="T190" s="1"/>
       <c r="U190" s="1"/>
       <c r="V190" s="1"/>
@@ -15547,7 +15747,7 @@
       <c r="P191" s="1"/>
       <c r="Q191" s="1"/>
       <c r="R191" s="1"/>
-      <c r="S191" s="1"/>
+      <c r="S191" s="25"/>
       <c r="T191" s="1"/>
       <c r="U191" s="1"/>
       <c r="V191" s="1"/>
@@ -15601,7 +15801,7 @@
       <c r="P192" s="1"/>
       <c r="Q192" s="1"/>
       <c r="R192" s="1"/>
-      <c r="S192" s="1"/>
+      <c r="S192" s="25"/>
       <c r="T192" s="1"/>
       <c r="U192" s="1"/>
       <c r="V192" s="1"/>
@@ -15655,7 +15855,7 @@
       <c r="P193" s="1"/>
       <c r="Q193" s="1"/>
       <c r="R193" s="1"/>
-      <c r="S193" s="1"/>
+      <c r="S193" s="25"/>
       <c r="T193" s="1"/>
       <c r="U193" s="1"/>
       <c r="V193" s="1"/>
@@ -15709,7 +15909,7 @@
       <c r="P194" s="1"/>
       <c r="Q194" s="1"/>
       <c r="R194" s="1"/>
-      <c r="S194" s="1"/>
+      <c r="S194" s="25"/>
       <c r="T194" s="1"/>
       <c r="U194" s="1"/>
       <c r="V194" s="1"/>
@@ -15763,7 +15963,7 @@
       <c r="P195" s="1"/>
       <c r="Q195" s="1"/>
       <c r="R195" s="1"/>
-      <c r="S195" s="1"/>
+      <c r="S195" s="25"/>
       <c r="T195" s="1"/>
       <c r="U195" s="1"/>
       <c r="V195" s="1"/>
@@ -15817,7 +16017,7 @@
       <c r="P196" s="1"/>
       <c r="Q196" s="1"/>
       <c r="R196" s="1"/>
-      <c r="S196" s="1"/>
+      <c r="S196" s="25"/>
       <c r="T196" s="1"/>
       <c r="U196" s="1"/>
       <c r="V196" s="1"/>
@@ -15871,7 +16071,7 @@
       <c r="P197" s="1"/>
       <c r="Q197" s="1"/>
       <c r="R197" s="1"/>
-      <c r="S197" s="1"/>
+      <c r="S197" s="25"/>
       <c r="T197" s="1"/>
       <c r="U197" s="1"/>
       <c r="V197" s="1"/>
@@ -15925,7 +16125,7 @@
       <c r="P198" s="1"/>
       <c r="Q198" s="1"/>
       <c r="R198" s="1"/>
-      <c r="S198" s="1"/>
+      <c r="S198" s="25"/>
       <c r="T198" s="1"/>
       <c r="U198" s="1"/>
       <c r="V198" s="1"/>
@@ -15979,7 +16179,7 @@
       <c r="P199" s="1"/>
       <c r="Q199" s="1"/>
       <c r="R199" s="1"/>
-      <c r="S199" s="1"/>
+      <c r="S199" s="25"/>
       <c r="T199" s="1"/>
       <c r="U199" s="1"/>
       <c r="V199" s="1"/>
@@ -16033,7 +16233,7 @@
       <c r="P200" s="1"/>
       <c r="Q200" s="1"/>
       <c r="R200" s="1"/>
-      <c r="S200" s="1"/>
+      <c r="S200" s="25"/>
       <c r="T200" s="1"/>
       <c r="U200" s="1"/>
       <c r="V200" s="1"/>
@@ -16087,7 +16287,7 @@
       <c r="P201" s="1"/>
       <c r="Q201" s="1"/>
       <c r="R201" s="1"/>
-      <c r="S201" s="1"/>
+      <c r="S201" s="25"/>
       <c r="T201" s="1"/>
       <c r="U201" s="1"/>
       <c r="V201" s="1"/>
@@ -16141,7 +16341,7 @@
       <c r="P202" s="1"/>
       <c r="Q202" s="1"/>
       <c r="R202" s="1"/>
-      <c r="S202" s="1"/>
+      <c r="S202" s="25"/>
       <c r="T202" s="1"/>
       <c r="U202" s="1"/>
       <c r="V202" s="1"/>
@@ -16195,7 +16395,7 @@
       <c r="P203" s="1"/>
       <c r="Q203" s="1"/>
       <c r="R203" s="1"/>
-      <c r="S203" s="1"/>
+      <c r="S203" s="25"/>
       <c r="T203" s="1"/>
       <c r="U203" s="1"/>
       <c r="V203" s="1"/>
@@ -16249,7 +16449,7 @@
       <c r="P204" s="1"/>
       <c r="Q204" s="1"/>
       <c r="R204" s="1"/>
-      <c r="S204" s="1"/>
+      <c r="S204" s="25"/>
       <c r="T204" s="1"/>
       <c r="U204" s="1"/>
       <c r="V204" s="1"/>
@@ -16303,7 +16503,7 @@
       <c r="P205" s="1"/>
       <c r="Q205" s="1"/>
       <c r="R205" s="1"/>
-      <c r="S205" s="1"/>
+      <c r="S205" s="25"/>
       <c r="T205" s="1"/>
       <c r="U205" s="1"/>
       <c r="V205" s="1"/>
@@ -16357,7 +16557,7 @@
       <c r="P206" s="1"/>
       <c r="Q206" s="1"/>
       <c r="R206" s="1"/>
-      <c r="S206" s="1"/>
+      <c r="S206" s="25"/>
       <c r="T206" s="1"/>
       <c r="U206" s="1"/>
       <c r="V206" s="1"/>
@@ -16411,7 +16611,7 @@
       <c r="P207" s="1"/>
       <c r="Q207" s="1"/>
       <c r="R207" s="1"/>
-      <c r="S207" s="1"/>
+      <c r="S207" s="25"/>
       <c r="T207" s="1"/>
       <c r="U207" s="1"/>
       <c r="V207" s="1"/>
@@ -16465,7 +16665,7 @@
       <c r="P208" s="1"/>
       <c r="Q208" s="1"/>
       <c r="R208" s="1"/>
-      <c r="S208" s="1"/>
+      <c r="S208" s="25"/>
       <c r="T208" s="1"/>
       <c r="U208" s="1"/>
       <c r="V208" s="1"/>
@@ -16519,7 +16719,7 @@
       <c r="P209" s="1"/>
       <c r="Q209" s="1"/>
       <c r="R209" s="1"/>
-      <c r="S209" s="1"/>
+      <c r="S209" s="25"/>
       <c r="T209" s="1"/>
       <c r="U209" s="1"/>
       <c r="V209" s="1"/>
@@ -16573,7 +16773,7 @@
       <c r="P210" s="1"/>
       <c r="Q210" s="1"/>
       <c r="R210" s="1"/>
-      <c r="S210" s="1"/>
+      <c r="S210" s="25"/>
       <c r="T210" s="1"/>
       <c r="U210" s="1"/>
       <c r="V210" s="1"/>
@@ -16627,7 +16827,7 @@
       <c r="P211" s="1"/>
       <c r="Q211" s="1"/>
       <c r="R211" s="1"/>
-      <c r="S211" s="1"/>
+      <c r="S211" s="25"/>
       <c r="T211" s="1"/>
       <c r="U211" s="1"/>
       <c r="V211" s="1"/>
@@ -16681,7 +16881,7 @@
       <c r="P212" s="1"/>
       <c r="Q212" s="1"/>
       <c r="R212" s="1"/>
-      <c r="S212" s="1"/>
+      <c r="S212" s="25"/>
       <c r="T212" s="1"/>
       <c r="U212" s="1"/>
       <c r="V212" s="1"/>
@@ -16735,7 +16935,7 @@
       <c r="P213" s="1"/>
       <c r="Q213" s="1"/>
       <c r="R213" s="1"/>
-      <c r="S213" s="1"/>
+      <c r="S213" s="25"/>
       <c r="T213" s="1"/>
       <c r="U213" s="1"/>
       <c r="V213" s="1"/>
@@ -16789,7 +16989,7 @@
       <c r="P214" s="1"/>
       <c r="Q214" s="1"/>
       <c r="R214" s="1"/>
-      <c r="S214" s="1"/>
+      <c r="S214" s="25"/>
       <c r="T214" s="1"/>
       <c r="U214" s="1"/>
       <c r="V214" s="1"/>
@@ -16843,7 +17043,7 @@
       <c r="P215" s="1"/>
       <c r="Q215" s="1"/>
       <c r="R215" s="1"/>
-      <c r="S215" s="1"/>
+      <c r="S215" s="25"/>
       <c r="T215" s="1"/>
       <c r="U215" s="1"/>
       <c r="V215" s="1"/>
@@ -16897,7 +17097,7 @@
       <c r="P216" s="1"/>
       <c r="Q216" s="1"/>
       <c r="R216" s="1"/>
-      <c r="S216" s="1"/>
+      <c r="S216" s="25"/>
       <c r="T216" s="1"/>
       <c r="U216" s="1"/>
       <c r="V216" s="1"/>
@@ -16951,7 +17151,7 @@
       <c r="P217" s="1"/>
       <c r="Q217" s="1"/>
       <c r="R217" s="1"/>
-      <c r="S217" s="1"/>
+      <c r="S217" s="25"/>
       <c r="T217" s="1"/>
       <c r="U217" s="1"/>
       <c r="V217" s="1"/>
@@ -17005,7 +17205,7 @@
       <c r="P218" s="1"/>
       <c r="Q218" s="1"/>
       <c r="R218" s="1"/>
-      <c r="S218" s="1"/>
+      <c r="S218" s="25"/>
       <c r="T218" s="1"/>
       <c r="U218" s="1"/>
       <c r="V218" s="1"/>
@@ -17059,7 +17259,7 @@
       <c r="P219" s="1"/>
       <c r="Q219" s="1"/>
       <c r="R219" s="1"/>
-      <c r="S219" s="1"/>
+      <c r="S219" s="25"/>
       <c r="T219" s="1"/>
       <c r="U219" s="1"/>
       <c r="V219" s="1"/>
@@ -17113,7 +17313,7 @@
       <c r="P220" s="1"/>
       <c r="Q220" s="1"/>
       <c r="R220" s="1"/>
-      <c r="S220" s="1"/>
+      <c r="S220" s="25"/>
       <c r="T220" s="1"/>
       <c r="U220" s="1"/>
       <c r="V220" s="1"/>
@@ -17167,7 +17367,7 @@
       <c r="P221" s="1"/>
       <c r="Q221" s="1"/>
       <c r="R221" s="1"/>
-      <c r="S221" s="1"/>
+      <c r="S221" s="25"/>
       <c r="T221" s="1"/>
       <c r="U221" s="1"/>
       <c r="V221" s="1"/>
@@ -17221,7 +17421,7 @@
       <c r="P222" s="1"/>
       <c r="Q222" s="1"/>
       <c r="R222" s="1"/>
-      <c r="S222" s="1"/>
+      <c r="S222" s="25"/>
       <c r="T222" s="1"/>
       <c r="U222" s="1"/>
       <c r="V222" s="1"/>
@@ -17275,7 +17475,7 @@
       <c r="P223" s="1"/>
       <c r="Q223" s="1"/>
       <c r="R223" s="1"/>
-      <c r="S223" s="1"/>
+      <c r="S223" s="25"/>
       <c r="T223" s="1"/>
       <c r="U223" s="1"/>
       <c r="V223" s="1"/>
@@ -17329,7 +17529,7 @@
       <c r="P224" s="1"/>
       <c r="Q224" s="1"/>
       <c r="R224" s="1"/>
-      <c r="S224" s="1"/>
+      <c r="S224" s="25"/>
       <c r="T224" s="1"/>
       <c r="U224" s="1"/>
       <c r="V224" s="1"/>
@@ -17383,7 +17583,7 @@
       <c r="P225" s="1"/>
       <c r="Q225" s="1"/>
       <c r="R225" s="1"/>
-      <c r="S225" s="1"/>
+      <c r="S225" s="25"/>
       <c r="T225" s="1"/>
       <c r="U225" s="1"/>
       <c r="V225" s="1"/>
@@ -17437,7 +17637,7 @@
       <c r="P226" s="1"/>
       <c r="Q226" s="1"/>
       <c r="R226" s="1"/>
-      <c r="S226" s="1"/>
+      <c r="S226" s="25"/>
       <c r="T226" s="1"/>
       <c r="U226" s="1"/>
       <c r="V226" s="1"/>
@@ -17491,7 +17691,7 @@
       <c r="P227" s="1"/>
       <c r="Q227" s="1"/>
       <c r="R227" s="1"/>
-      <c r="S227" s="1"/>
+      <c r="S227" s="25"/>
       <c r="T227" s="1"/>
       <c r="U227" s="1"/>
       <c r="V227" s="1"/>
@@ -17545,7 +17745,7 @@
       <c r="P228" s="1"/>
       <c r="Q228" s="1"/>
       <c r="R228" s="1"/>
-      <c r="S228" s="1"/>
+      <c r="S228" s="25"/>
       <c r="T228" s="1"/>
       <c r="U228" s="1"/>
       <c r="V228" s="1"/>
@@ -17599,7 +17799,7 @@
       <c r="P229" s="1"/>
       <c r="Q229" s="1"/>
       <c r="R229" s="1"/>
-      <c r="S229" s="1"/>
+      <c r="S229" s="25"/>
       <c r="T229" s="1"/>
       <c r="U229" s="1"/>
       <c r="V229" s="1"/>
@@ -17653,7 +17853,7 @@
       <c r="P230" s="1"/>
       <c r="Q230" s="1"/>
       <c r="R230" s="1"/>
-      <c r="S230" s="1"/>
+      <c r="S230" s="25"/>
       <c r="T230" s="1"/>
       <c r="U230" s="1"/>
       <c r="V230" s="1"/>
@@ -17707,7 +17907,7 @@
       <c r="P231" s="1"/>
       <c r="Q231" s="1"/>
       <c r="R231" s="1"/>
-      <c r="S231" s="1"/>
+      <c r="S231" s="25"/>
       <c r="T231" s="1"/>
       <c r="U231" s="1"/>
       <c r="V231" s="1"/>
@@ -17761,7 +17961,7 @@
       <c r="P232" s="1"/>
       <c r="Q232" s="1"/>
       <c r="R232" s="1"/>
-      <c r="S232" s="1"/>
+      <c r="S232" s="25"/>
       <c r="T232" s="1"/>
       <c r="U232" s="1"/>
       <c r="V232" s="1"/>
@@ -17815,7 +18015,7 @@
       <c r="P233" s="1"/>
       <c r="Q233" s="1"/>
       <c r="R233" s="1"/>
-      <c r="S233" s="1"/>
+      <c r="S233" s="25"/>
       <c r="T233" s="1"/>
       <c r="U233" s="1"/>
       <c r="V233" s="1"/>
@@ -17869,7 +18069,7 @@
       <c r="P234" s="1"/>
       <c r="Q234" s="1"/>
       <c r="R234" s="1"/>
-      <c r="S234" s="1"/>
+      <c r="S234" s="25"/>
       <c r="T234" s="1"/>
       <c r="U234" s="1"/>
       <c r="V234" s="1"/>
@@ -17923,7 +18123,7 @@
       <c r="P235" s="1"/>
       <c r="Q235" s="1"/>
       <c r="R235" s="1"/>
-      <c r="S235" s="1"/>
+      <c r="S235" s="25"/>
       <c r="T235" s="1"/>
       <c r="U235" s="1"/>
       <c r="V235" s="1"/>
@@ -17977,7 +18177,7 @@
       <c r="P236" s="1"/>
       <c r="Q236" s="1"/>
       <c r="R236" s="1"/>
-      <c r="S236" s="1"/>
+      <c r="S236" s="25"/>
       <c r="T236" s="1"/>
       <c r="U236" s="1"/>
       <c r="V236" s="1"/>
@@ -18031,7 +18231,7 @@
       <c r="P237" s="1"/>
       <c r="Q237" s="1"/>
       <c r="R237" s="1"/>
-      <c r="S237" s="1"/>
+      <c r="S237" s="25"/>
       <c r="T237" s="1"/>
       <c r="U237" s="1"/>
       <c r="V237" s="1"/>
@@ -18085,7 +18285,7 @@
       <c r="P238" s="1"/>
       <c r="Q238" s="1"/>
       <c r="R238" s="1"/>
-      <c r="S238" s="1"/>
+      <c r="S238" s="25"/>
       <c r="T238" s="1"/>
       <c r="U238" s="1"/>
       <c r="V238" s="1"/>
@@ -18139,7 +18339,7 @@
       <c r="P239" s="1"/>
       <c r="Q239" s="1"/>
       <c r="R239" s="1"/>
-      <c r="S239" s="1"/>
+      <c r="S239" s="25"/>
       <c r="T239" s="1"/>
       <c r="U239" s="1"/>
       <c r="V239" s="1"/>
@@ -18193,7 +18393,7 @@
       <c r="P240" s="1"/>
       <c r="Q240" s="1"/>
       <c r="R240" s="1"/>
-      <c r="S240" s="1"/>
+      <c r="S240" s="25"/>
       <c r="T240" s="1"/>
       <c r="U240" s="1"/>
       <c r="V240" s="1"/>
@@ -18247,7 +18447,7 @@
       <c r="P241" s="1"/>
       <c r="Q241" s="1"/>
       <c r="R241" s="1"/>
-      <c r="S241" s="1"/>
+      <c r="S241" s="25"/>
       <c r="T241" s="1"/>
       <c r="U241" s="1"/>
       <c r="V241" s="1"/>
@@ -18301,7 +18501,7 @@
       <c r="P242" s="1"/>
       <c r="Q242" s="1"/>
       <c r="R242" s="1"/>
-      <c r="S242" s="1"/>
+      <c r="S242" s="25"/>
       <c r="T242" s="1"/>
       <c r="U242" s="1"/>
       <c r="V242" s="1"/>
@@ -18355,7 +18555,7 @@
       <c r="P243" s="1"/>
       <c r="Q243" s="1"/>
       <c r="R243" s="1"/>
-      <c r="S243" s="1"/>
+      <c r="S243" s="25"/>
       <c r="T243" s="1"/>
       <c r="U243" s="1"/>
       <c r="V243" s="1"/>
@@ -18409,7 +18609,7 @@
       <c r="P244" s="1"/>
       <c r="Q244" s="1"/>
       <c r="R244" s="1"/>
-      <c r="S244" s="1"/>
+      <c r="S244" s="25"/>
       <c r="T244" s="1"/>
       <c r="U244" s="1"/>
       <c r="V244" s="1"/>
@@ -18463,7 +18663,7 @@
       <c r="P245" s="1"/>
       <c r="Q245" s="1"/>
       <c r="R245" s="1"/>
-      <c r="S245" s="1"/>
+      <c r="S245" s="25"/>
       <c r="T245" s="1"/>
       <c r="U245" s="1"/>
       <c r="V245" s="1"/>
@@ -18517,7 +18717,7 @@
       <c r="P246" s="1"/>
       <c r="Q246" s="1"/>
       <c r="R246" s="1"/>
-      <c r="S246" s="1"/>
+      <c r="S246" s="25"/>
       <c r="T246" s="1"/>
       <c r="U246" s="1"/>
       <c r="V246" s="1"/>
@@ -18571,7 +18771,7 @@
       <c r="P247" s="1"/>
       <c r="Q247" s="1"/>
       <c r="R247" s="1"/>
-      <c r="S247" s="1"/>
+      <c r="S247" s="25"/>
       <c r="T247" s="1"/>
       <c r="U247" s="1"/>
       <c r="V247" s="1"/>
@@ -18625,7 +18825,7 @@
       <c r="P248" s="1"/>
       <c r="Q248" s="1"/>
       <c r="R248" s="1"/>
-      <c r="S248" s="1"/>
+      <c r="S248" s="25"/>
       <c r="T248" s="1"/>
       <c r="U248" s="1"/>
       <c r="V248" s="1"/>
@@ -18679,7 +18879,7 @@
       <c r="P249" s="1"/>
       <c r="Q249" s="1"/>
       <c r="R249" s="1"/>
-      <c r="S249" s="1"/>
+      <c r="S249" s="25"/>
       <c r="T249" s="1"/>
       <c r="U249" s="1"/>
       <c r="V249" s="1"/>
@@ -18733,7 +18933,7 @@
       <c r="P250" s="1"/>
       <c r="Q250" s="1"/>
       <c r="R250" s="1"/>
-      <c r="S250" s="1"/>
+      <c r="S250" s="25"/>
       <c r="T250" s="1"/>
       <c r="U250" s="1"/>
       <c r="V250" s="1"/>
@@ -18787,7 +18987,7 @@
       <c r="P251" s="1"/>
       <c r="Q251" s="1"/>
       <c r="R251" s="1"/>
-      <c r="S251" s="1"/>
+      <c r="S251" s="25"/>
       <c r="T251" s="1"/>
       <c r="U251" s="1"/>
       <c r="V251" s="1"/>
@@ -18841,7 +19041,7 @@
       <c r="P252" s="1"/>
       <c r="Q252" s="1"/>
       <c r="R252" s="1"/>
-      <c r="S252" s="1"/>
+      <c r="S252" s="25"/>
       <c r="T252" s="1"/>
       <c r="U252" s="1"/>
       <c r="V252" s="1"/>
@@ -18895,7 +19095,7 @@
       <c r="P253" s="1"/>
       <c r="Q253" s="1"/>
       <c r="R253" s="1"/>
-      <c r="S253" s="1"/>
+      <c r="S253" s="25"/>
       <c r="T253" s="1"/>
       <c r="U253" s="1"/>
       <c r="V253" s="1"/>
@@ -18949,7 +19149,7 @@
       <c r="P254" s="1"/>
       <c r="Q254" s="1"/>
       <c r="R254" s="1"/>
-      <c r="S254" s="1"/>
+      <c r="S254" s="25"/>
       <c r="T254" s="1"/>
       <c r="U254" s="1"/>
       <c r="V254" s="1"/>
@@ -19003,7 +19203,7 @@
       <c r="P255" s="1"/>
       <c r="Q255" s="1"/>
       <c r="R255" s="1"/>
-      <c r="S255" s="1"/>
+      <c r="S255" s="25"/>
       <c r="T255" s="1"/>
       <c r="U255" s="1"/>
       <c r="V255" s="1"/>
@@ -19057,7 +19257,7 @@
       <c r="P256" s="1"/>
       <c r="Q256" s="1"/>
       <c r="R256" s="1"/>
-      <c r="S256" s="1"/>
+      <c r="S256" s="25"/>
       <c r="T256" s="1"/>
       <c r="U256" s="1"/>
       <c r="V256" s="1"/>
@@ -19111,7 +19311,7 @@
       <c r="P257" s="1"/>
       <c r="Q257" s="1"/>
       <c r="R257" s="1"/>
-      <c r="S257" s="1"/>
+      <c r="S257" s="25"/>
       <c r="T257" s="1"/>
       <c r="U257" s="1"/>
       <c r="V257" s="1"/>
@@ -19165,7 +19365,7 @@
       <c r="P258" s="1"/>
       <c r="Q258" s="1"/>
       <c r="R258" s="1"/>
-      <c r="S258" s="1"/>
+      <c r="S258" s="25"/>
       <c r="T258" s="1"/>
       <c r="U258" s="1"/>
       <c r="V258" s="1"/>
@@ -19219,7 +19419,7 @@
       <c r="P259" s="1"/>
       <c r="Q259" s="1"/>
       <c r="R259" s="1"/>
-      <c r="S259" s="1"/>
+      <c r="S259" s="25"/>
       <c r="T259" s="1"/>
       <c r="U259" s="1"/>
       <c r="V259" s="1"/>
@@ -19273,7 +19473,7 @@
       <c r="P260" s="1"/>
       <c r="Q260" s="1"/>
       <c r="R260" s="1"/>
-      <c r="S260" s="1"/>
+      <c r="S260" s="25"/>
       <c r="T260" s="1"/>
       <c r="U260" s="1"/>
       <c r="V260" s="1"/>
@@ -19327,7 +19527,7 @@
       <c r="P261" s="1"/>
       <c r="Q261" s="1"/>
       <c r="R261" s="1"/>
-      <c r="S261" s="1"/>
+      <c r="S261" s="25"/>
       <c r="T261" s="1"/>
       <c r="U261" s="1"/>
       <c r="V261" s="1"/>
@@ -19381,7 +19581,7 @@
       <c r="P262" s="1"/>
       <c r="Q262" s="1"/>
       <c r="R262" s="1"/>
-      <c r="S262" s="1"/>
+      <c r="S262" s="25"/>
       <c r="T262" s="1"/>
       <c r="U262" s="1"/>
       <c r="V262" s="1"/>
@@ -19435,7 +19635,7 @@
       <c r="P263" s="1"/>
       <c r="Q263" s="1"/>
       <c r="R263" s="1"/>
-      <c r="S263" s="1"/>
+      <c r="S263" s="25"/>
       <c r="T263" s="1"/>
       <c r="U263" s="1"/>
       <c r="V263" s="1"/>
@@ -19489,7 +19689,7 @@
       <c r="P264" s="1"/>
       <c r="Q264" s="1"/>
       <c r="R264" s="1"/>
-      <c r="S264" s="1"/>
+      <c r="S264" s="25"/>
       <c r="T264" s="1"/>
       <c r="U264" s="1"/>
       <c r="V264" s="1"/>
@@ -19543,7 +19743,7 @@
       <c r="P265" s="1"/>
       <c r="Q265" s="1"/>
       <c r="R265" s="1"/>
-      <c r="S265" s="1"/>
+      <c r="S265" s="25"/>
       <c r="T265" s="1"/>
       <c r="U265" s="1"/>
       <c r="V265" s="1"/>
@@ -19597,7 +19797,7 @@
       <c r="P266" s="1"/>
       <c r="Q266" s="1"/>
       <c r="R266" s="1"/>
-      <c r="S266" s="1"/>
+      <c r="S266" s="25"/>
       <c r="T266" s="1"/>
       <c r="U266" s="1"/>
       <c r="V266" s="1"/>
@@ -19651,7 +19851,7 @@
       <c r="P267" s="1"/>
       <c r="Q267" s="1"/>
       <c r="R267" s="1"/>
-      <c r="S267" s="1"/>
+      <c r="S267" s="25"/>
       <c r="T267" s="1"/>
       <c r="U267" s="1"/>
       <c r="V267" s="1"/>
@@ -19705,7 +19905,7 @@
       <c r="P268" s="1"/>
       <c r="Q268" s="1"/>
       <c r="R268" s="1"/>
-      <c r="S268" s="1"/>
+      <c r="S268" s="25"/>
       <c r="T268" s="1"/>
       <c r="U268" s="1"/>
       <c r="V268" s="1"/>
@@ -19759,7 +19959,7 @@
       <c r="P269" s="1"/>
       <c r="Q269" s="1"/>
       <c r="R269" s="1"/>
-      <c r="S269" s="1"/>
+      <c r="S269" s="25"/>
       <c r="T269" s="1"/>
       <c r="U269" s="1"/>
       <c r="V269" s="1"/>
@@ -19813,7 +20013,7 @@
       <c r="P270" s="1"/>
       <c r="Q270" s="1"/>
       <c r="R270" s="1"/>
-      <c r="S270" s="1"/>
+      <c r="S270" s="25"/>
       <c r="T270" s="1"/>
       <c r="U270" s="1"/>
       <c r="V270" s="1"/>
@@ -19867,7 +20067,7 @@
       <c r="P271" s="1"/>
       <c r="Q271" s="1"/>
       <c r="R271" s="1"/>
-      <c r="S271" s="1"/>
+      <c r="S271" s="25"/>
       <c r="T271" s="1"/>
       <c r="U271" s="1"/>
       <c r="V271" s="1"/>
@@ -19921,7 +20121,7 @@
       <c r="P272" s="1"/>
       <c r="Q272" s="1"/>
       <c r="R272" s="1"/>
-      <c r="S272" s="1"/>
+      <c r="S272" s="25"/>
       <c r="T272" s="1"/>
       <c r="U272" s="1"/>
       <c r="V272" s="1"/>
@@ -19975,7 +20175,7 @@
       <c r="P273" s="1"/>
       <c r="Q273" s="1"/>
       <c r="R273" s="1"/>
-      <c r="S273" s="1"/>
+      <c r="S273" s="25"/>
       <c r="T273" s="1"/>
       <c r="U273" s="1"/>
       <c r="V273" s="1"/>
@@ -20029,7 +20229,7 @@
       <c r="P274" s="1"/>
       <c r="Q274" s="1"/>
       <c r="R274" s="1"/>
-      <c r="S274" s="1"/>
+      <c r="S274" s="25"/>
       <c r="T274" s="1"/>
       <c r="U274" s="1"/>
       <c r="V274" s="1"/>
@@ -20083,7 +20283,7 @@
       <c r="P275" s="1"/>
       <c r="Q275" s="1"/>
       <c r="R275" s="1"/>
-      <c r="S275" s="1"/>
+      <c r="S275" s="25"/>
       <c r="T275" s="1"/>
       <c r="U275" s="1"/>
       <c r="V275" s="1"/>
@@ -20137,7 +20337,7 @@
       <c r="P276" s="1"/>
       <c r="Q276" s="1"/>
       <c r="R276" s="1"/>
-      <c r="S276" s="1"/>
+      <c r="S276" s="25"/>
       <c r="T276" s="1"/>
       <c r="U276" s="1"/>
       <c r="V276" s="1"/>
@@ -20191,7 +20391,7 @@
       <c r="P277" s="1"/>
       <c r="Q277" s="1"/>
       <c r="R277" s="1"/>
-      <c r="S277" s="1"/>
+      <c r="S277" s="25"/>
       <c r="T277" s="1"/>
       <c r="U277" s="1"/>
       <c r="V277" s="1"/>
@@ -20245,7 +20445,7 @@
       <c r="P278" s="1"/>
       <c r="Q278" s="1"/>
       <c r="R278" s="1"/>
-      <c r="S278" s="1"/>
+      <c r="S278" s="25"/>
       <c r="T278" s="1"/>
       <c r="U278" s="1"/>
       <c r="V278" s="1"/>
@@ -20299,7 +20499,7 @@
       <c r="P279" s="1"/>
       <c r="Q279" s="1"/>
       <c r="R279" s="1"/>
-      <c r="S279" s="1"/>
+      <c r="S279" s="25"/>
       <c r="T279" s="1"/>
       <c r="U279" s="1"/>
       <c r="V279" s="1"/>
@@ -20353,7 +20553,7 @@
       <c r="P280" s="1"/>
       <c r="Q280" s="1"/>
       <c r="R280" s="1"/>
-      <c r="S280" s="1"/>
+      <c r="S280" s="25"/>
       <c r="T280" s="1"/>
       <c r="U280" s="1"/>
       <c r="V280" s="1"/>
@@ -20407,7 +20607,7 @@
       <c r="P281" s="1"/>
       <c r="Q281" s="1"/>
       <c r="R281" s="1"/>
-      <c r="S281" s="1"/>
+      <c r="S281" s="25"/>
       <c r="T281" s="1"/>
       <c r="U281" s="1"/>
       <c r="V281" s="1"/>
@@ -20461,7 +20661,7 @@
       <c r="P282" s="1"/>
       <c r="Q282" s="1"/>
       <c r="R282" s="1"/>
-      <c r="S282" s="1"/>
+      <c r="S282" s="25"/>
       <c r="T282" s="1"/>
       <c r="U282" s="1"/>
       <c r="V282" s="1"/>
@@ -20515,7 +20715,7 @@
       <c r="P283" s="1"/>
       <c r="Q283" s="1"/>
       <c r="R283" s="1"/>
-      <c r="S283" s="1"/>
+      <c r="S283" s="25"/>
       <c r="T283" s="1"/>
       <c r="U283" s="1"/>
       <c r="V283" s="1"/>
@@ -20569,7 +20769,7 @@
       <c r="P284" s="1"/>
       <c r="Q284" s="1"/>
       <c r="R284" s="1"/>
-      <c r="S284" s="1"/>
+      <c r="S284" s="25"/>
       <c r="T284" s="1"/>
       <c r="U284" s="1"/>
       <c r="V284" s="1"/>
@@ -20623,7 +20823,7 @@
       <c r="P285" s="1"/>
       <c r="Q285" s="1"/>
       <c r="R285" s="1"/>
-      <c r="S285" s="1"/>
+      <c r="S285" s="25"/>
       <c r="T285" s="1"/>
       <c r="U285" s="1"/>
       <c r="V285" s="1"/>
@@ -20677,7 +20877,7 @@
       <c r="P286" s="1"/>
       <c r="Q286" s="1"/>
       <c r="R286" s="1"/>
-      <c r="S286" s="1"/>
+      <c r="S286" s="25"/>
       <c r="T286" s="1"/>
       <c r="U286" s="1"/>
       <c r="V286" s="1"/>
@@ -20731,7 +20931,7 @@
       <c r="P287" s="1"/>
       <c r="Q287" s="1"/>
       <c r="R287" s="1"/>
-      <c r="S287" s="1"/>
+      <c r="S287" s="25"/>
       <c r="T287" s="1"/>
       <c r="U287" s="1"/>
       <c r="V287" s="1"/>
@@ -20785,7 +20985,7 @@
       <c r="P288" s="1"/>
       <c r="Q288" s="1"/>
       <c r="R288" s="1"/>
-      <c r="S288" s="1"/>
+      <c r="S288" s="25"/>
       <c r="T288" s="1"/>
       <c r="U288" s="1"/>
       <c r="V288" s="1"/>
@@ -20839,7 +21039,7 @@
       <c r="P289" s="1"/>
       <c r="Q289" s="1"/>
       <c r="R289" s="1"/>
-      <c r="S289" s="1"/>
+      <c r="S289" s="25"/>
       <c r="T289" s="1"/>
       <c r="U289" s="1"/>
       <c r="V289" s="1"/>
@@ -20893,7 +21093,7 @@
       <c r="P290" s="1"/>
       <c r="Q290" s="1"/>
       <c r="R290" s="1"/>
-      <c r="S290" s="1"/>
+      <c r="S290" s="25"/>
       <c r="T290" s="1"/>
       <c r="U290" s="1"/>
       <c r="V290" s="1"/>
@@ -20947,7 +21147,7 @@
       <c r="P291" s="1"/>
       <c r="Q291" s="1"/>
       <c r="R291" s="1"/>
-      <c r="S291" s="1"/>
+      <c r="S291" s="25"/>
       <c r="T291" s="1"/>
       <c r="U291" s="1"/>
       <c r="V291" s="1"/>
@@ -21001,7 +21201,7 @@
       <c r="P292" s="1"/>
       <c r="Q292" s="1"/>
       <c r="R292" s="1"/>
-      <c r="S292" s="1"/>
+      <c r="S292" s="25"/>
       <c r="T292" s="1"/>
       <c r="U292" s="1"/>
       <c r="V292" s="1"/>
@@ -21055,7 +21255,7 @@
       <c r="P293" s="1"/>
       <c r="Q293" s="1"/>
       <c r="R293" s="1"/>
-      <c r="S293" s="1"/>
+      <c r="S293" s="25"/>
       <c r="T293" s="1"/>
       <c r="U293" s="1"/>
       <c r="V293" s="1"/>
@@ -21109,7 +21309,7 @@
       <c r="P294" s="1"/>
       <c r="Q294" s="1"/>
       <c r="R294" s="1"/>
-      <c r="S294" s="1"/>
+      <c r="S294" s="25"/>
       <c r="T294" s="1"/>
       <c r="U294" s="1"/>
       <c r="V294" s="1"/>
@@ -21163,7 +21363,7 @@
       <c r="P295" s="1"/>
       <c r="Q295" s="1"/>
       <c r="R295" s="1"/>
-      <c r="S295" s="1"/>
+      <c r="S295" s="25"/>
       <c r="T295" s="1"/>
       <c r="U295" s="1"/>
       <c r="V295" s="1"/>
@@ -21217,7 +21417,7 @@
       <c r="P296" s="1"/>
       <c r="Q296" s="1"/>
       <c r="R296" s="1"/>
-      <c r="S296" s="1"/>
+      <c r="S296" s="25"/>
       <c r="T296" s="1"/>
       <c r="U296" s="1"/>
       <c r="V296" s="1"/>
@@ -21271,7 +21471,7 @@
       <c r="P297" s="1"/>
       <c r="Q297" s="1"/>
       <c r="R297" s="1"/>
-      <c r="S297" s="1"/>
+      <c r="S297" s="25"/>
       <c r="T297" s="1"/>
       <c r="U297" s="1"/>
       <c r="V297" s="1"/>
@@ -21325,7 +21525,7 @@
       <c r="P298" s="1"/>
       <c r="Q298" s="1"/>
       <c r="R298" s="1"/>
-      <c r="S298" s="1"/>
+      <c r="S298" s="25"/>
       <c r="T298" s="1"/>
       <c r="U298" s="1"/>
       <c r="V298" s="1"/>
@@ -21379,7 +21579,7 @@
       <c r="P299" s="1"/>
       <c r="Q299" s="1"/>
       <c r="R299" s="1"/>
-      <c r="S299" s="1"/>
+      <c r="S299" s="25"/>
       <c r="T299" s="1"/>
       <c r="U299" s="1"/>
       <c r="V299" s="1"/>
@@ -21433,7 +21633,7 @@
       <c r="P300" s="1"/>
       <c r="Q300" s="1"/>
       <c r="R300" s="1"/>
-      <c r="S300" s="1"/>
+      <c r="S300" s="25"/>
       <c r="T300" s="1"/>
       <c r="U300" s="1"/>
       <c r="V300" s="1"/>
@@ -21487,7 +21687,7 @@
       <c r="P301" s="1"/>
       <c r="Q301" s="1"/>
       <c r="R301" s="1"/>
-      <c r="S301" s="1"/>
+      <c r="S301" s="25"/>
       <c r="T301" s="1"/>
       <c r="U301" s="1"/>
       <c r="V301" s="1"/>
@@ -21541,7 +21741,7 @@
       <c r="P302" s="1"/>
       <c r="Q302" s="1"/>
       <c r="R302" s="1"/>
-      <c r="S302" s="1"/>
+      <c r="S302" s="25"/>
       <c r="T302" s="1"/>
       <c r="U302" s="1"/>
       <c r="V302" s="1"/>
@@ -21595,7 +21795,7 @@
       <c r="P303" s="1"/>
       <c r="Q303" s="1"/>
       <c r="R303" s="1"/>
-      <c r="S303" s="1"/>
+      <c r="S303" s="25"/>
       <c r="T303" s="1"/>
       <c r="U303" s="1"/>
       <c r="V303" s="1"/>
@@ -21649,7 +21849,7 @@
       <c r="P304" s="1"/>
       <c r="Q304" s="1"/>
       <c r="R304" s="1"/>
-      <c r="S304" s="1"/>
+      <c r="S304" s="25"/>
       <c r="T304" s="1"/>
       <c r="U304" s="1"/>
       <c r="V304" s="1"/>
@@ -21703,7 +21903,7 @@
       <c r="P305" s="1"/>
       <c r="Q305" s="1"/>
       <c r="R305" s="1"/>
-      <c r="S305" s="1"/>
+      <c r="S305" s="25"/>
       <c r="T305" s="1"/>
       <c r="U305" s="1"/>
       <c r="V305" s="1"/>
@@ -21757,7 +21957,7 @@
       <c r="P306" s="1"/>
       <c r="Q306" s="1"/>
       <c r="R306" s="1"/>
-      <c r="S306" s="1"/>
+      <c r="S306" s="25"/>
       <c r="T306" s="1"/>
       <c r="U306" s="1"/>
       <c r="V306" s="1"/>
@@ -21811,7 +22011,7 @@
       <c r="P307" s="1"/>
       <c r="Q307" s="1"/>
       <c r="R307" s="1"/>
-      <c r="S307" s="1"/>
+      <c r="S307" s="25"/>
       <c r="T307" s="1"/>
       <c r="U307" s="1"/>
       <c r="V307" s="1"/>
@@ -21865,7 +22065,7 @@
       <c r="P308" s="1"/>
       <c r="Q308" s="1"/>
       <c r="R308" s="1"/>
-      <c r="S308" s="1"/>
+      <c r="S308" s="25"/>
       <c r="T308" s="1"/>
       <c r="U308" s="1"/>
       <c r="V308" s="1"/>
@@ -21919,7 +22119,7 @@
       <c r="P309" s="1"/>
       <c r="Q309" s="1"/>
       <c r="R309" s="1"/>
-      <c r="S309" s="1"/>
+      <c r="S309" s="25"/>
       <c r="T309" s="1"/>
       <c r="U309" s="1"/>
       <c r="V309" s="1"/>
@@ -21973,7 +22173,7 @@
       <c r="P310" s="1"/>
       <c r="Q310" s="1"/>
       <c r="R310" s="1"/>
-      <c r="S310" s="1"/>
+      <c r="S310" s="25"/>
       <c r="T310" s="1"/>
       <c r="U310" s="1"/>
       <c r="V310" s="1"/>
@@ -22027,7 +22227,7 @@
       <c r="P311" s="1"/>
       <c r="Q311" s="1"/>
       <c r="R311" s="1"/>
-      <c r="S311" s="1"/>
+      <c r="S311" s="25"/>
       <c r="T311" s="1"/>
       <c r="U311" s="1"/>
       <c r="V311" s="1"/>
@@ -22081,7 +22281,7 @@
       <c r="P312" s="1"/>
       <c r="Q312" s="1"/>
       <c r="R312" s="1"/>
-      <c r="S312" s="1"/>
+      <c r="S312" s="25"/>
       <c r="T312" s="1"/>
       <c r="U312" s="1"/>
       <c r="V312" s="1"/>
@@ -22135,7 +22335,7 @@
       <c r="P313" s="1"/>
       <c r="Q313" s="1"/>
       <c r="R313" s="1"/>
-      <c r="S313" s="1"/>
+      <c r="S313" s="25"/>
       <c r="T313" s="1"/>
       <c r="U313" s="1"/>
       <c r="V313" s="1"/>
@@ -22189,7 +22389,7 @@
       <c r="P314" s="1"/>
       <c r="Q314" s="1"/>
       <c r="R314" s="1"/>
-      <c r="S314" s="1"/>
+      <c r="S314" s="25"/>
       <c r="T314" s="1"/>
       <c r="U314" s="1"/>
       <c r="V314" s="1"/>
@@ -22243,7 +22443,7 @@
       <c r="P315" s="1"/>
       <c r="Q315" s="1"/>
       <c r="R315" s="1"/>
-      <c r="S315" s="1"/>
+      <c r="S315" s="25"/>
       <c r="T315" s="1"/>
       <c r="U315" s="1"/>
       <c r="V315" s="1"/>
@@ -22297,7 +22497,7 @@
       <c r="P316" s="1"/>
       <c r="Q316" s="1"/>
       <c r="R316" s="1"/>
-      <c r="S316" s="1"/>
+      <c r="S316" s="25"/>
       <c r="T316" s="1"/>
       <c r="U316" s="1"/>
       <c r="V316" s="1"/>
@@ -22351,7 +22551,7 @@
       <c r="P317" s="1"/>
       <c r="Q317" s="1"/>
       <c r="R317" s="1"/>
-      <c r="S317" s="1"/>
+      <c r="S317" s="25"/>
       <c r="T317" s="1"/>
       <c r="U317" s="1"/>
       <c r="V317" s="1"/>
@@ -22405,7 +22605,7 @@
       <c r="P318" s="1"/>
       <c r="Q318" s="1"/>
       <c r="R318" s="1"/>
-      <c r="S318" s="1"/>
+      <c r="S318" s="25"/>
       <c r="T318" s="1"/>
       <c r="U318" s="1"/>
       <c r="V318" s="1"/>
@@ -22459,7 +22659,7 @@
       <c r="P319" s="1"/>
       <c r="Q319" s="1"/>
       <c r="R319" s="1"/>
-      <c r="S319" s="1"/>
+      <c r="S319" s="25"/>
       <c r="T319" s="1"/>
       <c r="U319" s="1"/>
       <c r="V319" s="1"/>
@@ -22513,7 +22713,7 @@
       <c r="P320" s="1"/>
       <c r="Q320" s="1"/>
       <c r="R320" s="1"/>
-      <c r="S320" s="1"/>
+      <c r="S320" s="25"/>
       <c r="T320" s="1"/>
       <c r="U320" s="1"/>
       <c r="V320" s="1"/>
@@ -22567,7 +22767,7 @@
       <c r="P321" s="1"/>
       <c r="Q321" s="1"/>
       <c r="R321" s="1"/>
-      <c r="S321" s="1"/>
+      <c r="S321" s="25"/>
       <c r="T321" s="1"/>
       <c r="U321" s="1"/>
       <c r="V321" s="1"/>
@@ -22621,7 +22821,7 @@
       <c r="P322" s="1"/>
       <c r="Q322" s="1"/>
       <c r="R322" s="1"/>
-      <c r="S322" s="1"/>
+      <c r="S322" s="25"/>
       <c r="T322" s="1"/>
       <c r="U322" s="1"/>
       <c r="V322" s="1"/>
@@ -22675,7 +22875,7 @@
       <c r="P323" s="1"/>
       <c r="Q323" s="1"/>
       <c r="R323" s="1"/>
-      <c r="S323" s="1"/>
+      <c r="S323" s="25"/>
       <c r="T323" s="1"/>
       <c r="U323" s="1"/>
       <c r="V323" s="1"/>
@@ -22729,7 +22929,7 @@
       <c r="P324" s="1"/>
       <c r="Q324" s="1"/>
       <c r="R324" s="1"/>
-      <c r="S324" s="1"/>
+      <c r="S324" s="25"/>
       <c r="T324" s="1"/>
       <c r="U324" s="1"/>
       <c r="V324" s="1"/>
@@ -22783,7 +22983,7 @@
       <c r="P325" s="1"/>
       <c r="Q325" s="1"/>
       <c r="R325" s="1"/>
-      <c r="S325" s="1"/>
+      <c r="S325" s="25"/>
       <c r="T325" s="1"/>
       <c r="U325" s="1"/>
       <c r="V325" s="1"/>
@@ -22837,7 +23037,7 @@
       <c r="P326" s="1"/>
       <c r="Q326" s="1"/>
       <c r="R326" s="1"/>
-      <c r="S326" s="1"/>
+      <c r="S326" s="25"/>
       <c r="T326" s="1"/>
       <c r="U326" s="1"/>
       <c r="V326" s="1"/>
@@ -22891,7 +23091,7 @@
       <c r="P327" s="1"/>
       <c r="Q327" s="1"/>
       <c r="R327" s="1"/>
-      <c r="S327" s="1"/>
+      <c r="S327" s="25"/>
       <c r="T327" s="1"/>
       <c r="U327" s="1"/>
       <c r="V327" s="1"/>
@@ -22945,7 +23145,7 @@
       <c r="P328" s="1"/>
       <c r="Q328" s="1"/>
       <c r="R328" s="1"/>
-      <c r="S328" s="1"/>
+      <c r="S328" s="25"/>
       <c r="T328" s="1"/>
       <c r="U328" s="1"/>
       <c r="V328" s="1"/>
@@ -22999,7 +23199,7 @@
       <c r="P329" s="1"/>
       <c r="Q329" s="1"/>
       <c r="R329" s="1"/>
-      <c r="S329" s="1"/>
+      <c r="S329" s="25"/>
       <c r="T329" s="1"/>
       <c r="U329" s="1"/>
       <c r="V329" s="1"/>
@@ -23053,7 +23253,7 @@
       <c r="P330" s="1"/>
       <c r="Q330" s="1"/>
       <c r="R330" s="1"/>
-      <c r="S330" s="1"/>
+      <c r="S330" s="25"/>
       <c r="T330" s="1"/>
       <c r="U330" s="1"/>
       <c r="V330" s="1"/>
@@ -23107,7 +23307,7 @@
       <c r="P331" s="1"/>
       <c r="Q331" s="1"/>
       <c r="R331" s="1"/>
-      <c r="S331" s="1"/>
+      <c r="S331" s="25"/>
       <c r="T331" s="1"/>
       <c r="U331" s="1"/>
       <c r="V331" s="1"/>
@@ -23161,7 +23361,7 @@
       <c r="P332" s="1"/>
       <c r="Q332" s="1"/>
       <c r="R332" s="1"/>
-      <c r="S332" s="1"/>
+      <c r="S332" s="25"/>
       <c r="T332" s="1"/>
       <c r="U332" s="1"/>
       <c r="V332" s="1"/>
@@ -23215,7 +23415,7 @@
       <c r="P333" s="1"/>
       <c r="Q333" s="1"/>
       <c r="R333" s="1"/>
-      <c r="S333" s="1"/>
+      <c r="S333" s="25"/>
       <c r="T333" s="1"/>
       <c r="U333" s="1"/>
       <c r="V333" s="1"/>
@@ -23269,7 +23469,7 @@
       <c r="P334" s="1"/>
       <c r="Q334" s="1"/>
       <c r="R334" s="1"/>
-      <c r="S334" s="1"/>
+      <c r="S334" s="25"/>
       <c r="T334" s="1"/>
       <c r="U334" s="1"/>
       <c r="V334" s="1"/>
@@ -23323,7 +23523,7 @@
       <c r="P335" s="1"/>
       <c r="Q335" s="1"/>
       <c r="R335" s="1"/>
-      <c r="S335" s="1"/>
+      <c r="S335" s="25"/>
       <c r="T335" s="1"/>
       <c r="U335" s="1"/>
       <c r="V335" s="1"/>
@@ -23377,7 +23577,7 @@
       <c r="P336" s="1"/>
       <c r="Q336" s="1"/>
       <c r="R336" s="1"/>
-      <c r="S336" s="1"/>
+      <c r="S336" s="25"/>
       <c r="T336" s="1"/>
       <c r="U336" s="1"/>
       <c r="V336" s="1"/>
@@ -23431,7 +23631,7 @@
       <c r="P337" s="1"/>
       <c r="Q337" s="1"/>
       <c r="R337" s="1"/>
-      <c r="S337" s="1"/>
+      <c r="S337" s="25"/>
       <c r="T337" s="1"/>
       <c r="U337" s="1"/>
       <c r="V337" s="1"/>
@@ -23485,7 +23685,7 @@
       <c r="P338" s="1"/>
       <c r="Q338" s="1"/>
       <c r="R338" s="1"/>
-      <c r="S338" s="1"/>
+      <c r="S338" s="25"/>
       <c r="T338" s="1"/>
       <c r="U338" s="1"/>
       <c r="V338" s="1"/>
@@ -23539,7 +23739,7 @@
       <c r="P339" s="1"/>
       <c r="Q339" s="1"/>
       <c r="R339" s="1"/>
-      <c r="S339" s="1"/>
+      <c r="S339" s="25"/>
       <c r="T339" s="1"/>
       <c r="U339" s="1"/>
       <c r="V339" s="1"/>
@@ -23593,7 +23793,7 @@
       <c r="P340" s="1"/>
       <c r="Q340" s="1"/>
       <c r="R340" s="1"/>
-      <c r="S340" s="1"/>
+      <c r="S340" s="25"/>
       <c r="T340" s="1"/>
       <c r="U340" s="1"/>
       <c r="V340" s="1"/>
@@ -23647,7 +23847,7 @@
       <c r="P341" s="1"/>
       <c r="Q341" s="1"/>
       <c r="R341" s="1"/>
-      <c r="S341" s="1"/>
+      <c r="S341" s="25"/>
       <c r="T341" s="1"/>
       <c r="U341" s="1"/>
       <c r="V341" s="1"/>
@@ -23701,7 +23901,7 @@
       <c r="P342" s="1"/>
       <c r="Q342" s="1"/>
       <c r="R342" s="1"/>
-      <c r="S342" s="1"/>
+      <c r="S342" s="25"/>
       <c r="T342" s="1"/>
       <c r="U342" s="1"/>
       <c r="V342" s="1"/>
@@ -23755,7 +23955,7 @@
       <c r="P343" s="1"/>
       <c r="Q343" s="1"/>
       <c r="R343" s="1"/>
-      <c r="S343" s="1"/>
+      <c r="S343" s="25"/>
       <c r="T343" s="1"/>
       <c r="U343" s="1"/>
       <c r="V343" s="1"/>
@@ -23809,7 +24009,7 @@
       <c r="P344" s="1"/>
       <c r="Q344" s="1"/>
       <c r="R344" s="1"/>
-      <c r="S344" s="1"/>
+      <c r="S344" s="25"/>
       <c r="T344" s="1"/>
       <c r="U344" s="1"/>
       <c r="V344" s="1"/>
@@ -23863,7 +24063,7 @@
       <c r="P345" s="1"/>
       <c r="Q345" s="1"/>
       <c r="R345" s="1"/>
-      <c r="S345" s="1"/>
+      <c r="S345" s="25"/>
       <c r="T345" s="1"/>
       <c r="U345" s="1"/>
       <c r="V345" s="1"/>
@@ -23917,7 +24117,7 @@
       <c r="P346" s="1"/>
       <c r="Q346" s="1"/>
       <c r="R346" s="1"/>
-      <c r="S346" s="1"/>
+      <c r="S346" s="25"/>
       <c r="T346" s="1"/>
       <c r="U346" s="1"/>
       <c r="V346" s="1"/>
@@ -23971,7 +24171,7 @@
       <c r="P347" s="1"/>
       <c r="Q347" s="1"/>
       <c r="R347" s="1"/>
-      <c r="S347" s="1"/>
+      <c r="S347" s="25"/>
       <c r="T347" s="1"/>
       <c r="U347" s="1"/>
       <c r="V347" s="1"/>
@@ -24025,7 +24225,7 @@
       <c r="P348" s="1"/>
       <c r="Q348" s="1"/>
       <c r="R348" s="1"/>
-      <c r="S348" s="1"/>
+      <c r="S348" s="25"/>
       <c r="T348" s="1"/>
       <c r="U348" s="1"/>
       <c r="V348" s="1"/>
@@ -24079,7 +24279,7 @@
       <c r="P349" s="1"/>
       <c r="Q349" s="1"/>
       <c r="R349" s="1"/>
-      <c r="S349" s="1"/>
+      <c r="S349" s="25"/>
       <c r="T349" s="1"/>
       <c r="U349" s="1"/>
       <c r="V349" s="1"/>
@@ -24133,7 +24333,7 @@
       <c r="P350" s="1"/>
       <c r="Q350" s="1"/>
       <c r="R350" s="1"/>
-      <c r="S350" s="1"/>
+      <c r="S350" s="25"/>
       <c r="T350" s="1"/>
       <c r="U350" s="1"/>
       <c r="V350" s="1"/>
@@ -24187,7 +24387,7 @@
       <c r="P351" s="1"/>
       <c r="Q351" s="1"/>
       <c r="R351" s="1"/>
-      <c r="S351" s="1"/>
+      <c r="S351" s="25"/>
       <c r="T351" s="1"/>
       <c r="U351" s="1"/>
       <c r="V351" s="1"/>
@@ -24241,7 +24441,7 @@
       <c r="P352" s="1"/>
       <c r="Q352" s="1"/>
       <c r="R352" s="1"/>
-      <c r="S352" s="1"/>
+      <c r="S352" s="25"/>
       <c r="T352" s="1"/>
       <c r="U352" s="1"/>
       <c r="V352" s="1"/>
@@ -24295,7 +24495,7 @@
       <c r="P353" s="1"/>
       <c r="Q353" s="1"/>
       <c r="R353" s="1"/>
-      <c r="S353" s="1"/>
+      <c r="S353" s="25"/>
       <c r="T353" s="1"/>
       <c r="U353" s="1"/>
       <c r="V353" s="1"/>
@@ -24349,7 +24549,7 @@
       <c r="P354" s="1"/>
       <c r="Q354" s="1"/>
       <c r="R354" s="1"/>
-      <c r="S354" s="1"/>
+      <c r="S354" s="25"/>
       <c r="T354" s="1"/>
       <c r="U354" s="1"/>
       <c r="V354" s="1"/>
@@ -24403,7 +24603,7 @@
       <c r="P355" s="1"/>
       <c r="Q355" s="1"/>
       <c r="R355" s="1"/>
-      <c r="S355" s="1"/>
+      <c r="S355" s="25"/>
       <c r="T355" s="1"/>
       <c r="U355" s="1"/>
       <c r="V355" s="1"/>
@@ -24457,7 +24657,7 @@
       <c r="P356" s="1"/>
       <c r="Q356" s="1"/>
       <c r="R356" s="1"/>
-      <c r="S356" s="1"/>
+      <c r="S356" s="25"/>
       <c r="T356" s="1"/>
       <c r="U356" s="1"/>
       <c r="V356" s="1"/>
@@ -24511,7 +24711,7 @@
       <c r="P357" s="1"/>
       <c r="Q357" s="1"/>
       <c r="R357" s="1"/>
-      <c r="S357" s="1"/>
+      <c r="S357" s="25"/>
       <c r="T357" s="1"/>
       <c r="U357" s="1"/>
       <c r="V357" s="1"/>
@@ -24565,7 +24765,7 @@
       <c r="P358" s="1"/>
       <c r="Q358" s="1"/>
       <c r="R358" s="1"/>
-      <c r="S358" s="1"/>
+      <c r="S358" s="25"/>
       <c r="T358" s="1"/>
       <c r="U358" s="1"/>
       <c r="V358" s="1"/>
@@ -24619,7 +24819,7 @@
       <c r="P359" s="1"/>
       <c r="Q359" s="1"/>
       <c r="R359" s="1"/>
-      <c r="S359" s="1"/>
+      <c r="S359" s="25"/>
       <c r="T359" s="1"/>
       <c r="U359" s="1"/>
       <c r="V359" s="1"/>
@@ -24673,7 +24873,7 @@
       <c r="P360" s="1"/>
       <c r="Q360" s="1"/>
       <c r="R360" s="1"/>
-      <c r="S360" s="1"/>
+      <c r="S360" s="25"/>
       <c r="T360" s="1"/>
       <c r="U360" s="1"/>
       <c r="V360" s="1"/>
@@ -24727,7 +24927,7 @@
       <c r="P361" s="1"/>
       <c r="Q361" s="1"/>
       <c r="R361" s="1"/>
-      <c r="S361" s="1"/>
+      <c r="S361" s="25"/>
       <c r="T361" s="1"/>
       <c r="U361" s="1"/>
       <c r="V361" s="1"/>
@@ -24781,7 +24981,7 @@
       <c r="P362" s="1"/>
       <c r="Q362" s="1"/>
       <c r="R362" s="1"/>
-      <c r="S362" s="1"/>
+      <c r="S362" s="25"/>
       <c r="T362" s="1"/>
       <c r="U362" s="1"/>
       <c r="V362" s="1"/>
@@ -24835,7 +25035,7 @@
       <c r="P363" s="1"/>
       <c r="Q363" s="1"/>
       <c r="R363" s="1"/>
-      <c r="S363" s="1"/>
+      <c r="S363" s="25"/>
       <c r="T363" s="1"/>
       <c r="U363" s="1"/>
       <c r="V363" s="1"/>
@@ -24889,7 +25089,7 @@
       <c r="P364" s="1"/>
       <c r="Q364" s="1"/>
       <c r="R364" s="1"/>
-      <c r="S364" s="1"/>
+      <c r="S364" s="25"/>
       <c r="T364" s="1"/>
       <c r="U364" s="1"/>
       <c r="V364" s="1"/>
@@ -24943,7 +25143,7 @@
       <c r="P365" s="1"/>
       <c r="Q365" s="1"/>
       <c r="R365" s="1"/>
-      <c r="S365" s="1"/>
+      <c r="S365" s="25"/>
       <c r="T365" s="1"/>
       <c r="U365" s="1"/>
       <c r="V365" s="1"/>
@@ -24997,7 +25197,7 @@
       <c r="P366" s="1"/>
       <c r="Q366" s="1"/>
       <c r="R366" s="1"/>
-      <c r="S366" s="1"/>
+      <c r="S366" s="25"/>
       <c r="T366" s="1"/>
       <c r="U366" s="1"/>
       <c r="V366" s="1"/>
@@ -25051,7 +25251,7 @@
       <c r="P367" s="1"/>
       <c r="Q367" s="1"/>
       <c r="R367" s="1"/>
-      <c r="S367" s="1"/>
+      <c r="S367" s="25"/>
       <c r="T367" s="1"/>
       <c r="U367" s="1"/>
       <c r="V367" s="1"/>
@@ -25105,7 +25305,7 @@
       <c r="P368" s="1"/>
       <c r="Q368" s="1"/>
       <c r="R368" s="1"/>
-      <c r="S368" s="1"/>
+      <c r="S368" s="25"/>
       <c r="T368" s="1"/>
       <c r="U368" s="1"/>
       <c r="V368" s="1"/>
@@ -25159,7 +25359,7 @@
       <c r="P369" s="1"/>
       <c r="Q369" s="1"/>
       <c r="R369" s="1"/>
-      <c r="S369" s="1"/>
+      <c r="S369" s="25"/>
       <c r="T369" s="1"/>
       <c r="U369" s="1"/>
       <c r="V369" s="1"/>
@@ -25213,7 +25413,7 @@
       <c r="P370" s="1"/>
       <c r="Q370" s="1"/>
       <c r="R370" s="1"/>
-      <c r="S370" s="1"/>
+      <c r="S370" s="25"/>
       <c r="T370" s="1"/>
       <c r="U370" s="1"/>
       <c r="V370" s="1"/>
@@ -25267,7 +25467,7 @@
       <c r="P371" s="1"/>
       <c r="Q371" s="1"/>
       <c r="R371" s="1"/>
-      <c r="S371" s="1"/>
+      <c r="S371" s="25"/>
       <c r="T371" s="1"/>
       <c r="U371" s="1"/>
       <c r="V371" s="1"/>
@@ -25321,7 +25521,7 @@
       <c r="P372" s="1"/>
       <c r="Q372" s="1"/>
       <c r="R372" s="1"/>
-      <c r="S372" s="1"/>
+      <c r="S372" s="25"/>
       <c r="T372" s="1"/>
       <c r="U372" s="1"/>
       <c r="V372" s="1"/>
@@ -25375,7 +25575,7 @@
       <c r="P373" s="1"/>
       <c r="Q373" s="1"/>
       <c r="R373" s="1"/>
-      <c r="S373" s="1"/>
+      <c r="S373" s="25"/>
       <c r="T373" s="1"/>
       <c r="U373" s="1"/>
       <c r="V373" s="1"/>
@@ -25429,7 +25629,7 @@
       <c r="P374" s="1"/>
       <c r="Q374" s="1"/>
       <c r="R374" s="1"/>
-      <c r="S374" s="1"/>
+      <c r="S374" s="25"/>
       <c r="T374" s="1"/>
       <c r="U374" s="1"/>
       <c r="V374" s="1"/>
@@ -25483,7 +25683,7 @@
       <c r="P375" s="1"/>
       <c r="Q375" s="1"/>
       <c r="R375" s="1"/>
-      <c r="S375" s="1"/>
+      <c r="S375" s="25"/>
       <c r="T375" s="1"/>
       <c r="U375" s="1"/>
       <c r="V375" s="1"/>
@@ -25537,7 +25737,7 @@
       <c r="P376" s="1"/>
       <c r="Q376" s="1"/>
       <c r="R376" s="1"/>
-      <c r="S376" s="1"/>
+      <c r="S376" s="25"/>
       <c r="T376" s="1"/>
       <c r="U376" s="1"/>
       <c r="V376" s="1"/>
@@ -25591,7 +25791,7 @@
       <c r="P377" s="1"/>
       <c r="Q377" s="1"/>
       <c r="R377" s="1"/>
-      <c r="S377" s="1"/>
+      <c r="S377" s="25"/>
       <c r="T377" s="1"/>
       <c r="U377" s="1"/>
       <c r="V377" s="1"/>
@@ -25645,7 +25845,7 @@
       <c r="P378" s="1"/>
       <c r="Q378" s="1"/>
       <c r="R378" s="1"/>
-      <c r="S378" s="1"/>
+      <c r="S378" s="25"/>
       <c r="T378" s="1"/>
       <c r="U378" s="1"/>
       <c r="V378" s="1"/>
@@ -25699,7 +25899,7 @@
       <c r="P379" s="1"/>
       <c r="Q379" s="1"/>
       <c r="R379" s="1"/>
-      <c r="S379" s="1"/>
+      <c r="S379" s="25"/>
       <c r="T379" s="1"/>
       <c r="U379" s="1"/>
       <c r="V379" s="1"/>
@@ -25753,7 +25953,7 @@
       <c r="P380" s="1"/>
       <c r="Q380" s="1"/>
       <c r="R380" s="1"/>
-      <c r="S380" s="1"/>
+      <c r="S380" s="25"/>
       <c r="T380" s="1"/>
       <c r="U380" s="1"/>
       <c r="V380" s="1"/>
@@ -25807,7 +26007,7 @@
       <c r="P381" s="1"/>
       <c r="Q381" s="1"/>
       <c r="R381" s="1"/>
-      <c r="S381" s="1"/>
+      <c r="S381" s="25"/>
       <c r="T381" s="1"/>
       <c r="U381" s="1"/>
       <c r="V381" s="1"/>
@@ -25861,7 +26061,7 @@
       <c r="P382" s="1"/>
       <c r="Q382" s="1"/>
       <c r="R382" s="1"/>
-      <c r="S382" s="1"/>
+      <c r="S382" s="25"/>
       <c r="T382" s="1"/>
       <c r="U382" s="1"/>
       <c r="V382" s="1"/>
@@ -25915,7 +26115,7 @@
       <c r="P383" s="1"/>
       <c r="Q383" s="1"/>
       <c r="R383" s="1"/>
-      <c r="S383" s="1"/>
+      <c r="S383" s="25"/>
       <c r="T383" s="1"/>
       <c r="U383" s="1"/>
       <c r="V383" s="1"/>
@@ -25969,7 +26169,7 @@
       <c r="P384" s="1"/>
       <c r="Q384" s="1"/>
       <c r="R384" s="1"/>
-      <c r="S384" s="1"/>
+      <c r="S384" s="25"/>
       <c r="T384" s="1"/>
       <c r="U384" s="1"/>
       <c r="V384" s="1"/>
@@ -26023,7 +26223,7 @@
       <c r="P385" s="1"/>
       <c r="Q385" s="1"/>
       <c r="R385" s="1"/>
-      <c r="S385" s="1"/>
+      <c r="S385" s="25"/>
       <c r="T385" s="1"/>
       <c r="U385" s="1"/>
       <c r="V385" s="1"/>
@@ -26077,7 +26277,7 @@
       <c r="P386" s="1"/>
       <c r="Q386" s="1"/>
       <c r="R386" s="1"/>
-      <c r="S386" s="1"/>
+      <c r="S386" s="25"/>
       <c r="T386" s="1"/>
       <c r="U386" s="1"/>
       <c r="V386" s="1"/>
@@ -26131,7 +26331,7 @@
       <c r="P387" s="1"/>
       <c r="Q387" s="1"/>
       <c r="R387" s="1"/>
-      <c r="S387" s="1"/>
+      <c r="S387" s="25"/>
       <c r="T387" s="1"/>
       <c r="U387" s="1"/>
       <c r="V387" s="1"/>
@@ -26185,7 +26385,7 @@
       <c r="P388" s="1"/>
       <c r="Q388" s="1"/>
       <c r="R388" s="1"/>
-      <c r="S388" s="1"/>
+      <c r="S388" s="25"/>
       <c r="T388" s="1"/>
       <c r="U388" s="1"/>
       <c r="V388" s="1"/>
@@ -26239,7 +26439,7 @@
       <c r="P389" s="1"/>
       <c r="Q389" s="1"/>
       <c r="R389" s="1"/>
-      <c r="S389" s="1"/>
+      <c r="S389" s="25"/>
       <c r="T389" s="1"/>
       <c r="U389" s="1"/>
       <c r="V389" s="1"/>
@@ -26293,7 +26493,7 @@
       <c r="P390" s="1"/>
       <c r="Q390" s="1"/>
       <c r="R390" s="1"/>
-      <c r="S390" s="1"/>
+      <c r="S390" s="25"/>
       <c r="T390" s="1"/>
       <c r="U390" s="1"/>
       <c r="V390" s="1"/>
@@ -26347,7 +26547,7 @@
       <c r="P391" s="1"/>
       <c r="Q391" s="1"/>
       <c r="R391" s="1"/>
-      <c r="S391" s="1"/>
+      <c r="S391" s="25"/>
       <c r="T391" s="1"/>
       <c r="U391" s="1"/>
       <c r="V391" s="1"/>
@@ -26401,7 +26601,7 @@
       <c r="P392" s="1"/>
       <c r="Q392" s="1"/>
       <c r="R392" s="1"/>
-      <c r="S392" s="1"/>
+      <c r="S392" s="25"/>
       <c r="T392" s="1"/>
       <c r="U392" s="1"/>
       <c r="V392" s="1"/>
@@ -26455,7 +26655,7 @@
       <c r="P393" s="1"/>
       <c r="Q393" s="1"/>
       <c r="R393" s="1"/>
-      <c r="S393" s="1"/>
+      <c r="S393" s="25"/>
       <c r="T393" s="1"/>
       <c r="U393" s="1"/>
       <c r="V393" s="1"/>
@@ -26509,7 +26709,7 @@
       <c r="P394" s="1"/>
       <c r="Q394" s="1"/>
       <c r="R394" s="1"/>
-      <c r="S394" s="1"/>
+      <c r="S394" s="25"/>
       <c r="T394" s="1"/>
       <c r="U394" s="1"/>
       <c r="V394" s="1"/>
@@ -26563,7 +26763,7 @@
       <c r="P395" s="1"/>
       <c r="Q395" s="1"/>
       <c r="R395" s="1"/>
-      <c r="S395" s="1"/>
+      <c r="S395" s="25"/>
       <c r="T395" s="1"/>
       <c r="U395" s="1"/>
       <c r="V395" s="1"/>
@@ -26617,7 +26817,7 @@
       <c r="P396" s="1"/>
       <c r="Q396" s="1"/>
       <c r="R396" s="1"/>
-      <c r="S396" s="1"/>
+      <c r="S396" s="25"/>
       <c r="T396" s="1"/>
       <c r="U396" s="1"/>
       <c r="V396" s="1"/>
@@ -26671,7 +26871,7 @@
       <c r="P397" s="1"/>
       <c r="Q397" s="1"/>
       <c r="R397" s="1"/>
-      <c r="S397" s="1"/>
+      <c r="S397" s="25"/>
       <c r="T397" s="1"/>
       <c r="U397" s="1"/>
       <c r="V397" s="1"/>
@@ -26725,7 +26925,7 @@
       <c r="P398" s="1"/>
       <c r="Q398" s="1"/>
       <c r="R398" s="1"/>
-      <c r="S398" s="1"/>
+      <c r="S398" s="25"/>
       <c r="T398" s="1"/>
       <c r="U398" s="1"/>
       <c r="V398" s="1"/>
@@ -26779,7 +26979,7 @@
       <c r="P399" s="1"/>
       <c r="Q399" s="1"/>
       <c r="R399" s="1"/>
-      <c r="S399" s="1"/>
+      <c r="S399" s="25"/>
       <c r="T399" s="1"/>
       <c r="U399" s="1"/>
       <c r="V399" s="1"/>
@@ -26833,7 +27033,7 @@
       <c r="P400" s="1"/>
       <c r="Q400" s="1"/>
       <c r="R400" s="1"/>
-      <c r="S400" s="1"/>
+      <c r="S400" s="25"/>
       <c r="T400" s="1"/>
       <c r="U400" s="1"/>
       <c r="V400" s="1"/>
@@ -26887,7 +27087,7 @@
       <c r="P401" s="1"/>
       <c r="Q401" s="1"/>
       <c r="R401" s="1"/>
-      <c r="S401" s="1"/>
+      <c r="S401" s="25"/>
       <c r="T401" s="1"/>
       <c r="U401" s="1"/>
       <c r="V401" s="1"/>
@@ -26941,7 +27141,7 @@
       <c r="P402" s="1"/>
       <c r="Q402" s="1"/>
       <c r="R402" s="1"/>
-      <c r="S402" s="1"/>
+      <c r="S402" s="25"/>
       <c r="T402" s="1"/>
       <c r="U402" s="1"/>
       <c r="V402" s="1"/>
@@ -26995,7 +27195,7 @@
       <c r="P403" s="1"/>
       <c r="Q403" s="1"/>
       <c r="R403" s="1"/>
-      <c r="S403" s="1"/>
+      <c r="S403" s="25"/>
       <c r="T403" s="1"/>
       <c r="U403" s="1"/>
       <c r="V403" s="1"/>
@@ -27049,7 +27249,7 @@
       <c r="P404" s="1"/>
       <c r="Q404" s="1"/>
       <c r="R404" s="1"/>
-      <c r="S404" s="1"/>
+      <c r="S404" s="25"/>
       <c r="T404" s="1"/>
       <c r="U404" s="1"/>
       <c r="V404" s="1"/>
@@ -27103,7 +27303,7 @@
       <c r="P405" s="1"/>
       <c r="Q405" s="1"/>
       <c r="R405" s="1"/>
-      <c r="S405" s="1"/>
+      <c r="S405" s="25"/>
       <c r="T405" s="1"/>
       <c r="U405" s="1"/>
       <c r="V405" s="1"/>
@@ -27157,7 +27357,7 @@
       <c r="P406" s="1"/>
       <c r="Q406" s="1"/>
       <c r="R406" s="1"/>
-      <c r="S406" s="1"/>
+      <c r="S406" s="25"/>
       <c r="T406" s="1"/>
       <c r="U406" s="1"/>
       <c r="V406" s="1"/>
@@ -27211,7 +27411,7 @@
       <c r="P407" s="1"/>
       <c r="Q407" s="1"/>
       <c r="R407" s="1"/>
-      <c r="S407" s="1"/>
+      <c r="S407" s="25"/>
       <c r="T407" s="1"/>
       <c r="U407" s="1"/>
       <c r="V407" s="1"/>
@@ -27265,7 +27465,7 @@
       <c r="P408" s="1"/>
       <c r="Q408" s="1"/>
       <c r="R408" s="1"/>
-      <c r="S408" s="1"/>
+      <c r="S408" s="25"/>
       <c r="T408" s="1"/>
       <c r="U408" s="1"/>
       <c r="V408" s="1"/>
@@ -27319,7 +27519,7 @@
       <c r="P409" s="1"/>
       <c r="Q409" s="1"/>
       <c r="R409" s="1"/>
-      <c r="S409" s="1"/>
+      <c r="S409" s="25"/>
       <c r="T409" s="1"/>
       <c r="U409" s="1"/>
       <c r="V409" s="1"/>
@@ -27373,7 +27573,7 @@
       <c r="P410" s="1"/>
       <c r="Q410" s="1"/>
       <c r="R410" s="1"/>
-      <c r="S410" s="1"/>
+      <c r="S410" s="25"/>
       <c r="T410" s="1"/>
       <c r="U410" s="1"/>
       <c r="V410" s="1"/>
@@ -27427,7 +27627,7 @@
       <c r="P411" s="1"/>
       <c r="Q411" s="1"/>
       <c r="R411" s="1"/>
-      <c r="S411" s="1"/>
+      <c r="S411" s="25"/>
       <c r="T411" s="1"/>
       <c r="U411" s="1"/>
       <c r="V411" s="1"/>
@@ -27481,7 +27681,7 @@
       <c r="P412" s="1"/>
       <c r="Q412" s="1"/>
       <c r="R412" s="1"/>
-      <c r="S412" s="1"/>
+      <c r="S412" s="25"/>
       <c r="T412" s="1"/>
       <c r="U412" s="1"/>
       <c r="V412" s="1"/>
@@ -27535,7 +27735,7 @@
       <c r="P413" s="1"/>
       <c r="Q413" s="1"/>
       <c r="R413" s="1"/>
-      <c r="S413" s="1"/>
+      <c r="S413" s="25"/>
       <c r="T413" s="1"/>
       <c r="U413" s="1"/>
       <c r="V413" s="1"/>
@@ -27589,7 +27789,7 @@
       <c r="P414" s="1"/>
       <c r="Q414" s="1"/>
       <c r="R414" s="1"/>
-      <c r="S414" s="1"/>
+      <c r="S414" s="25"/>
       <c r="T414" s="1"/>
       <c r="U414" s="1"/>
       <c r="V414" s="1"/>
@@ -27643,7 +27843,7 @@
       <c r="P415" s="1"/>
       <c r="Q415" s="1"/>
       <c r="R415" s="1"/>
-      <c r="S415" s="1"/>
+      <c r="S415" s="25"/>
       <c r="T415" s="1"/>
       <c r="U415" s="1"/>
       <c r="V415" s="1"/>
@@ -27697,7 +27897,7 @@
       <c r="P416" s="1"/>
       <c r="Q416" s="1"/>
       <c r="R416" s="1"/>
-      <c r="S416" s="1"/>
+      <c r="S416" s="25"/>
       <c r="T416" s="1"/>
       <c r="U416" s="1"/>
       <c r="V416" s="1"/>
@@ -27751,7 +27951,7 @@
       <c r="P417" s="1"/>
       <c r="Q417" s="1"/>
       <c r="R417" s="1"/>
-      <c r="S417" s="1"/>
+      <c r="S417" s="25"/>
       <c r="T417" s="1"/>
       <c r="U417" s="1"/>
       <c r="V417" s="1"/>
@@ -27805,7 +28005,7 @@
       <c r="P418" s="1"/>
       <c r="Q418" s="1"/>
       <c r="R418" s="1"/>
-      <c r="S418" s="1"/>
+      <c r="S418" s="25"/>
       <c r="T418" s="1"/>
       <c r="U418" s="1"/>
       <c r="V418" s="1"/>
@@ -27859,7 +28059,7 @@
       <c r="P419" s="1"/>
       <c r="Q419" s="1"/>
       <c r="R419" s="1"/>
-      <c r="S419" s="1"/>
+      <c r="S419" s="25"/>
       <c r="T419" s="1"/>
       <c r="U419" s="1"/>
       <c r="V419" s="1"/>
@@ -27913,7 +28113,7 @@
       <c r="P420" s="1"/>
       <c r="Q420" s="1"/>
       <c r="R420" s="1"/>
-      <c r="S420" s="1"/>
+      <c r="S420" s="25"/>
       <c r="T420" s="1"/>
       <c r="U420" s="1"/>
       <c r="V420" s="1"/>
@@ -27967,7 +28167,7 @@
       <c r="P421" s="1"/>
       <c r="Q421" s="1"/>
       <c r="R421" s="1"/>
-      <c r="S421" s="1"/>
+      <c r="S421" s="25"/>
       <c r="T421" s="1"/>
       <c r="U421" s="1"/>
       <c r="V421" s="1"/>
@@ -28021,7 +28221,7 @@
       <c r="P422" s="1"/>
       <c r="Q422" s="1"/>
       <c r="R422" s="1"/>
-      <c r="S422" s="1"/>
+      <c r="S422" s="25"/>
       <c r="T422" s="1"/>
       <c r="U422" s="1"/>
       <c r="V422" s="1"/>
@@ -28075,7 +28275,7 @@
       <c r="P423" s="1"/>
       <c r="Q423" s="1"/>
       <c r="R423" s="1"/>
-      <c r="S423" s="1"/>
+      <c r="S423" s="25"/>
       <c r="T423" s="1"/>
       <c r="U423" s="1"/>
       <c r="V423" s="1"/>
@@ -28129,7 +28329,7 @@
       <c r="P424" s="1"/>
       <c r="Q424" s="1"/>
       <c r="R424" s="1"/>
-      <c r="S424" s="1"/>
+      <c r="S424" s="25"/>
       <c r="T424" s="1"/>
       <c r="U424" s="1"/>
       <c r="V424" s="1"/>
@@ -28183,7 +28383,7 @@
       <c r="P425" s="1"/>
       <c r="Q425" s="1"/>
       <c r="R425" s="1"/>
-      <c r="S425" s="1"/>
+      <c r="S425" s="25"/>
       <c r="T425" s="1"/>
       <c r="U425" s="1"/>
       <c r="V425" s="1"/>
@@ -28237,7 +28437,7 @@
       <c r="P426" s="1"/>
       <c r="Q426" s="1"/>
       <c r="R426" s="1"/>
-      <c r="S426" s="1"/>
+      <c r="S426" s="25"/>
       <c r="T426" s="1"/>
       <c r="U426" s="1"/>
       <c r="V426" s="1"/>
@@ -28291,7 +28491,7 @@
       <c r="P427" s="1"/>
       <c r="Q427" s="1"/>
       <c r="R427" s="1"/>
-      <c r="S427" s="1"/>
+      <c r="S427" s="25"/>
       <c r="T427" s="1"/>
       <c r="U427" s="1"/>
       <c r="V427" s="1"/>
@@ -28345,7 +28545,7 @@
       <c r="P428" s="1"/>
       <c r="Q428" s="1"/>
       <c r="R428" s="1"/>
-      <c r="S428" s="1"/>
+      <c r="S428" s="25"/>
       <c r="T428" s="1"/>
       <c r="U428" s="1"/>
       <c r="V428" s="1"/>
@@ -28399,7 +28599,7 @@
       <c r="P429" s="1"/>
       <c r="Q429" s="1"/>
       <c r="R429" s="1"/>
-      <c r="S429" s="1"/>
+      <c r="S429" s="25"/>
       <c r="T429" s="1"/>
       <c r="U429" s="1"/>
       <c r="V429" s="1"/>
@@ -28453,7 +28653,7 @@
       <c r="P430" s="1"/>
       <c r="Q430" s="1"/>
       <c r="R430" s="1"/>
-      <c r="S430" s="1"/>
+      <c r="S430" s="25"/>
       <c r="T430" s="1"/>
       <c r="U430" s="1"/>
       <c r="V430" s="1"/>
@@ -28507,7 +28707,7 @@
       <c r="P431" s="1"/>
       <c r="Q431" s="1"/>
       <c r="R431" s="1"/>
-      <c r="S431" s="1"/>
+      <c r="S431" s="25"/>
       <c r="T431" s="1"/>
       <c r="U431" s="1"/>
       <c r="V431" s="1"/>
@@ -28561,7 +28761,7 @@
       <c r="P432" s="1"/>
       <c r="Q432" s="1"/>
       <c r="R432" s="1"/>
-      <c r="S432" s="1"/>
+      <c r="S432" s="25"/>
       <c r="T432" s="1"/>
       <c r="U432" s="1"/>
       <c r="V432" s="1"/>
@@ -28615,7 +28815,7 @@
       <c r="P433" s="1"/>
       <c r="Q433" s="1"/>
       <c r="R433" s="1"/>
-      <c r="S433" s="1"/>
+      <c r="S433" s="25"/>
       <c r="T433" s="1"/>
       <c r="U433" s="1"/>
       <c r="V433" s="1"/>
@@ -28669,7 +28869,7 @@
       <c r="P434" s="1"/>
       <c r="Q434" s="1"/>
       <c r="R434" s="1"/>
-      <c r="S434" s="1"/>
+      <c r="S434" s="25"/>
       <c r="T434" s="1"/>
       <c r="U434" s="1"/>
       <c r="V434" s="1"/>
@@ -28723,7 +28923,7 @@
       <c r="P435" s="1"/>
       <c r="Q435" s="1"/>
       <c r="R435" s="1"/>
-      <c r="S435" s="1"/>
+      <c r="S435" s="25"/>
       <c r="T435" s="1"/>
       <c r="U435" s="1"/>
       <c r="V435" s="1"/>
@@ -28777,7 +28977,7 @@
       <c r="P436" s="1"/>
       <c r="Q436" s="1"/>
       <c r="R436" s="1"/>
-      <c r="S436" s="1"/>
+      <c r="S436" s="25"/>
       <c r="T436" s="1"/>
       <c r="U436" s="1"/>
       <c r="V436" s="1"/>
@@ -28831,7 +29031,7 @@
       <c r="P437" s="1"/>
       <c r="Q437" s="1"/>
       <c r="R437" s="1"/>
-      <c r="S437" s="1"/>
+      <c r="S437" s="25"/>
       <c r="T437" s="1"/>
       <c r="U437" s="1"/>
       <c r="V437" s="1"/>
@@ -28885,7 +29085,7 @@
       <c r="P438" s="1"/>
       <c r="Q438" s="1"/>
       <c r="R438" s="1"/>
-      <c r="S438" s="1"/>
+      <c r="S438" s="25"/>
       <c r="T438" s="1"/>
       <c r="U438" s="1"/>
       <c r="V438" s="1"/>
@@ -28939,7 +29139,7 @@
       <c r="P439" s="1"/>
       <c r="Q439" s="1"/>
       <c r="R439" s="1"/>
-      <c r="S439" s="1"/>
+      <c r="S439" s="25"/>
       <c r="T439" s="1"/>
       <c r="U439" s="1"/>
       <c r="V439" s="1"/>
@@ -28993,7 +29193,7 @@
       <c r="P440" s="1"/>
       <c r="Q440" s="1"/>
       <c r="R440" s="1"/>
-      <c r="S440" s="1"/>
+      <c r="S440" s="25"/>
       <c r="T440" s="1"/>
       <c r="U440" s="1"/>
       <c r="V440" s="1"/>
@@ -29047,7 +29247,7 @@
       <c r="P441" s="1"/>
       <c r="Q441" s="1"/>
       <c r="R441" s="1"/>
-      <c r="S441" s="1"/>
+      <c r="S441" s="25"/>
       <c r="T441" s="1"/>
       <c r="U441" s="1"/>
       <c r="V441" s="1"/>
@@ -29101,7 +29301,7 @@
       <c r="P442" s="1"/>
       <c r="Q442" s="1"/>
       <c r="R442" s="1"/>
-      <c r="S442" s="1"/>
+      <c r="S442" s="25"/>
       <c r="T442" s="1"/>
       <c r="U442" s="1"/>
       <c r="V442" s="1"/>
@@ -29155,7 +29355,7 @@
       <c r="P443" s="1"/>
       <c r="Q443" s="1"/>
       <c r="R443" s="1"/>
-      <c r="S443" s="1"/>
+      <c r="S443" s="25"/>
       <c r="T443" s="1"/>
       <c r="U443" s="1"/>
       <c r="V443" s="1"/>
@@ -29209,7 +29409,7 @@
       <c r="P444" s="1"/>
       <c r="Q444" s="1"/>
       <c r="R444" s="1"/>
-      <c r="S444" s="1"/>
+      <c r="S444" s="25"/>
       <c r="T444" s="1"/>
       <c r="U444" s="1"/>
       <c r="V444" s="1"/>
@@ -29263,7 +29463,7 @@
       <c r="P445" s="1"/>
       <c r="Q445" s="1"/>
       <c r="R445" s="1"/>
-      <c r="S445" s="1"/>
+      <c r="S445" s="25"/>
       <c r="T445" s="1"/>
       <c r="U445" s="1"/>
       <c r="V445" s="1"/>
@@ -29317,7 +29517,7 @@
       <c r="P446" s="1"/>
       <c r="Q446" s="1"/>
       <c r="R446" s="1"/>
-      <c r="S446" s="1"/>
+      <c r="S446" s="25"/>
       <c r="T446" s="1"/>
       <c r="U446" s="1"/>
       <c r="V446" s="1"/>
@@ -29371,7 +29571,7 @@
       <c r="P447" s="1"/>
       <c r="Q447" s="1"/>
       <c r="R447" s="1"/>
-      <c r="S447" s="1"/>
+      <c r="S447" s="25"/>
       <c r="T447" s="1"/>
       <c r="U447" s="1"/>
       <c r="V447" s="1"/>
@@ -29425,7 +29625,7 @@
       <c r="P448" s="1"/>
       <c r="Q448" s="1"/>
       <c r="R448" s="1"/>
-      <c r="S448" s="1"/>
+      <c r="S448" s="25"/>
       <c r="T448" s="1"/>
       <c r="U448" s="1"/>
       <c r="V448" s="1"/>
@@ -29479,7 +29679,7 @@
       <c r="P449" s="1"/>
       <c r="Q449" s="1"/>
       <c r="R449" s="1"/>
-      <c r="S449" s="1"/>
+      <c r="S449" s="25"/>
       <c r="T449" s="1"/>
       <c r="U449" s="1"/>
       <c r="V449" s="1"/>
@@ -29533,7 +29733,7 @@
       <c r="P450" s="1"/>
       <c r="Q450" s="1"/>
       <c r="R450" s="1"/>
-      <c r="S450" s="1"/>
+      <c r="S450" s="25"/>
       <c r="T450" s="1"/>
       <c r="U450" s="1"/>
       <c r="V450" s="1"/>
@@ -29587,7 +29787,7 @@
       <c r="P451" s="1"/>
       <c r="Q451" s="1"/>
       <c r="R451" s="1"/>
-      <c r="S451" s="1"/>
+      <c r="S451" s="25"/>
       <c r="T451" s="1"/>
       <c r="U451" s="1"/>
       <c r="V451" s="1"/>
@@ -29641,7 +29841,7 @@
       <c r="P452" s="1"/>
       <c r="Q452" s="1"/>
       <c r="R452" s="1"/>
-      <c r="S452" s="1"/>
+      <c r="S452" s="25"/>
       <c r="T452" s="1"/>
       <c r="U452" s="1"/>
       <c r="V452" s="1"/>
@@ -29695,7 +29895,7 @@
       <c r="P453" s="1"/>
       <c r="Q453" s="1"/>
       <c r="R453" s="1"/>
-      <c r="S453" s="1"/>
+      <c r="S453" s="25"/>
       <c r="T453" s="1"/>
       <c r="U453" s="1"/>
       <c r="V453" s="1"/>
@@ -29749,7 +29949,7 @@
       <c r="P454" s="1"/>
       <c r="Q454" s="1"/>
       <c r="R454" s="1"/>
-      <c r="S454" s="1"/>
+      <c r="S454" s="25"/>
       <c r="T454" s="1"/>
       <c r="U454" s="1"/>
       <c r="V454" s="1"/>
@@ -29803,7 +30003,7 @@
       <c r="P455" s="1"/>
       <c r="Q455" s="1"/>
       <c r="R455" s="1"/>
-      <c r="S455" s="1"/>
+      <c r="S455" s="25"/>
       <c r="T455" s="1"/>
       <c r="U455" s="1"/>
       <c r="V455" s="1"/>
@@ -29857,7 +30057,7 @@
       <c r="P456" s="1"/>
       <c r="Q456" s="1"/>
       <c r="R456" s="1"/>
-      <c r="S456" s="1"/>
+      <c r="S456" s="25"/>
       <c r="T456" s="1"/>
       <c r="U456" s="1"/>
       <c r="V456" s="1"/>
@@ -29911,7 +30111,7 @@
       <c r="P457" s="1"/>
       <c r="Q457" s="1"/>
       <c r="R457" s="1"/>
-      <c r="S457" s="1"/>
+      <c r="S457" s="25"/>
       <c r="T457" s="1"/>
       <c r="U457" s="1"/>
       <c r="V457" s="1"/>
@@ -29965,7 +30165,7 @@
       <c r="P458" s="1"/>
       <c r="Q458" s="1"/>
       <c r="R458" s="1"/>
-      <c r="S458" s="1"/>
+      <c r="S458" s="25"/>
       <c r="T458" s="1"/>
       <c r="U458" s="1"/>
       <c r="V458" s="1"/>
@@ -30019,7 +30219,7 @@
       <c r="P459" s="1"/>
       <c r="Q459" s="1"/>
       <c r="R459" s="1"/>
-      <c r="S459" s="1"/>
+      <c r="S459" s="25"/>
       <c r="T459" s="1"/>
       <c r="U459" s="1"/>
       <c r="V459" s="1"/>
@@ -30073,7 +30273,7 @@
       <c r="P460" s="1"/>
       <c r="Q460" s="1"/>
       <c r="R460" s="1"/>
-      <c r="S460" s="1"/>
+      <c r="S460" s="25"/>
       <c r="T460" s="1"/>
       <c r="U460" s="1"/>
       <c r="V460" s="1"/>
@@ -30127,7 +30327,7 @@
       <c r="P461" s="1"/>
       <c r="Q461" s="1"/>
       <c r="R461" s="1"/>
-      <c r="S461" s="1"/>
+      <c r="S461" s="25"/>
       <c r="T461" s="1"/>
       <c r="U461" s="1"/>
       <c r="V461" s="1"/>
@@ -30181,7 +30381,7 @@
       <c r="P462" s="1"/>
       <c r="Q462" s="1"/>
       <c r="R462" s="1"/>
-      <c r="S462" s="1"/>
+      <c r="S462" s="25"/>
       <c r="T462" s="1"/>
       <c r="U462" s="1"/>
       <c r="V462" s="1"/>
@@ -30235,7 +30435,7 @@
       <c r="P463" s="1"/>
       <c r="Q463" s="1"/>
       <c r="R463" s="1"/>
-      <c r="S463" s="1"/>
+      <c r="S463" s="25"/>
       <c r="T463" s="1"/>
       <c r="U463" s="1"/>
       <c r="V463" s="1"/>
@@ -30289,7 +30489,7 @@
       <c r="P464" s="1"/>
       <c r="Q464" s="1"/>
       <c r="R464" s="1"/>
-      <c r="S464" s="1"/>
+      <c r="S464" s="25"/>
       <c r="T464" s="1"/>
       <c r="U464" s="1"/>
       <c r="V464" s="1"/>
@@ -30343,7 +30543,7 @@
       <c r="P465" s="1"/>
       <c r="Q465" s="1"/>
       <c r="R465" s="1"/>
-      <c r="S465" s="1"/>
+      <c r="S465" s="25"/>
       <c r="T465" s="1"/>
       <c r="U465" s="1"/>
       <c r="V465" s="1"/>
@@ -30397,7 +30597,7 @@
       <c r="P466" s="1"/>
       <c r="Q466" s="1"/>
       <c r="R466" s="1"/>
-      <c r="S466" s="1"/>
+      <c r="S466" s="25"/>
       <c r="T466" s="1"/>
       <c r="U466" s="1"/>
       <c r="V466" s="1"/>
@@ -30451,7 +30651,7 @@
       <c r="P467" s="1"/>
       <c r="Q467" s="1"/>
       <c r="R467" s="1"/>
-      <c r="S467" s="1"/>
+      <c r="S467" s="25"/>
       <c r="T467" s="1"/>
       <c r="U467" s="1"/>
       <c r="V467" s="1"/>
@@ -30505,7 +30705,7 @@
       <c r="P468" s="1"/>
       <c r="Q468" s="1"/>
       <c r="R468" s="1"/>
-      <c r="S468" s="1"/>
+      <c r="S468" s="25"/>
       <c r="T468" s="1"/>
       <c r="U468" s="1"/>
       <c r="V468" s="1"/>
@@ -30559,7 +30759,7 @@
       <c r="P469" s="1"/>
       <c r="Q469" s="1"/>
       <c r="R469" s="1"/>
-      <c r="S469" s="1"/>
+      <c r="S469" s="25"/>
       <c r="T469" s="1"/>
       <c r="U469" s="1"/>
       <c r="V469" s="1"/>
@@ -30613,7 +30813,7 @@
       <c r="P470" s="1"/>
       <c r="Q470" s="1"/>
       <c r="R470" s="1"/>
-      <c r="S470" s="1"/>
+      <c r="S470" s="25"/>
       <c r="T470" s="1"/>
       <c r="U470" s="1"/>
       <c r="V470" s="1"/>
@@ -30667,7 +30867,7 @@
       <c r="P471" s="1"/>
       <c r="Q471" s="1"/>
       <c r="R471" s="1"/>
-      <c r="S471" s="1"/>
+      <c r="S471" s="25"/>
       <c r="T471" s="1"/>
       <c r="U471" s="1"/>
       <c r="V471" s="1"/>
@@ -30721,7 +30921,7 @@
       <c r="P472" s="1"/>
       <c r="Q472" s="1"/>
       <c r="R472" s="1"/>
-      <c r="S472" s="1"/>
+      <c r="S472" s="25"/>
       <c r="T472" s="1"/>
       <c r="U472" s="1"/>
       <c r="V472" s="1"/>
@@ -30775,7 +30975,7 @@
       <c r="P473" s="1"/>
       <c r="Q473" s="1"/>
       <c r="R473" s="1"/>
-      <c r="S473" s="1"/>
+      <c r="S473" s="25"/>
       <c r="T473" s="1"/>
       <c r="U473" s="1"/>
       <c r="V473" s="1"/>
@@ -30829,7 +31029,7 @@
       <c r="P474" s="1"/>
       <c r="Q474" s="1"/>
       <c r="R474" s="1"/>
-      <c r="S474" s="1"/>
+      <c r="S474" s="25"/>
       <c r="T474" s="1"/>
       <c r="U474" s="1"/>
       <c r="V474" s="1"/>
@@ -30883,7 +31083,7 @@
       <c r="P475" s="1"/>
       <c r="Q475" s="1"/>
       <c r="R475" s="1"/>
-      <c r="S475" s="1"/>
+      <c r="S475" s="25"/>
       <c r="T475" s="1"/>
       <c r="U475" s="1"/>
       <c r="V475" s="1"/>
@@ -30937,7 +31137,7 @@
       <c r="P476" s="1"/>
       <c r="Q476" s="1"/>
       <c r="R476" s="1"/>
-      <c r="S476" s="1"/>
+      <c r="S476" s="25"/>
       <c r="T476" s="1"/>
       <c r="U476" s="1"/>
       <c r="V476" s="1"/>
@@ -30991,7 +31191,7 @@
       <c r="P477" s="1"/>
       <c r="Q477" s="1"/>
       <c r="R477" s="1"/>
-      <c r="S477" s="1"/>
+      <c r="S477" s="25"/>
       <c r="T477" s="1"/>
       <c r="U477" s="1"/>
       <c r="V477" s="1"/>
@@ -31045,7 +31245,7 @@
       <c r="P478" s="1"/>
       <c r="Q478" s="1"/>
       <c r="R478" s="1"/>
-      <c r="S478" s="1"/>
+      <c r="S478" s="25"/>
       <c r="T478" s="1"/>
       <c r="U478" s="1"/>
       <c r="V478" s="1"/>
@@ -31099,7 +31299,7 @@
       <c r="P479" s="1"/>
       <c r="Q479" s="1"/>
       <c r="R479" s="1"/>
-      <c r="S479" s="1"/>
+      <c r="S479" s="25"/>
       <c r="T479" s="1"/>
       <c r="U479" s="1"/>
       <c r="V479" s="1"/>
@@ -31153,7 +31353,7 @@
       <c r="P480" s="1"/>
       <c r="Q480" s="1"/>
       <c r="R480" s="1"/>
-      <c r="S480" s="1"/>
+      <c r="S480" s="25"/>
       <c r="T480" s="1"/>
       <c r="U480" s="1"/>
       <c r="V480" s="1"/>
@@ -31207,7 +31407,7 @@
       <c r="P481" s="1"/>
       <c r="Q481" s="1"/>
       <c r="R481" s="1"/>
-      <c r="S481" s="1"/>
+      <c r="S481" s="25"/>
       <c r="T481" s="1"/>
       <c r="U481" s="1"/>
       <c r="V481" s="1"/>
@@ -31261,7 +31461,7 @@
       <c r="P482" s="1"/>
       <c r="Q482" s="1"/>
       <c r="R482" s="1"/>
-      <c r="S482" s="1"/>
+      <c r="S482" s="25"/>
       <c r="T482" s="1"/>
       <c r="U482" s="1"/>
       <c r="V482" s="1"/>
@@ -31315,7 +31515,7 @@
       <c r="P483" s="1"/>
       <c r="Q483" s="1"/>
       <c r="R483" s="1"/>
-      <c r="S483" s="1"/>
+      <c r="S483" s="25"/>
       <c r="T483" s="1"/>
       <c r="U483" s="1"/>
       <c r="V483" s="1"/>
@@ -31369,7 +31569,7 @@
       <c r="P484" s="1"/>
       <c r="Q484" s="1"/>
       <c r="R484" s="1"/>
-      <c r="S484" s="1"/>
+      <c r="S484" s="25"/>
       <c r="T484" s="1"/>
       <c r="U484" s="1"/>
       <c r="V484" s="1"/>
@@ -31423,7 +31623,7 @@
       <c r="P485" s="1"/>
       <c r="Q485" s="1"/>
       <c r="R485" s="1"/>
-      <c r="S485" s="1"/>
+      <c r="S485" s="25"/>
       <c r="T485" s="1"/>
       <c r="U485" s="1"/>
       <c r="V485" s="1"/>
@@ -31477,7 +31677,7 @@
       <c r="P486" s="1"/>
       <c r="Q486" s="1"/>
       <c r="R486" s="1"/>
-      <c r="S486" s="1"/>
+      <c r="S486" s="25"/>
       <c r="T486" s="1"/>
       <c r="U486" s="1"/>
       <c r="V486" s="1"/>
@@ -31531,7 +31731,7 @@
       <c r="P487" s="1"/>
       <c r="Q487" s="1"/>
       <c r="R487" s="1"/>
-      <c r="S487" s="1"/>
+      <c r="S487" s="25"/>
       <c r="T487" s="1"/>
       <c r="U487" s="1"/>
       <c r="V487" s="1"/>
@@ -31585,7 +31785,7 @@
       <c r="P488" s="1"/>
       <c r="Q488" s="1"/>
       <c r="R488" s="1"/>
-      <c r="S488" s="1"/>
+      <c r="S488" s="25"/>
       <c r="T488" s="1"/>
       <c r="U488" s="1"/>
       <c r="V488" s="1"/>
@@ -31639,7 +31839,7 @@
       <c r="P489" s="1"/>
       <c r="Q489" s="1"/>
       <c r="R489" s="1"/>
-      <c r="S489" s="1"/>
+      <c r="S489" s="25"/>
       <c r="T489" s="1"/>
       <c r="U489" s="1"/>
       <c r="V489" s="1"/>
@@ -31693,7 +31893,7 @@
       <c r="P490" s="1"/>
       <c r="Q490" s="1"/>
       <c r="R490" s="1"/>
-      <c r="S490" s="1"/>
+      <c r="S490" s="25"/>
       <c r="T490" s="1"/>
       <c r="U490" s="1"/>
       <c r="V490" s="1"/>
@@ -31747,7 +31947,7 @@
       <c r="P491" s="1"/>
       <c r="Q491" s="1"/>
       <c r="R491" s="1"/>
-      <c r="S491" s="1"/>
+      <c r="S491" s="25"/>
       <c r="T491" s="1"/>
       <c r="U491" s="1"/>
       <c r="V491" s="1"/>
@@ -31801,7 +32001,7 @@
       <c r="P492" s="1"/>
       <c r="Q492" s="1"/>
       <c r="R492" s="1"/>
-      <c r="S492" s="1"/>
+      <c r="S492" s="25"/>
       <c r="T492" s="1"/>
       <c r="U492" s="1"/>
       <c r="V492" s="1"/>
@@ -31855,7 +32055,7 @@
       <c r="P493" s="1"/>
       <c r="Q493" s="1"/>
       <c r="R493" s="1"/>
-      <c r="S493" s="1"/>
+      <c r="S493" s="25"/>
       <c r="T493" s="1"/>
       <c r="U493" s="1"/>
       <c r="V493" s="1"/>
@@ -31909,7 +32109,7 @@
       <c r="P494" s="1"/>
       <c r="Q494" s="1"/>
       <c r="R494" s="1"/>
-      <c r="S494" s="1"/>
+      <c r="S494" s="25"/>
       <c r="T494" s="1"/>
       <c r="U494" s="1"/>
       <c r="V494" s="1"/>
@@ -31963,7 +32163,7 @@
       <c r="P495" s="1"/>
       <c r="Q495" s="1"/>
       <c r="R495" s="1"/>
-      <c r="S495" s="1"/>
+      <c r="S495" s="25"/>
       <c r="T495" s="1"/>
       <c r="U495" s="1"/>
       <c r="V495" s="1"/>
@@ -32017,7 +32217,7 @@
       <c r="P496" s="1"/>
       <c r="Q496" s="1"/>
       <c r="R496" s="1"/>
-      <c r="S496" s="1"/>
+      <c r="S496" s="25"/>
       <c r="T496" s="1"/>
       <c r="U496" s="1"/>
       <c r="V496" s="1"/>
@@ -32071,7 +32271,7 @@
       <c r="P497" s="1"/>
       <c r="Q497" s="1"/>
       <c r="R497" s="1"/>
-      <c r="S497" s="1"/>
+      <c r="S497" s="25"/>
       <c r="T497" s="1"/>
       <c r="U497" s="1"/>
       <c r="V497" s="1"/>
@@ -32125,7 +32325,7 @@
       <c r="P498" s="1"/>
       <c r="Q498" s="1"/>
       <c r="R498" s="1"/>
-      <c r="S498" s="1"/>
+      <c r="S498" s="25"/>
       <c r="T498" s="1"/>
       <c r="U498" s="1"/>
       <c r="V498" s="1"/>
@@ -32179,7 +32379,7 @@
       <c r="P499" s="1"/>
       <c r="Q499" s="1"/>
       <c r="R499" s="1"/>
-      <c r="S499" s="1"/>
+      <c r="S499" s="25"/>
       <c r="T499" s="1"/>
       <c r="U499" s="1"/>
       <c r="V499" s="1"/>
@@ -32233,7 +32433,7 @@
       <c r="P500" s="1"/>
       <c r="Q500" s="1"/>
       <c r="R500" s="1"/>
-      <c r="S500" s="1"/>
+      <c r="S500" s="25"/>
       <c r="T500" s="1"/>
       <c r="U500" s="1"/>
       <c r="V500" s="1"/>
